--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2617,136 +2617,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>31</v>
+        <v>27.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>14</v>
       </c>
-      <c r="AR5" t="n">
-        <v>13</v>
-      </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BH5" t="n">
         <v>8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BJ5" t="n">
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
         <v>2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.39</v>
@@ -2755,61 +2755,61 @@
         <v>1.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.31</v>
+        <v>4.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="CC5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CS5" t="n">
         <v>2.05</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.09</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
@@ -2820,88 +2820,88 @@
         <v>1.83</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DB5" t="n">
         <v>2</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="DD5" t="n">
-        <v>81</v>
+        <v>79.33</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="DG5" t="n">
         <v>5</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DI5" t="n">
-        <v>29</v>
+        <v>28.17</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="DN5" t="n">
-        <v>7</v>
+        <v>7.83</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>54.6</v>
+        <v>55.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>18.6</v>
+        <v>17.5</v>
       </c>
       <c r="DU5" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="DV5" t="n">
-        <v>8.4</v>
+        <v>7.67</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.8</v>
+        <v>16.83</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="6">
@@ -8752,61 +8752,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F21" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="H21" t="n">
-        <v>103.67</v>
+        <v>87.75</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M21" t="n">
-        <v>35.33</v>
+        <v>33.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
-        <v>4.67</v>
+        <v>6.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.67</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.33</v>
+        <v>17.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -8923,49 +8923,49 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="n">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU21" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8974,19 +8974,19 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CC21" t="n">
         <v>2.71</v>
@@ -8995,49 +8995,49 @@
         <v>2.94</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.8</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CO21" t="n">
         <v>1.23</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CT21" t="n">
         <v>1.83</v>
@@ -9055,52 +9055,52 @@
         <v>1.41</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="DA21" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DB21" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DC21" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="DD21" t="n">
-        <v>102</v>
+        <v>95.11</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DI21" t="n">
-        <v>30.25</v>
+        <v>30</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DL21" t="n">
-        <v>11.75</v>
+        <v>12.11</v>
       </c>
       <c r="DM21" t="n">
-        <v>7.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DN21" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9112,28 +9112,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>49.12</v>
+        <v>48.11</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT21" t="n">
-        <v>14.63</v>
+        <v>14.33</v>
       </c>
       <c r="DU21" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="DV21" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.62</v>
+        <v>15.56</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
@@ -1363,49 +1363,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>105.33</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>48.75</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="P2" t="n">
-        <v>13.67</v>
+        <v>12.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.67</v>
+        <v>15.25</v>
       </c>
       <c r="R2" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>54.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.33</v>
+        <v>9.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.67</v>
+        <v>19.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1522,70 +1522,70 @@
         <v>1.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.71</v>
+        <v>7.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="CC2" t="n">
         <v>5.7</v>
@@ -1594,58 +1594,58 @@
         <v>6.86</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH2" t="n">
         <v>1.3</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="CM2" t="n">
         <v>2.14</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
         <v>1.44</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="CU2" t="n">
         <v>1.87</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="CW2" t="n">
         <v>1.86</v>
@@ -1654,52 +1654,52 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DD2" t="n">
-        <v>84.86</v>
+        <v>82.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="DI2" t="n">
-        <v>33.86</v>
+        <v>33.38</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="DM2" t="n">
-        <v>11.86</v>
+        <v>12.88</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.72</v>
+        <v>6.62</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>50.43</v>
+        <v>49.38</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DT2" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="DU2" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="DV2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DW2" t="n">
-        <v>17.72</v>
+        <v>17.62</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1835,124 +1835,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" t="n">
-        <v>82</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.67</v>
+        <v>52.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.67</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.71</v>
+        <v>6.38</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
         <v>1.71</v>
@@ -1973,55 +1973,55 @@
         <v>1.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.43</v>
+        <v>3.23</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="CP3" t="n">
         <v>2.23</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="CR3" t="n">
         <v>1.77</v>
@@ -2030,100 +2030,100 @@
         <v>2.08</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="CU3" t="n">
         <v>1.95</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DC3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DD3" t="n">
-        <v>90</v>
+        <v>88.62</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>33.29</v>
+        <v>34.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="DL3" t="n">
-        <v>15.57</v>
+        <v>16.12</v>
       </c>
       <c r="DM3" t="n">
-        <v>12.86</v>
+        <v>12.25</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>56.29</v>
+        <v>56.5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DT3" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.71</v>
+        <v>5.25</v>
       </c>
       <c r="DW3" t="n">
-        <v>15.72</v>
+        <v>14.88</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="4">
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0.5</v>
@@ -3004,49 +3004,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>63.25</v>
+        <v>59.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3058,82 +3058,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37.75</v>
+        <v>37.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BF6" t="n">
         <v>2</v>
       </c>
-      <c r="BD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BY6" t="n">
         <v>3.16</v>
@@ -3142,40 +3142,40 @@
         <v>3.54</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.32</v>
+        <v>8.35</v>
       </c>
       <c r="CD6" t="n">
-        <v>11.18</v>
+        <v>10.87</v>
       </c>
       <c r="CE6" t="n">
         <v>1.47</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI6" t="n">
         <v>1.56</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CK6" t="n">
         <v>1.71</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
         <v>2.04</v>
@@ -3184,82 +3184,82 @@
         <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CT6" t="n">
         <v>1.83</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CV6" t="n">
         <v>1.9</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>80</v>
+        <v>76.22</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>19.25</v>
+        <v>18.44</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DL6" t="n">
-        <v>14.38</v>
+        <v>13.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>12.25</v>
+        <v>12.67</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
@@ -3271,28 +3271,28 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>45.88</v>
+        <v>45</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>9.119999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DU6" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="DV6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DW6" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="DY6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4854,13 +4854,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4947,136 +4947,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>73.33</v>
+        <v>68.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.33</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.33</v>
+        <v>4.25</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>40.67</v>
+        <v>41.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>10.67</v>
+        <v>11.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.14</v>
+        <v>6.38</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.29</v>
+        <v>0.75</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
         <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
         <v>3.06</v>
@@ -5085,61 +5085,61 @@
         <v>3.4</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="CC11" t="n">
-        <v>7.17</v>
+        <v>6.92</v>
       </c>
       <c r="CD11" t="n">
-        <v>7.91</v>
+        <v>8.57</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH11" t="n">
         <v>1.3</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CK11" t="n">
         <v>1.68</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CM11" t="n">
         <v>2.09</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CT11" t="n">
         <v>1.83</v>
@@ -5154,88 +5154,88 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.54</v>
+        <v>4.42</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="DD11" t="n">
-        <v>65.43000000000001</v>
+        <v>64</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>15.57</v>
+        <v>14.62</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>8.140000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>3.43</v>
+        <v>5</v>
       </c>
       <c r="DO11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>42.86</v>
+        <v>43.12</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DT11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DU11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="DW11" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -6039,49 +6039,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>73.5</v>
+        <v>76.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>23.25</v>
+        <v>21.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>13.25</v>
+        <v>11.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.75</v>
+        <v>9.4</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.75</v>
+        <v>51.2</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6198,64 +6198,64 @@
         <v>4.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.71</v>
+        <v>3.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.29</v>
+        <v>3.62</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.54</v>
+        <v>2.83</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="CA14" t="n">
         <v>3.26</v>
@@ -6270,49 +6270,49 @@
         <v>6.5</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CK14" t="n">
         <v>1.81</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN14" t="n">
         <v>1.53</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CT14" t="n">
         <v>1.86</v>
@@ -6327,55 +6327,55 @@
         <v>1.79</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.45</v>
+        <v>4.37</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="DC14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DD14" t="n">
-        <v>64.43000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.43</v>
+        <v>3.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="DI14" t="n">
-        <v>18.86</v>
+        <v>18.38</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DK14" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="DL14" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="DM14" t="n">
         <v>11</v>
       </c>
-      <c r="DM14" t="n">
-        <v>11.43</v>
-      </c>
       <c r="DN14" t="n">
-        <v>5.29</v>
+        <v>4.5</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
@@ -6387,28 +6387,28 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>44.57</v>
+        <v>46.13</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>6.43</v>
+        <v>7.88</v>
       </c>
       <c r="DU14" t="n">
-        <v>3.86</v>
+        <v>5.25</v>
       </c>
       <c r="DV14" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DW14" t="n">
-        <v>10.43</v>
+        <v>10</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="15">
@@ -6418,13 +6418,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0.33</v>
@@ -6508,118 +6508,118 @@
         <v>3.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>101.25</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>32</v>
+        <v>27.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>8</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>53.75</v>
+        <v>51.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>13.25</v>
+        <v>11.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BF15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BP15" t="n">
         <v>2.5</v>
       </c>
-      <c r="BG15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>3</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6628,19 +6628,19 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BU15" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
         <v>1.8</v>
@@ -6649,16 +6649,16 @@
         <v>1.83</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.09</v>
+        <v>3.65</v>
       </c>
       <c r="CE15" t="n">
         <v>1.42</v>
@@ -6667,7 +6667,7 @@
         <v>2.94</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CH15" t="n">
         <v>1.34</v>
@@ -6676,34 +6676,34 @@
         <v>1.79</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CR15" t="n">
         <v>1.83</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
@@ -6720,82 +6720,82 @@
         <v>2.12</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DB15" t="n">
         <v>2</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="DD15" t="n">
-        <v>106.71</v>
+        <v>101.75</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DG15" t="n">
-        <v>5</v>
+        <v>4.38</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>37.28</v>
+        <v>33.75</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.43</v>
+        <v>10.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>8.43</v>
+        <v>7.88</v>
       </c>
       <c r="DN15" t="n">
-        <v>4.43</v>
+        <v>3.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>56.43</v>
+        <v>54.75</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>15.72</v>
+        <v>14.88</v>
       </c>
       <c r="DU15" t="n">
-        <v>10.14</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="DW15" t="n">
-        <v>14.57</v>
+        <v>13.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -7583,94 +7583,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F18" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>76.75</v>
+        <v>79.8</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>25.5</v>
+        <v>26.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.75</v>
+        <v>51.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.5</v>
+        <v>15.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.25</v>
+        <v>18.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7754,70 +7754,70 @@
         <v>3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.38</v>
+        <v>0.78</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.62</v>
+        <v>4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BR18" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS18" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="CA18" t="n">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="CC18" t="n">
         <v>2.92</v>
@@ -7829,19 +7829,19 @@
         <v>1.45</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CK18" t="n">
         <v>1.65</v>
@@ -7853,22 +7853,22 @@
         <v>2.1</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
         <v>1.4</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="CT18" t="n">
         <v>1.85</v>
@@ -7883,88 +7883,88 @@
         <v>1.82</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DB18" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="DD18" t="n">
-        <v>74.12</v>
+        <v>76.11</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="DI18" t="n">
-        <v>26.75</v>
+        <v>27.33</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DK18" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.88</v>
+        <v>10.33</v>
       </c>
       <c r="DM18" t="n">
-        <v>8.119999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DN18" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>45.62</v>
+        <v>46.67</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>12.88</v>
+        <v>13.89</v>
       </c>
       <c r="DU18" t="n">
-        <v>9.25</v>
+        <v>9.33</v>
       </c>
       <c r="DV18" t="n">
-        <v>3.62</v>
+        <v>4.56</v>
       </c>
       <c r="DW18" t="n">
-        <v>17.25</v>
+        <v>17.56</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="19">
@@ -7974,61 +7974,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>93.75</v>
+        <v>96.2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>40.5</v>
+        <v>48.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8040,28 +8040,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.25</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.25</v>
+        <v>11.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AF19" t="n">
         <v>0.25</v>
@@ -8145,37 +8145,37 @@
         <v>3.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.62</v>
+        <v>10.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8184,31 +8184,31 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU19" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX19" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="CC19" t="n">
         <v>3.3</v>
@@ -8220,52 +8220,52 @@
         <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CH19" t="n">
         <v>1.31</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CS19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CV19" t="n">
         <v>1.88</v>
@@ -8277,85 +8277,85 @@
         <v>1.38</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ19" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>89.25</v>
+        <v>91.11</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DG19" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="DI19" t="n">
-        <v>39.62</v>
+        <v>44</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DK19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DL19" t="n">
-        <v>9.880000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="DM19" t="n">
-        <v>9.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="DN19" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>52.38</v>
+        <v>53.44</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>13.75</v>
+        <v>14.44</v>
       </c>
       <c r="DU19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DV19" t="n">
-        <v>5.62</v>
+        <v>6</v>
       </c>
       <c r="DW19" t="n">
-        <v>10.75</v>
+        <v>11.67</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1579,13 +1579,13 @@
         <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CA2" t="n">
         <v>3.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC2" t="n">
         <v>5.7</v>
@@ -1654,10 +1654,10 @@
         <v>1.46</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
@@ -1895,19 +1895,19 @@
         <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="BB3" t="n">
         <v>5.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
         <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF3" t="n">
         <v>3.25</v>
@@ -1976,13 +1976,13 @@
         <v>3.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC3" t="n">
         <v>3.23</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
@@ -2042,13 +2042,13 @@
         <v>1.78</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
@@ -2108,19 +2108,19 @@
         <v>0.38</v>
       </c>
       <c r="DT3" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="DU3" t="n">
         <v>8.75</v>
       </c>
       <c r="DV3" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="DW3" t="n">
         <v>14.88</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DY3" t="n">
         <v>3.38</v>
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2226,49 +2226,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>93.67</v>
+        <v>86.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.67</v>
+        <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.67</v>
+        <v>10.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.67</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2280,82 +2280,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>54.67</v>
+        <v>51.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
         <v>14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.14</v>
+        <v>7.12</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="BR4" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.89</v>
@@ -2364,22 +2364,22 @@
         <v>1.92</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CG4" t="n">
         <v>2.33</v>
@@ -2397,10 +2397,10 @@
         <v>1.73</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN4" t="n">
         <v>1.63</v>
@@ -2409,19 +2409,19 @@
         <v>1.52</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.82</v>
+        <v>4.86</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CU4" t="n">
         <v>1.84</v>
@@ -2436,52 +2436,52 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CZ4" t="n">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="DD4" t="n">
-        <v>97.72</v>
+        <v>93.62</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DI4" t="n">
-        <v>38.86</v>
+        <v>36.75</v>
       </c>
       <c r="DJ4" t="n">
         <v>1</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DL4" t="n">
-        <v>13.43</v>
+        <v>12.88</v>
       </c>
       <c r="DM4" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>5.72</v>
+        <v>6</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>54.14</v>
+        <v>52.62</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>11.86</v>
+        <v>11.12</v>
       </c>
       <c r="DU4" t="n">
-        <v>7.86</v>
+        <v>7.25</v>
       </c>
       <c r="DV4" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DW4" t="n">
-        <v>15.71</v>
+        <v>15.5</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2617,40 +2617,40 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>74.33</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>27.5</v>
+        <v>26.33</v>
       </c>
       <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1</v>
       </c>
-      <c r="AP5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>11.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="AS5" t="n">
         <v>10</v>
@@ -2659,94 +2659,94 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>59.5</v>
+        <v>52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BD5" t="n">
         <v>14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP5" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>83.33</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
         <v>1.39</v>
@@ -2755,22 +2755,22 @@
         <v>1.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.09</v>
+        <v>3.99</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG5" t="n">
         <v>2.84</v>
@@ -2779,37 +2779,37 @@
         <v>1.39</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CK5" t="n">
         <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
@@ -2823,85 +2823,85 @@
         <v>1.3</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DB5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="DD5" t="n">
-        <v>79.33</v>
+        <v>77</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="DG5" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DI5" t="n">
-        <v>28.17</v>
+        <v>27.57</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.17</v>
+        <v>10.57</v>
       </c>
       <c r="DN5" t="n">
-        <v>7.83</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>55.5</v>
+        <v>52.86</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>17.5</v>
+        <v>16.71</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.83</v>
+        <v>9.57</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.83</v>
+        <v>16.43</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="6">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3395,55 +3395,55 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>76</v>
+        <v>87.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>24.67</v>
+        <v>35.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.67</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.67</v>
+        <v>10.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -3452,58 +3452,58 @@
         <v>47</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.67</v>
+        <v>8.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.33</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BJ7" t="n">
         <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="BO7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3512,13 +3512,13 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -3533,40 +3533,40 @@
         <v>2.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.32</v>
+        <v>5.01</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="CI7" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="CM7" t="n">
         <v>1.74</v>
@@ -3578,16 +3578,16 @@
         <v>1.44</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CT7" t="n">
         <v>1.82</v>
@@ -3598,88 +3598,88 @@
       </c>
       <c r="CW7" t="inlineStr"/>
       <c r="CX7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.87</v>
+        <v>1.22</v>
       </c>
       <c r="DD7" t="n">
-        <v>67.62</v>
+        <v>73.56</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="DH7" t="n">
         <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>23.88</v>
+        <v>28.89</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DL7" t="n">
-        <v>12</v>
+        <v>11.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>11</v>
+        <v>10.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>43.62</v>
+        <v>44</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DT7" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.63</v>
+        <v>4.33</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="DW7" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="8">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -3701,82 +3701,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="H8" t="n">
-        <v>120</v>
+        <v>112.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>44.33</v>
+        <v>46.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>8.33</v>
+        <v>9.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="R8" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.33</v>
+        <v>61.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.33</v>
+        <v>15.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.33</v>
+        <v>18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0.2</v>
@@ -3860,70 +3860,70 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CC8" t="n">
         <v>3.12</v>
@@ -3932,49 +3932,49 @@
         <v>3.73</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="CH8" t="n">
         <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN8" t="n">
         <v>1.62</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CT8" t="n">
         <v>1.84</v>
@@ -3989,88 +3989,88 @@
         <v>1.92</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.47</v>
+        <v>4.36</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>90.88</v>
+        <v>90.78</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DG8" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="DI8" t="n">
-        <v>29.87</v>
+        <v>32.44</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DK8" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="DL8" t="n">
-        <v>10.5</v>
+        <v>10.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>7.87</v>
+        <v>7.89</v>
       </c>
       <c r="DN8" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>51.62</v>
+        <v>52.89</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DT8" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="DW8" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DY8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -4080,94 +4080,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>101.25</v>
+        <v>98.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26.25</v>
+        <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>13.25</v>
+        <v>13.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>57.25</v>
+        <v>54.4</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.75</v>
+        <v>8.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4251,70 +4251,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BR9" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS9" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CC9" t="n">
         <v>3.69</v>
@@ -4323,37 +4323,37 @@
         <v>3.32</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF9" t="n">
         <v>3.26</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CK9" t="n">
         <v>1.7</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN9" t="n">
         <v>1.63</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP9" t="n">
         <v>2.34</v>
@@ -4362,10 +4362,10 @@
         <v>4.36</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
@@ -4376,88 +4376,88 @@
       </c>
       <c r="CW9" t="inlineStr"/>
       <c r="CX9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CY9" t="n">
         <v>2.45</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="DD9" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DI9" t="n">
-        <v>28.62</v>
+        <v>26.67</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DL9" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="DM9" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="DN9" t="n">
-        <v>7.12</v>
+        <v>7.33</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>53.38</v>
+        <v>52.22</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="DU9" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="DV9" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="DW9" t="n">
-        <v>15.25</v>
+        <v>16.44</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4467,94 +4467,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>83.75</v>
+        <v>98.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>33.75</v>
+        <v>50</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="R10" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54.25</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.75</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4638,70 +4638,70 @@
         <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.5</v>
+        <v>7.89</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.23</v>
+        <v>2.95</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.39</v>
+        <v>3.01</v>
       </c>
       <c r="CA10" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="CC10" t="n">
         <v>4.22</v>
@@ -4710,49 +4710,49 @@
         <v>4.36</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.14</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CO10" t="n">
         <v>1.49</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CQ10" t="n">
-        <v>5.08</v>
+        <v>4.98</v>
       </c>
       <c r="CR10" t="n">
         <v>1.65</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CT10" t="n">
         <v>1.92</v>
@@ -4763,88 +4763,88 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="CZ10" t="n">
-        <v>5.31</v>
+        <v>5.12</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DD10" t="n">
-        <v>84</v>
+        <v>92.33</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DI10" t="n">
-        <v>32.62</v>
+        <v>41.78</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="DL10" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="DM10" t="n">
-        <v>12.12</v>
+        <v>11.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>53.88</v>
+        <v>53.78</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT10" t="n">
-        <v>11.25</v>
+        <v>12.44</v>
       </c>
       <c r="DU10" t="n">
-        <v>7.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DV10" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="DW10" t="n">
-        <v>16.5</v>
+        <v>17.67</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="DY10" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="11">
@@ -5245,13 +5245,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5338,136 +5338,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.75</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.25</v>
+        <v>35.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT12" t="n">
         <v>2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.25</v>
+        <v>17</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH12" t="n">
-        <v>7</v>
+        <v>7.44</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY12" t="n">
         <v>2.08</v>
@@ -5476,61 +5476,61 @@
         <v>2.11</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CC12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.08</v>
+        <v>5.27</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CP12" t="n">
         <v>2.38</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CT12" t="n">
         <v>1.8</v>
@@ -5545,88 +5545,88 @@
         <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CY12" t="n">
         <v>2.44</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DD12" t="n">
-        <v>105.5</v>
+        <v>105.67</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DI12" t="n">
-        <v>36.88</v>
+        <v>35.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>10.38</v>
+        <v>11.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>55.38</v>
+        <v>55.56</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>13.88</v>
+        <v>13.78</v>
       </c>
       <c r="DU12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="DW12" t="n">
-        <v>16.12</v>
+        <v>16.56</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DY12" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="13">
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -5648,82 +5648,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33</v>
+        <v>4.75</v>
       </c>
       <c r="H13" t="n">
-        <v>115</v>
+        <v>109.5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>6.33</v>
+        <v>7.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.33</v>
+        <v>11.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>66.33</v>
+        <v>64.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>21.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>16.67</v>
+        <v>14.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.33</v>
+        <v>6.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.67</v>
+        <v>17</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5807,49 +5807,49 @@
         <v>3.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BL13" t="n">
         <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5858,19 +5858,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="CA13" t="n">
         <v>3.06</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="CC13" t="n">
         <v>2.67</v>
@@ -5879,145 +5879,145 @@
         <v>2.74</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
         <v>1.71</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.83</v>
+        <v>3.97</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CS13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CT13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CU13" t="n">
         <v>1.95</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW13" t="n">
         <v>1.76</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="DD13" t="n">
-        <v>88.12</v>
+        <v>88.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DG13" t="n">
-        <v>5</v>
+        <v>5.78</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>31.38</v>
+        <v>33.11</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DL13" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>10.75</v>
+        <v>10.44</v>
       </c>
       <c r="DN13" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>52</v>
+        <v>52.67</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT13" t="n">
-        <v>15.12</v>
+        <v>15.56</v>
       </c>
       <c r="DU13" t="n">
-        <v>10.63</v>
+        <v>10.44</v>
       </c>
       <c r="DV13" t="n">
-        <v>4.5</v>
+        <v>5.11</v>
       </c>
       <c r="DW13" t="n">
-        <v>14.5</v>
+        <v>15.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="14">
@@ -6255,13 +6255,13 @@
         <v>2.83</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CA14" t="n">
         <v>3.26</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC14" t="n">
         <v>5.5</v>
@@ -6315,13 +6315,13 @@
         <v>2.16</v>
       </c>
       <c r="CT14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CU14" t="n">
         <v>1.94</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW14" t="n">
         <v>1.79</v>
@@ -6658,7 +6658,7 @@
         <v>3</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CE15" t="n">
         <v>1.42</v>
@@ -6705,11 +6705,15 @@
       <c r="CS15" t="n">
         <v>2.03</v>
       </c>
-      <c r="CT15" t="inlineStr"/>
+      <c r="CT15" t="n">
+        <v>1.75</v>
+      </c>
       <c r="CU15" t="n">
         <v>1.78</v>
       </c>
-      <c r="CV15" t="inlineStr"/>
+      <c r="CV15" t="n">
+        <v>1.98</v>
+      </c>
       <c r="CW15" t="n">
         <v>1.95</v>
       </c>
@@ -6805,13 +6809,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -6895,52 +6899,52 @@
         <v>4.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>73.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>34.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -6952,82 +6956,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>38.25</v>
+        <v>40.2</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>13.75</v>
+        <v>16.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.75</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BS16" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.72</v>
@@ -7036,61 +7040,61 @@
         <v>2.6</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.38</v>
+        <v>4.98</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.01</v>
+        <v>4.65</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="CI16" t="n">
         <v>1.65</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CP16" t="n">
         <v>2.38</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CT16" t="n">
         <v>1.9</v>
@@ -7101,55 +7105,55 @@
       </c>
       <c r="CW16" t="inlineStr"/>
       <c r="CX16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DD16" t="n">
-        <v>77.25</v>
+        <v>85.78</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DI16" t="n">
-        <v>21</v>
+        <v>27.22</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="DL16" t="n">
-        <v>13.25</v>
+        <v>13.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>9.75</v>
+        <v>10.11</v>
       </c>
       <c r="DN16" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
@@ -7161,28 +7165,28 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>45.5</v>
+        <v>45.78</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>12.75</v>
+        <v>12.44</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="DV16" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DW16" t="n">
-        <v>13.25</v>
+        <v>15</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DY16" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="17">
@@ -8365,10 +8369,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -8377,49 +8381,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>84.33</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="M20" t="n">
-        <v>40</v>
+        <v>51.25</v>
       </c>
       <c r="N20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="R20" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8431,28 +8435,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>47</v>
+        <v>48.25</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>19.33</v>
+        <v>19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8536,70 +8540,70 @@
         <v>2.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BP20" t="n">
         <v>6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="BR20" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CA20" t="n">
         <v>3.1</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CC20" t="n">
         <v>3.56</v>
@@ -8611,16 +8615,16 @@
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH20" t="n">
         <v>1.29</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.05</v>
@@ -8629,10 +8633,10 @@
         <v>1.66</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN20" t="n">
         <v>1.7</v>
@@ -8641,16 +8645,16 @@
         <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="n">
@@ -8661,55 +8665,55 @@
         <v>1.88</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CZ20" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DD20" t="n">
-        <v>78.14</v>
+        <v>87.5</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="DG20" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>31</v>
+        <v>37.75</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="DK20" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DL20" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="DM20" t="n">
-        <v>9.289999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DN20" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8721,28 +8725,28 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>46.86</v>
+        <v>47.5</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>12.14</v>
+        <v>12.12</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="DW20" t="n">
-        <v>16.28</v>
+        <v>16.5</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>125.25</v>
+        <v>118.4</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -5272,67 +5272,67 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>34.5</v>
+        <v>33.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="S12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.75</v>
+        <v>59.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.75</v>
+        <v>14.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>16</v>
+        <v>17.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5416,70 +5416,70 @@
         <v>1.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="CC12" t="n">
         <v>4.2</v>
@@ -5488,46 +5488,46 @@
         <v>5.27</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
         <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CS12" t="n">
         <v>2.19</v>
@@ -5545,88 +5545,88 @@
         <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DC12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>105.67</v>
+        <v>104.2</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DI12" t="n">
-        <v>35.11</v>
+        <v>34.4</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="DN12" t="n">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>55.56</v>
+        <v>56.1</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>13.78</v>
+        <v>13.4</v>
       </c>
       <c r="DU12" t="n">
-        <v>9.67</v>
+        <v>9.1</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="DW12" t="n">
-        <v>16.56</v>
+        <v>17.3</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -6027,13 +6027,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6120,49 +6120,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>52.33</v>
+        <v>55.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6174,82 +6174,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>37.67</v>
+        <v>38</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.67</v>
+        <v>6.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.33</v>
+        <v>12</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU14" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
         <v>2.83</v>
@@ -6258,61 +6258,61 @@
         <v>3.06</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="CR14" t="n">
         <v>1.71</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CT14" t="n">
         <v>1.84</v>
@@ -6327,55 +6327,55 @@
         <v>1.79</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DD14" t="n">
-        <v>67.62</v>
+        <v>67.33</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DI14" t="n">
-        <v>18.38</v>
+        <v>18.67</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DK14" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DL14" t="n">
-        <v>10.12</v>
+        <v>10.56</v>
       </c>
       <c r="DM14" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
@@ -6387,28 +6387,28 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>46.13</v>
+        <v>45.33</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DT14" t="n">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="DU14" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="DV14" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="DW14" t="n">
-        <v>10</v>
+        <v>10.78</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1444,49 +1444,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1507,73 +1507,73 @@
         <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
         <v>2.08</v>
@@ -1582,25 +1582,25 @@
         <v>2.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.7</v>
+        <v>5.76</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.86</v>
+        <v>6.8</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CH2" t="n">
         <v>1.3</v>
@@ -1609,97 +1609,97 @@
         <v>1.64</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CK2" t="n">
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN2" t="n">
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.37</v>
+        <v>4.25</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CT2" t="n">
         <v>1.82</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CV2" t="n">
         <v>1.9</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>82.75</v>
+        <v>80.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>33.38</v>
+        <v>33.67</v>
       </c>
       <c r="DJ2" t="n">
         <v>1</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DL2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DM2" t="n">
-        <v>12.88</v>
+        <v>12.44</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>49.38</v>
+        <v>47.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DU2" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DV2" t="n">
         <v>3</v>
       </c>
       <c r="DW2" t="n">
-        <v>17.62</v>
+        <v>17.56</v>
       </c>
       <c r="DX2" t="n">
         <v>1.21</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -4080,94 +4080,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>3.33</v>
       </c>
       <c r="H9" t="n">
-        <v>98.2</v>
+        <v>99.67</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6.17</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>23.2</v>
+        <v>28.67</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P9" t="n">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>54.4</v>
+        <v>55.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.6</v>
+        <v>13.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.4</v>
+        <v>9.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.2</v>
+        <v>17.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4251,70 +4251,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="BR9" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT9" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC9" t="n">
         <v>3.69</v>
@@ -4326,7 +4326,7 @@
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CG9" t="n">
         <v>2.43</v>
@@ -4335,129 +4335,133 @@
         <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CS9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>2.08</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
       </c>
-      <c r="CU9" t="inlineStr"/>
+      <c r="CU9" t="n">
+        <v>1.87</v>
+      </c>
       <c r="CV9" t="n">
         <v>1.84</v>
       </c>
-      <c r="CW9" t="inlineStr"/>
+      <c r="CW9" t="n">
+        <v>1.86</v>
+      </c>
       <c r="CX9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.66</v>
+        <v>4.55</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="DD9" t="n">
-        <v>94</v>
+        <v>95.3</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="DG9" t="n">
-        <v>4.44</v>
+        <v>5.2</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DI9" t="n">
-        <v>26.67</v>
+        <v>29.6</v>
       </c>
       <c r="DJ9" t="n">
         <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.11</v>
+        <v>13.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="DN9" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>52.22</v>
+        <v>53.2</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.33</v>
+        <v>12.7</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DV9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DW9" t="n">
-        <v>16.44</v>
+        <v>16.9</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DY9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -6120,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
@@ -6132,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AL14" t="n">
         <v>1.25</v>
@@ -6195,7 +6199,7 @@
         <v>0.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
         <v>2.89</v>
@@ -6339,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="DC14" t="n">
         <v>1</v>
@@ -6351,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="DG14" t="n">
         <v>3.78</v>
@@ -6408,7 +6412,7 @@
         <v>0.87</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="15">
@@ -6418,94 +6422,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>114</v>
+        <v>112.25</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>7.67</v>
+        <v>8.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M15" t="n">
-        <v>44.33</v>
+        <v>48.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>13.67</v>
+        <v>12.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.67</v>
+        <v>10.25</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.67</v>
+        <v>19.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>14.33</v>
+        <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.33</v>
+        <v>17.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6589,37 +6593,37 @@
         <v>2.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BP15" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6628,31 +6632,31 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="CC15" t="n">
         <v>3</v>
@@ -6661,46 +6665,46 @@
         <v>3.64</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH15" t="n">
         <v>1.34</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK15" t="n">
         <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CS15" t="n">
         <v>2.03</v>
@@ -6709,94 +6713,94 @@
         <v>1.75</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="CV15" t="n">
         <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="n">
         <v>1.35</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DB15" t="n">
         <v>2</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.87</v>
+        <v>1.33</v>
       </c>
       <c r="DD15" t="n">
-        <v>101.75</v>
+        <v>102.33</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
         <v>3</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.38</v>
+        <v>5.22</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DI15" t="n">
-        <v>33.75</v>
+        <v>36.67</v>
       </c>
       <c r="DJ15" t="n">
         <v>1</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.13</v>
+        <v>10.11</v>
       </c>
       <c r="DM15" t="n">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="DN15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>54.75</v>
+        <v>56</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>14.88</v>
+        <v>15.22</v>
       </c>
       <c r="DU15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="DW15" t="n">
-        <v>13.12</v>
+        <v>14.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="DY15" t="n">
         <v>3</v>
@@ -6809,13 +6813,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -6899,139 +6903,139 @@
         <v>4.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>89.59999999999999</v>
+        <v>89.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>34.6</v>
+        <v>30.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.6</v>
+        <v>15.17</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>10.83</v>
       </c>
       <c r="AS16" t="n">
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BP16" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="BR16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV16" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY16" t="n">
         <v>2.72</v>
@@ -7040,28 +7044,28 @@
         <v>2.6</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CB16" t="n">
         <v>3.1</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.98</v>
+        <v>4.7</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.65</v>
+        <v>4.46</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="CI16" t="n">
         <v>1.65</v>
@@ -7070,90 +7074,94 @@
         <v>2.12</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CT16" t="n">
         <v>1.9</v>
       </c>
-      <c r="CU16" t="inlineStr"/>
+      <c r="CU16" t="n">
+        <v>1.88</v>
+      </c>
       <c r="CV16" t="n">
         <v>1.82</v>
       </c>
-      <c r="CW16" t="inlineStr"/>
+      <c r="CW16" t="n">
+        <v>1.84</v>
+      </c>
       <c r="CX16" t="n">
         <v>1.47</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DD16" t="n">
-        <v>85.78</v>
+        <v>86.2</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="DI16" t="n">
-        <v>27.22</v>
+        <v>25.6</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>13.33</v>
+        <v>13.3</v>
       </c>
       <c r="DM16" t="n">
-        <v>10.11</v>
+        <v>9.6</v>
       </c>
       <c r="DN16" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
@@ -7165,28 +7173,28 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>45.78</v>
+        <v>45.2</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>12.44</v>
+        <v>11.8</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.56</v>
+        <v>7.3</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DY16" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -7196,10 +7204,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -7208,79 +7216,79 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>86.75</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M17" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.75</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.75</v>
+        <v>19.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7367,49 +7375,49 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.75</v>
+        <v>4.11</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU17" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7418,19 +7426,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC17" t="n">
         <v>4.9</v>
@@ -7442,58 +7450,58 @@
         <v>1.49</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ17" t="n">
         <v>2.18</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CV17" t="n">
         <v>1.92</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX17" t="n">
         <v>1.5</v>
@@ -7502,82 +7510,82 @@
         <v>2.58</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.93</v>
+        <v>4.95</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DD17" t="n">
-        <v>81.12</v>
+        <v>82.33</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>20.12</v>
+        <v>21.89</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="DL17" t="n">
-        <v>8</v>
+        <v>8.44</v>
       </c>
       <c r="DM17" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="DN17" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>47.38</v>
+        <v>48.78</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DT17" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DU17" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DW17" t="n">
-        <v>16.12</v>
+        <v>16.89</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="18">
@@ -7978,13 +7986,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>0.4</v>
@@ -8068,118 +8076,118 @@
         <v>3.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>84.75</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>38.75</v>
+        <v>35.6</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>46.75</v>
+        <v>45</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.25</v>
+        <v>13.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.33</v>
+        <v>10.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.44</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8188,19 +8196,19 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BY19" t="n">
         <v>1.82</v>
@@ -8209,22 +8217,22 @@
         <v>1.8</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CE19" t="n">
         <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG19" t="n">
         <v>2.49</v>
@@ -8233,37 +8241,37 @@
         <v>1.31</v>
       </c>
       <c r="CI19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CN19" t="n">
         <v>1.74</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>1.73</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CS19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
@@ -8278,88 +8286,88 @@
         <v>1.86</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CZ19" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="DD19" t="n">
-        <v>91.11</v>
+        <v>87.8</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>6.78</v>
+        <v>6.3</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DI19" t="n">
-        <v>44</v>
+        <v>41.9</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DK19" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DL19" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="DN19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>53.44</v>
+        <v>51.9</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>14.44</v>
+        <v>14.3</v>
       </c>
       <c r="DU19" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DV19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="DW19" t="n">
-        <v>11.67</v>
+        <v>12.2</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2620,133 +2620,133 @@
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.33</v>
+        <v>83.25</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AL5" t="n">
         <v>6</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.33</v>
+        <v>31</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.33</v>
+        <v>13.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.67</v>
+        <v>13.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52</v>
+        <v>55.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>14.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.39</v>
@@ -2755,25 +2755,25 @@
         <v>1.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.31</v>
+        <v>1.73</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.39</v>
@@ -2782,34 +2782,34 @@
         <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
@@ -2829,79 +2829,79 @@
         <v>3.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="DD5" t="n">
-        <v>77</v>
+        <v>81.12</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DI5" t="n">
-        <v>27.57</v>
+        <v>29.75</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DK5" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.14</v>
+        <v>12.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>52.86</v>
+        <v>54.38</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.71</v>
+        <v>16.88</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.14</v>
+        <v>7.12</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.43</v>
+        <v>16</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="6">
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -8389,49 +8389,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>101.5</v>
+        <v>94</v>
       </c>
       <c r="I20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="K20" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M20" t="n">
-        <v>51.25</v>
+        <v>46.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.75</v>
+        <v>15.2</v>
       </c>
       <c r="R20" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8443,28 +8443,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>48.25</v>
+        <v>45.6</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.25</v>
+        <v>11.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8548,70 +8548,70 @@
         <v>2.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.619999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BP20" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BR20" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS20" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT20" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU20" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV20" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CC20" t="n">
         <v>3.56</v>
@@ -8620,49 +8620,49 @@
         <v>4.12</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.36</v>
+        <v>4.22</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="n">
@@ -8673,55 +8673,55 @@
         <v>1.88</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CZ20" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG20" t="n">
         <v>4.56</v>
       </c>
-      <c r="DA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="DE20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DG20" t="n">
-        <v>5</v>
-      </c>
       <c r="DH20" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DI20" t="n">
-        <v>37.75</v>
+        <v>36.44</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DK20" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DL20" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="DM20" t="n">
-        <v>9.880000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="DN20" t="n">
-        <v>6.88</v>
+        <v>7.44</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8733,28 +8733,28 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>47.5</v>
+        <v>46.11</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>12.12</v>
+        <v>11.78</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="DW20" t="n">
-        <v>16.5</v>
+        <v>15.67</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1835,124 +1835,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.25</v>
+        <v>86.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.75</v>
+        <v>15.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.5</v>
+        <v>55.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.75</v>
+        <v>11.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.25</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
         <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BP3" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
         <v>1.71</v>
@@ -1973,28 +1973,28 @@
         <v>1.8</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="CI3" t="n">
         <v>1.71</v>
@@ -2003,28 +2003,28 @@
         <v>2.04</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.64</v>
+        <v>3.77</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CS3" t="n">
         <v>2.08</v>
@@ -2045,85 +2045,85 @@
         <v>1.43</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.36</v>
+        <v>4.44</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DD3" t="n">
-        <v>88.62</v>
+        <v>90.56</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF3" t="n">
         <v>4</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>34.12</v>
+        <v>36.78</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="DL3" t="n">
-        <v>16.12</v>
+        <v>15.67</v>
       </c>
       <c r="DM3" t="n">
-        <v>12.25</v>
+        <v>11.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.25</v>
+        <v>7.11</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>56.5</v>
+        <v>57.78</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="DU3" t="n">
-        <v>8.75</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DV3" t="n">
-        <v>5.38</v>
+        <v>5</v>
       </c>
       <c r="DW3" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="4">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -2145,49 +2145,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>100.75</v>
+        <v>103</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>43.5</v>
+        <v>40.2</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.75</v>
+        <v>10.8</v>
       </c>
       <c r="R4" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2199,28 +2199,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.75</v>
+        <v>53.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.25</v>
+        <v>14.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.25</v>
+        <v>10.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>17</v>
+        <v>15.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2304,70 +2304,70 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.12</v>
+        <v>7.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="BQ4" t="n">
         <v>3</v>
       </c>
       <c r="BR4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="CC4" t="n">
         <v>2.66</v>
@@ -2376,49 +2376,49 @@
         <v>2.46</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CI4" t="n">
         <v>1.62</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="CR4" t="n">
         <v>1.67</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CT4" t="n">
         <v>1.82</v>
@@ -2427,61 +2427,61 @@
         <v>1.84</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW4" t="n">
         <v>1.88</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="CZ4" t="n">
-        <v>5.08</v>
+        <v>4.85</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DD4" t="n">
-        <v>93.62</v>
+        <v>95.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DI4" t="n">
-        <v>36.75</v>
+        <v>35.67</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="DM4" t="n">
-        <v>11.75</v>
+        <v>10.78</v>
       </c>
       <c r="DN4" t="n">
-        <v>6</v>
+        <v>6.22</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>52.62</v>
+        <v>52.78</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>11.12</v>
+        <v>12.11</v>
       </c>
       <c r="DU4" t="n">
-        <v>7.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="DW4" t="n">
-        <v>15.5</v>
+        <v>14.89</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2617,136 +2617,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BN5" t="n">
         <v>2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>55.25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY5" t="n">
         <v>1.39</v>
@@ -2755,43 +2755,43 @@
         <v>1.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CH5" t="n">
         <v>1.39</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN5" t="n">
         <v>1.7</v>
@@ -2806,10 +2806,10 @@
         <v>3.19</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
@@ -2829,79 +2829,79 @@
         <v>3.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DC5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DD5" t="n">
-        <v>81.12</v>
+        <v>83.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="DG5" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DI5" t="n">
-        <v>29.75</v>
+        <v>31.67</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="DL5" t="n">
-        <v>12.38</v>
+        <v>12.11</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.25</v>
+        <v>7.78</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>54.38</v>
+        <v>55.78</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.88</v>
+        <v>16.78</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DW5" t="n">
-        <v>16</v>
+        <v>16.56</v>
       </c>
       <c r="DX5" t="n">
         <v>1.78</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3395,115 +3395,115 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>87.25</v>
+        <v>84.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>3.5</v>
       </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="BH7" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL7" t="n">
         <v>1</v>
       </c>
-      <c r="AP7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>47</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BM7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3512,19 +3512,19 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BY7" t="n">
         <v>2.62</v>
@@ -3533,153 +3533,157 @@
         <v>2.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.22</v>
+        <v>3.47</v>
       </c>
       <c r="CC7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.01</v>
+        <v>6.27</v>
       </c>
       <c r="CE7" t="n">
         <v>1.32</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="CI7" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL7" t="n">
         <v>2.2</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CT7" t="n">
         <v>1.82</v>
       </c>
-      <c r="CU7" t="inlineStr"/>
+      <c r="CU7" t="n">
+        <v>1.92</v>
+      </c>
       <c r="CV7" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW7" t="inlineStr"/>
+      <c r="CW7" t="n">
+        <v>1.81</v>
+      </c>
       <c r="CX7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DD7" t="n">
-        <v>73.56</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="DH7" t="n">
         <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>28.89</v>
+        <v>27.4</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>11.22</v>
+        <v>11.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.220000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>44</v>
+        <v>45.1</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DT7" t="n">
-        <v>7.89</v>
+        <v>7.5</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="DW7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -4471,94 +4475,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>98.8</v>
+        <v>91.33</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>45.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.6</v>
+        <v>8.33</v>
       </c>
       <c r="R10" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.4</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4642,70 +4646,70 @@
         <v>3.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.89</v>
+        <v>7.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BZ10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CA10" t="n">
         <v>3.01</v>
       </c>
-      <c r="CA10" t="n">
-        <v>3.02</v>
-      </c>
       <c r="CB10" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CC10" t="n">
         <v>4.22</v>
@@ -4717,7 +4721,7 @@
         <v>1.56</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CG10" t="n">
         <v>2.3</v>
@@ -4729,34 +4733,34 @@
         <v>1.66</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="CM10" t="n">
         <v>1.9</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO10" t="n">
         <v>1.49</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CT10" t="n">
         <v>1.92</v>
@@ -4767,88 +4771,88 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY10" t="n">
         <v>2.62</v>
       </c>
       <c r="CZ10" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DD10" t="n">
-        <v>92.33</v>
+        <v>88.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DI10" t="n">
-        <v>41.78</v>
+        <v>40</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.89</v>
+        <v>6.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>53.78</v>
+        <v>51.6</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DT10" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="DU10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="DW10" t="n">
-        <v>17.67</v>
+        <v>17.4</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="DY10" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4858,13 +4862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4951,136 +4955,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>68.5</v>
+        <v>63.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.75</v>
+        <v>42.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BD11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BG11" t="n">
         <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.38</v>
+        <v>6.67</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
         <v>3.06</v>
@@ -5089,64 +5093,64 @@
         <v>3.4</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.43</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.92</v>
+        <v>7.3</v>
       </c>
       <c r="CD11" t="n">
-        <v>8.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CS11" t="n">
         <v>2.25</v>
       </c>
       <c r="CT11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CU11" t="n">
         <v>1.93</v>
@@ -5158,88 +5162,88 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DG11" t="n">
         <v>1.44</v>
       </c>
-      <c r="CY11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>64</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>14.62</v>
+        <v>13.67</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.38</v>
+        <v>10.56</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="DN11" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>43.12</v>
+        <v>43.44</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT11" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DU11" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="DW11" t="n">
-        <v>12.25</v>
+        <v>12.44</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="12">
@@ -6031,13 +6035,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6124,49 +6128,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>18.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.75</v>
+        <v>15.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6178,58 +6182,58 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>38</v>
+        <v>40.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="BF14" t="n">
         <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BH14" t="n">
         <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="BQ14" t="n">
         <v>4</v>
@@ -6238,22 +6242,22 @@
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
         <v>2.83</v>
@@ -6262,76 +6266,76 @@
         <v>3.06</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.88</v>
+        <v>5.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.48</v>
+        <v>6.04</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CO14" t="n">
         <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CT14" t="n">
         <v>1.84</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="CV14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CW14" t="n">
         <v>1.88</v>
       </c>
-      <c r="CW14" t="n">
-        <v>1.79</v>
-      </c>
       <c r="CX14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CY14" t="n">
         <v>2.32</v>
@@ -6343,43 +6347,43 @@
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DC14" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="DD14" t="n">
-        <v>67.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DI14" t="n">
-        <v>18.67</v>
+        <v>20</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DL14" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="DM14" t="n">
-        <v>11.33</v>
+        <v>12.3</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.89</v>
+        <v>5.3</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
@@ -6391,28 +6395,28 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>45.33</v>
+        <v>45.9</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT14" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="DU14" t="n">
-        <v>5.44</v>
+        <v>6</v>
       </c>
       <c r="DV14" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DW14" t="n">
-        <v>10.78</v>
+        <v>11.4</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15">
@@ -6422,94 +6426,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>112.25</v>
+        <v>101.2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>8.75</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>48.25</v>
+        <v>43.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>12.75</v>
+        <v>12.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="R15" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>61.5</v>
+        <v>55.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.25</v>
+        <v>16.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.5</v>
+        <v>11.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.75</v>
+        <v>15.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6593,37 +6597,37 @@
         <v>2.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.67</v>
+        <v>9.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
         <v>1</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6632,31 +6636,31 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CC15" t="n">
         <v>3</v>
@@ -6668,7 +6672,7 @@
         <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG15" t="n">
         <v>2.64</v>
@@ -6677,16 +6681,16 @@
         <v>1.34</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CM15" t="n">
         <v>2.15</v>
@@ -6695,19 +6699,19 @@
         <v>1.7</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CT15" t="n">
         <v>1.75</v>
@@ -6722,88 +6726,88 @@
         <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DB15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DD15" t="n">
-        <v>102.33</v>
+        <v>97.8</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DG15" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DI15" t="n">
-        <v>36.67</v>
+        <v>35.6</v>
       </c>
       <c r="DJ15" t="n">
         <v>1</v>
       </c>
       <c r="DK15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="DM15" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>56</v>
+        <v>53.7</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>15.22</v>
+        <v>14.1</v>
       </c>
       <c r="DU15" t="n">
-        <v>9.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.44</v>
+        <v>5.1</v>
       </c>
       <c r="DW15" t="n">
-        <v>14.11</v>
+        <v>13.5</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="DY15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -7204,88 +7208,88 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>87.8</v>
+        <v>84.17</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>25.8</v>
+        <v>26.67</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="P17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51</v>
+        <v>50.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.4</v>
+        <v>6.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.6</v>
+        <v>20.33</v>
       </c>
       <c r="AD17" t="n">
         <v>1.05</v>
@@ -7375,49 +7379,49 @@
         <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU17" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7426,13 +7430,13 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="CA17" t="n">
         <v>3.09</v>
@@ -7450,142 +7454,142 @@
         <v>1.49</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CG17" t="n">
         <v>2.45</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP17" t="n">
         <v>2.4</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CX17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DB17" t="n">
         <v>1.5</v>
       </c>
-      <c r="CY17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>1.56</v>
-      </c>
       <c r="DC17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DD17" t="n">
-        <v>82.33</v>
+        <v>80.7</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="DG17" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="DH17" t="n">
         <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>21.89</v>
+        <v>22.8</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DL17" t="n">
-        <v>8.44</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DM17" t="n">
-        <v>7.78</v>
+        <v>8.5</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>48.78</v>
+        <v>48.8</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DT17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DU17" t="n">
-        <v>5.78</v>
+        <v>6.1</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="DW17" t="n">
-        <v>16.89</v>
+        <v>17.6</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -7595,94 +7599,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="H18" t="n">
-        <v>79.8</v>
+        <v>80.67</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>6.17</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>26.8</v>
+        <v>24</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.2</v>
+        <v>6.67</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.2</v>
+        <v>16.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.199999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.6</v>
+        <v>19.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7766,70 +7770,70 @@
         <v>3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.44</v>
+        <v>9.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BR18" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS18" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="CC18" t="n">
         <v>2.92</v>
@@ -7838,16 +7842,16 @@
         <v>3.27</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CI18" t="n">
         <v>1.74</v>
@@ -7856,25 +7860,25 @@
         <v>2.04</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="CR18" t="n">
         <v>1.76</v>
@@ -7886,7 +7890,7 @@
         <v>1.85</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CV18" t="n">
         <v>1.87</v>
@@ -7895,88 +7899,88 @@
         <v>1.82</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.28</v>
+        <v>4.07</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="DD18" t="n">
-        <v>76.11</v>
+        <v>77</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DI18" t="n">
-        <v>27.33</v>
+        <v>25.6</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>8.220000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="DN18" t="n">
-        <v>7.44</v>
+        <v>6.8</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>46.67</v>
+        <v>46.5</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>13.89</v>
+        <v>14.6</v>
       </c>
       <c r="DU18" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="DV18" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="DW18" t="n">
-        <v>17.56</v>
+        <v>18.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2524,94 +2524,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>28</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.25</v>
+        <v>17.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2695,70 +2695,70 @@
         <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="CC5" t="n">
         <v>1.89</v>
@@ -2770,138 +2770,138 @@
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CH5" t="n">
         <v>1.39</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="DD5" t="n">
-        <v>83.78</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="DI5" t="n">
-        <v>31.67</v>
+        <v>31.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DL5" t="n">
-        <v>12.11</v>
+        <v>11.7</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="DN5" t="n">
-        <v>7.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>55.78</v>
+        <v>55.8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.78</v>
+        <v>16.1</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DV5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.56</v>
+        <v>16.3</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4568,136 +4568,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.25</v>
+        <v>86.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.5</v>
+        <v>29.6</v>
       </c>
       <c r="AO10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP10" t="n">
         <v>2</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>9.75</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>13.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>53.5</v>
+        <v>51.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.75</v>
+        <v>13.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.8</v>
+        <v>7.91</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="BR10" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
         <v>2.87</v>
@@ -4706,61 +4706,61 @@
         <v>2.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.36</v>
+        <v>4.51</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="CT10" t="n">
         <v>1.92</v>
@@ -4771,88 +4771,88 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="CZ10" t="n">
-        <v>5.11</v>
+        <v>4.96</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="DD10" t="n">
-        <v>88.5</v>
+        <v>89.27</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DI10" t="n">
-        <v>40</v>
+        <v>38.37</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.5</v>
+        <v>8.91</v>
       </c>
       <c r="DM10" t="n">
-        <v>11.4</v>
+        <v>10.73</v>
       </c>
       <c r="DN10" t="n">
-        <v>6.6</v>
+        <v>5.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>51.6</v>
+        <v>50.91</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="DT10" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="DU10" t="n">
-        <v>8.1</v>
+        <v>8.82</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="DW10" t="n">
-        <v>17.4</v>
+        <v>16.46</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="11">
@@ -7208,13 +7208,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7301,127 +7301,127 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>75.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>25.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
         <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.25</v>
+        <v>10.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.88</v>
+        <v>1.04</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP17" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU17" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY17" t="n">
         <v>2.32</v>
@@ -7439,61 +7439,61 @@
         <v>2.4</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.64</v>
+        <v>6.46</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CK17" t="n">
         <v>1.66</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CM17" t="n">
         <v>2.08</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="CR17" t="n">
         <v>1.7</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
@@ -7508,88 +7508,88 @@
         <v>1.86</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="DD17" t="n">
-        <v>80.7</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DI17" t="n">
-        <v>22.8</v>
+        <v>26.18</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="DL17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.6</v>
+        <v>5.73</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>48.8</v>
+        <v>48.37</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DT17" t="n">
-        <v>9.300000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="DU17" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DW17" t="n">
-        <v>17.6</v>
+        <v>17.54</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="18">
@@ -7990,94 +7990,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>96.2</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>48.2</v>
+        <v>45</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>10.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.8</v>
+        <v>58.33</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>11.2</v>
+        <v>10.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.4</v>
+        <v>7.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AF19" t="n">
         <v>0.2</v>
@@ -8161,37 +8161,37 @@
         <v>3.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.7</v>
+        <v>10.55</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8200,31 +8200,31 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU19" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BX19" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CC19" t="n">
         <v>3.28</v>
@@ -8233,49 +8233,49 @@
         <v>3.67</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI19" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CM19" t="n">
         <v>2.17</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CS19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
@@ -8293,85 +8293,85 @@
         <v>1.37</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ19" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="DD19" t="n">
-        <v>87.8</v>
+        <v>89</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="DG19" t="n">
-        <v>6.3</v>
+        <v>5.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DI19" t="n">
-        <v>41.9</v>
+        <v>40.73</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DK19" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DL19" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="DM19" t="n">
-        <v>9.5</v>
+        <v>8.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>5.9</v>
+        <v>5.27</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>51.9</v>
+        <v>52.27</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>14.3</v>
+        <v>14.09</v>
       </c>
       <c r="DU19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="DV19" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="DW19" t="n">
-        <v>12.2</v>
+        <v>11.45</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1444,136 +1444,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>68.8</v>
+        <v>69.17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.6</v>
+        <v>22.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG2" t="n">
         <v>2.4</v>
       </c>
-      <c r="AU2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BH2" t="n">
-        <v>8.220000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>2.08</v>
@@ -1582,28 +1582,28 @@
         <v>2.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.76</v>
+        <v>5.84</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI2" t="n">
         <v>1.64</v>
@@ -1615,28 +1615,28 @@
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN2" t="n">
         <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CT2" t="n">
         <v>1.82</v>
@@ -1654,10 +1654,10 @@
         <v>1.44</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
@@ -1666,40 +1666,40 @@
         <v>2</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>80.89</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="DI2" t="n">
-        <v>33.67</v>
+        <v>32.9</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>11.11</v>
+        <v>10.6</v>
       </c>
       <c r="DM2" t="n">
-        <v>12.44</v>
+        <v>11.9</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>47.67</v>
+        <v>47.4</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>11.89</v>
+        <v>11.4</v>
       </c>
       <c r="DU2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="DV2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DW2" t="n">
-        <v>17.56</v>
+        <v>18.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -1754,82 +1754,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
         <v>96</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>43.25</v>
+        <v>44.6</v>
       </c>
       <c r="N3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.75</v>
-      </c>
       <c r="P3" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="R3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60.5</v>
+        <v>59.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.25</v>
+        <v>11.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.75</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1913,46 +1913,46 @@
         <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,19 +1964,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC3" t="n">
         <v>3.13</v>
@@ -1985,145 +1985,145 @@
         <v>3.46</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="CR3" t="n">
         <v>1.76</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CU3" t="n">
         <v>1.95</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CY3" t="n">
         <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>90.56</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DI3" t="n">
-        <v>36.78</v>
+        <v>38.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DL3" t="n">
-        <v>15.67</v>
+        <v>15.6</v>
       </c>
       <c r="DM3" t="n">
-        <v>11.89</v>
+        <v>12.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>57.78</v>
+        <v>57.5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.11</v>
+        <v>14.3</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DV3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="DW3" t="n">
-        <v>14.78</v>
+        <v>15</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2226,136 +2226,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="BL4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BQ4" t="n">
         <v>3</v>
       </c>
       <c r="BR4" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
         <v>1.79</v>
@@ -2364,25 +2364,25 @@
         <v>1.81</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
@@ -2391,37 +2391,37 @@
         <v>1.62</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="CM4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CQ4" t="n">
         <v>4.67</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CU4" t="n">
         <v>1.84</v>
@@ -2436,52 +2436,52 @@
         <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DD4" t="n">
-        <v>95.67</v>
+        <v>97.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DI4" t="n">
-        <v>35.67</v>
+        <v>35.3</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DL4" t="n">
-        <v>12.67</v>
+        <v>11.8</v>
       </c>
       <c r="DM4" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.22</v>
+        <v>6.6</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>52.78</v>
+        <v>52.4</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.11</v>
+        <v>12.4</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DV4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="DW4" t="n">
-        <v>14.89</v>
+        <v>15.9</v>
       </c>
       <c r="DX4" t="n">
         <v>1.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -2911,61 +2911,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="n">
-        <v>96.75</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>16.75</v>
+        <v>14.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -2977,28 +2977,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.75</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3082,70 +3082,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.56</v>
+        <v>7.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC6" t="n">
         <v>8.35</v>
@@ -3160,43 +3160,43 @@
         <v>3.19</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH6" t="n">
         <v>1.29</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CK6" t="n">
         <v>1.71</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN6" t="n">
         <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="CR6" t="n">
         <v>1.57</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CT6" t="n">
         <v>1.83</v>
@@ -3220,46 +3220,46 @@
         <v>4.74</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DD6" t="n">
-        <v>76.22</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DI6" t="n">
-        <v>18.44</v>
+        <v>17.7</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="DL6" t="n">
-        <v>13.33</v>
+        <v>12.6</v>
       </c>
       <c r="DM6" t="n">
-        <v>12.67</v>
+        <v>11.9</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
@@ -3271,28 +3271,28 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>9.56</v>
+        <v>9.5</v>
       </c>
       <c r="DU6" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="DV6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DW6" t="n">
-        <v>10.89</v>
+        <v>10.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -3314,82 +3314,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>62.6</v>
+        <v>63.83</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>23.4</v>
+        <v>25.17</v>
       </c>
       <c r="N7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.6</v>
-      </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>9.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.6</v>
+        <v>13.17</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>41.6</v>
+        <v>45.67</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
         <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3473,37 +3473,37 @@
         <v>2.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3512,31 +3512,31 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CC7" t="n">
         <v>4.5</v>
@@ -3545,22 +3545,22 @@
         <v>6.27</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF7" t="n">
         <v>2.86</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
         <v>1.61</v>
@@ -3569,25 +3569,25 @@
         <v>2.2</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CO7" t="n">
         <v>1.41</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CT7" t="n">
         <v>1.82</v>
@@ -3608,82 +3608,82 @@
         <v>2.26</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="DD7" t="n">
-        <v>73.40000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DI7" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="DL7" t="n">
-        <v>11.5</v>
+        <v>10.82</v>
       </c>
       <c r="DM7" t="n">
-        <v>10.2</v>
+        <v>10.73</v>
       </c>
       <c r="DN7" t="n">
-        <v>10.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>45.1</v>
+        <v>47</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="DT7" t="n">
-        <v>7.5</v>
+        <v>7.73</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="DW7" t="n">
-        <v>13.5</v>
+        <v>13.64</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="8">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3783,52 +3783,52 @@
         <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG8" t="n">
         <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.8</v>
+        <v>12.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>8.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3840,82 +3840,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.8</v>
+        <v>45.67</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>11.6</v>
+        <v>12.67</v>
       </c>
       <c r="BE8" t="n">
         <v>1.07</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.89</v>
+        <v>10.5</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
         <v>2</v>
@@ -3924,70 +3924,70 @@
         <v>2.06</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.73</v>
+        <v>3.86</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
         <v>3.17</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK8" t="n">
         <v>1.73</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO8" t="n">
         <v>1.42</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.31</v>
+        <v>4.39</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CS8" t="n">
         <v>2.08</v>
       </c>
       <c r="CT8" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CU8" t="n">
         <v>1.8</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW8" t="n">
         <v>1.92</v>
@@ -3999,82 +3999,82 @@
         <v>2.37</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DD8" t="n">
-        <v>90.78</v>
+        <v>88.3</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DI8" t="n">
-        <v>32.44</v>
+        <v>32.4</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>10.78</v>
+        <v>11.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>7.89</v>
+        <v>8.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>52.89</v>
+        <v>52.1</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DT8" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="DW8" t="n">
-        <v>14.44</v>
+        <v>14.8</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DY8" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4177,49 +4177,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>88.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>31</v>
+        <v>28.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.75</v>
+        <v>13.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4231,82 +4231,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.25</v>
+        <v>7.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY9" t="n">
         <v>2.25</v>
@@ -4315,157 +4315,157 @@
         <v>2.27</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="CE9" t="n">
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH9" t="n">
         <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO9" t="n">
         <v>1.41</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CV9" t="n">
         <v>1.84</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="DD9" t="n">
-        <v>95.3</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DI9" t="n">
-        <v>29.6</v>
+        <v>28.64</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DK9" t="n">
         <v>2</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.3</v>
+        <v>13.55</v>
       </c>
       <c r="DM9" t="n">
-        <v>10.7</v>
+        <v>10.09</v>
       </c>
       <c r="DN9" t="n">
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>53.2</v>
+        <v>51.46</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.7</v>
+        <v>12.37</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="DW9" t="n">
-        <v>16.9</v>
+        <v>16.73</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="10">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -4877,46 +4877,46 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>59.5</v>
+        <v>65.2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>15.75</v>
+        <v>19.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="P11" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="R11" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -4928,28 +4928,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44.5</v>
+        <v>46.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5033,70 +5033,70 @@
         <v>2.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1</v>
       </c>
-      <c r="BM11" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BP11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CC11" t="n">
         <v>7.3</v>
@@ -5111,7 +5111,7 @@
         <v>3.11</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH11" t="n">
         <v>1.31</v>
@@ -5120,19 +5120,19 @@
         <v>1.67</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CK11" t="n">
         <v>1.69</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
@@ -5141,22 +5141,22 @@
         <v>2.2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CT11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CU11" t="n">
         <v>1.93</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW11" t="n">
         <v>1.8</v>
@@ -5165,85 +5165,85 @@
         <v>1.43</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DD11" t="n">
-        <v>61.67</v>
+        <v>64.3</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>13.67</v>
+        <v>15.8</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.56</v>
+        <v>10.6</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.22</v>
+        <v>7.7</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>43.44</v>
+        <v>44.7</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="DU11" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="DW11" t="n">
-        <v>12.44</v>
+        <v>13.5</v>
       </c>
       <c r="DX11" t="n">
         <v>0.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
@@ -5346,43 +5346,43 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>88.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.6</v>
+        <v>33.83</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.6</v>
+        <v>12.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -5391,91 +5391,91 @@
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>53</v>
+        <v>51.67</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>17</v>
+        <v>16.83</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY12" t="n">
         <v>1.94</v>
@@ -5484,16 +5484,16 @@
         <v>2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.27</v>
+        <v>5.18</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
@@ -5502,43 +5502,43 @@
         <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.95</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CO12" t="n">
         <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CT12" t="n">
         <v>1.8</v>
@@ -5553,88 +5553,88 @@
         <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="DD12" t="n">
-        <v>104.2</v>
+        <v>102.18</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>34.4</v>
+        <v>33.54</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.7</v>
+        <v>11.91</v>
       </c>
       <c r="DN12" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>56.1</v>
+        <v>55.09</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="DU12" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="DW12" t="n">
-        <v>17.3</v>
+        <v>17.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13">
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5737,127 +5737,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>72</v>
+        <v>79.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>22.8</v>
+        <v>21.67</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.4</v>
+        <v>10.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>4.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.4</v>
+        <v>47.83</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.44</v>
+        <v>9.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU13" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY13" t="n">
         <v>1.75</v>
@@ -5875,25 +5875,25 @@
         <v>1.98</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
@@ -5905,10 +5905,10 @@
         <v>1.99</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
@@ -5920,16 +5920,16 @@
         <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CS13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CT13" t="n">
         <v>1.81</v>
@@ -5944,88 +5944,88 @@
         <v>1.76</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CZ13" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="DD13" t="n">
-        <v>88.67</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DF13" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="DG13" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="DI13" t="n">
-        <v>33.11</v>
+        <v>31.4</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>10.22</v>
+        <v>9.6</v>
       </c>
       <c r="DM13" t="n">
-        <v>10.44</v>
+        <v>9.9</v>
       </c>
       <c r="DN13" t="n">
-        <v>4.22</v>
+        <v>3.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>52.67</v>
+        <v>54.4</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>15.56</v>
+        <v>14.9</v>
       </c>
       <c r="DU13" t="n">
-        <v>10.44</v>
+        <v>9.9</v>
       </c>
       <c r="DV13" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="DW13" t="n">
-        <v>15.22</v>
+        <v>14.6</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
@@ -6047,49 +6047,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H14" t="n">
+        <v>72.17</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>11.4</v>
+        <v>10.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6101,28 +6101,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.2</v>
+        <v>47.67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6206,70 +6206,70 @@
         <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="CA14" t="n">
         <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC14" t="n">
         <v>5.46</v>
@@ -6281,7 +6281,7 @@
         <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG14" t="n">
         <v>2.51</v>
@@ -6290,16 +6290,16 @@
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CM14" t="n">
         <v>2</v>
@@ -6308,19 +6308,19 @@
         <v>1.6</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CT14" t="n">
         <v>1.84</v>
@@ -6335,55 +6335,55 @@
         <v>1.88</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>68.40000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="DI14" t="n">
-        <v>20</v>
+        <v>18.55</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DK14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DL14" t="n">
-        <v>11</v>
+        <v>10.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>12.3</v>
+        <v>11.55</v>
       </c>
       <c r="DN14" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
@@ -6395,28 +6395,28 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>45.9</v>
+        <v>44.46</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT14" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="DU14" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="DV14" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DW14" t="n">
-        <v>11.4</v>
+        <v>10.45</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="15">
@@ -6426,25 +6426,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="H15" t="n">
-        <v>101.2</v>
+        <v>95.83</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -6453,67 +6453,67 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>7.17</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>43.8</v>
+        <v>41.67</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>12.6</v>
+        <v>12.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="R15" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.8</v>
+        <v>55.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.2</v>
+        <v>10.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.8</v>
+        <v>17.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AF15" t="n">
         <v>0.2</v>
@@ -6600,34 +6600,34 @@
         <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="BI15" t="n">
         <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BK15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6636,28 +6636,28 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="CB15" t="n">
         <v>3.63</v>
@@ -6672,10 +6672,10 @@
         <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH15" t="n">
         <v>1.34</v>
@@ -6690,7 +6690,7 @@
         <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM15" t="n">
         <v>2.15</v>
@@ -6702,10 +6702,10 @@
         <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CR15" t="n">
         <v>1.85</v>
@@ -6732,82 +6732,82 @@
         <v>2.09</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="DD15" t="n">
-        <v>97.8</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DG15" t="n">
         <v>5</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>35.6</v>
+        <v>35.18</v>
       </c>
       <c r="DJ15" t="n">
         <v>1</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.3</v>
+        <v>10.63</v>
       </c>
       <c r="DM15" t="n">
-        <v>8.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DN15" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>53.7</v>
+        <v>53.82</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>14.1</v>
+        <v>13.91</v>
       </c>
       <c r="DU15" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.1</v>
+        <v>5.27</v>
       </c>
       <c r="DW15" t="n">
-        <v>13.5</v>
+        <v>14.46</v>
       </c>
       <c r="DX15" t="n">
         <v>1.51</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="16">
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -6829,49 +6829,49 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>22.6</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>6.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -6883,28 +6883,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.75</v>
+        <v>52.4</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.25</v>
+        <v>12.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.75</v>
+        <v>13.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0.33</v>
@@ -6988,58 +6988,58 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BH16" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BR16" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV16" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BY16" t="n">
         <v>2.72</v>
@@ -7048,10 +7048,10 @@
         <v>2.6</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CC16" t="n">
         <v>4.7</v>
@@ -7060,49 +7060,49 @@
         <v>4.46</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="CI16" t="n">
         <v>1.65</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP16" t="n">
         <v>2.4</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CR16" t="n">
         <v>1.74</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CT16" t="n">
         <v>1.9</v>
@@ -7111,7 +7111,7 @@
         <v>1.88</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
@@ -7123,49 +7123,49 @@
         <v>2.5</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="DD16" t="n">
-        <v>86.2</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DI16" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DL16" t="n">
-        <v>13.3</v>
+        <v>12.91</v>
       </c>
       <c r="DM16" t="n">
-        <v>9.6</v>
+        <v>9.09</v>
       </c>
       <c r="DN16" t="n">
-        <v>5.7</v>
+        <v>6.73</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
@@ -7177,28 +7177,28 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>45.2</v>
+        <v>45.73</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>11.8</v>
+        <v>11.37</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.3</v>
+        <v>7.18</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="DW16" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="DY16" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="17">
@@ -7599,13 +7599,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>0.33</v>
@@ -7692,136 +7692,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>71.5</v>
+        <v>72.2</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>24.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.25</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>40.5</v>
+        <v>41.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.25</v>
+        <v>14.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.25</v>
+        <v>13.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.1</v>
+        <v>9.27</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="BR18" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY18" t="n">
         <v>1.79</v>
@@ -7830,28 +7830,28 @@
         <v>1.65</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI18" t="n">
         <v>1.74</v>
@@ -7860,31 +7860,31 @@
         <v>2.04</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
         <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CT18" t="n">
         <v>1.85</v>
@@ -7899,88 +7899,88 @@
         <v>1.82</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="DD18" t="n">
-        <v>77</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DI18" t="n">
-        <v>25.6</v>
+        <v>24.27</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="DM18" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="DN18" t="n">
-        <v>6.8</v>
+        <v>6.09</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>46.5</v>
+        <v>46.55</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DT18" t="n">
-        <v>14.6</v>
+        <v>15.46</v>
       </c>
       <c r="DU18" t="n">
-        <v>10</v>
+        <v>10.54</v>
       </c>
       <c r="DV18" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="DW18" t="n">
-        <v>18.1</v>
+        <v>16.73</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="19">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8474,49 +8474,49 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>73.5</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>24.25</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8528,82 +8528,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>46.75</v>
+        <v>46.2</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS20" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BT20" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU20" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV20" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
         <v>1.55</v>
@@ -8612,31 +8612,31 @@
         <v>2.71</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.03</v>
@@ -8645,34 +8645,38 @@
         <v>1.65</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CS20" t="n">
         <v>2.02</v>
       </c>
-      <c r="CT20" t="inlineStr"/>
+      <c r="CT20" t="n">
+        <v>1.76</v>
+      </c>
       <c r="CU20" t="n">
         <v>1.85</v>
       </c>
-      <c r="CV20" t="inlineStr"/>
+      <c r="CV20" t="n">
+        <v>1.95</v>
+      </c>
       <c r="CW20" t="n">
         <v>1.88</v>
       </c>
@@ -8680,52 +8684,52 @@
         <v>1.43</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ20" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DD20" t="n">
-        <v>84.89</v>
+        <v>86</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DI20" t="n">
-        <v>36.44</v>
+        <v>37.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DK20" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DL20" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="DM20" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="DN20" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8737,28 +8741,28 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>46.11</v>
+        <v>45.9</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="DW20" t="n">
-        <v>15.67</v>
+        <v>16.6</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -8768,61 +8772,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>87.75</v>
+        <v>90.2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>33.5</v>
+        <v>34.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>14.25</v>
+        <v>12.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="R21" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -8834,28 +8838,28 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -8939,49 +8943,49 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>7.89</v>
+        <v>8.1</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT21" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU21" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8990,19 +8994,19 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>2.03</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>2.15</v>
-      </c>
       <c r="CA21" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CC21" t="n">
         <v>2.71</v>
@@ -9011,49 +9015,49 @@
         <v>2.94</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CI21" t="n">
         <v>1.56</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CT21" t="n">
         <v>1.83</v>
@@ -9068,55 +9072,55 @@
         <v>1.83</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CY21" t="n">
         <v>2.29</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="DD21" t="n">
-        <v>95.11</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DK21" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DL21" t="n">
-        <v>12.11</v>
+        <v>11.6</v>
       </c>
       <c r="DM21" t="n">
-        <v>8.109999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="DN21" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9128,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>48.11</v>
+        <v>48.8</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT21" t="n">
-        <v>14.33</v>
+        <v>13.8</v>
       </c>
       <c r="DU21" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="DV21" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.56</v>
+        <v>15.8</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0.4</v>
@@ -2617,136 +2617,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3</v>
       </c>
-      <c r="AL5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU5" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV5" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY5" t="n">
         <v>1.36</v>
@@ -2755,25 +2755,25 @@
         <v>1.4</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="CE5" t="n">
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CH5" t="n">
         <v>1.39</v>
@@ -2788,28 +2788,28 @@
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM5" t="n">
         <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
@@ -2820,88 +2820,88 @@
         <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DD5" t="n">
-        <v>83.09999999999999</v>
+        <v>81.55</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DI5" t="n">
-        <v>31.1</v>
+        <v>30.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.7</v>
+        <v>11.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.7</v>
+        <v>11.09</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>55.8</v>
+        <v>55.36</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.1</v>
+        <v>15.36</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.6</v>
+        <v>6.09</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.3</v>
+        <v>15.82</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="6">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3395,115 +3395,115 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>84.2</v>
+        <v>85.17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.4</v>
+        <v>33</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.8</v>
+        <v>9.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>48.6</v>
+        <v>48.17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>8.17</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.8</v>
+        <v>17.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3512,19 +3512,19 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY7" t="n">
         <v>2.77</v>
@@ -3533,157 +3533,157 @@
         <v>2.98</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB7" t="n">
         <v>3.43</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.27</v>
+        <v>6.05</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.67</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CT7" t="n">
         <v>1.82</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CV7" t="n">
         <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="DD7" t="n">
-        <v>73.09</v>
+        <v>74.5</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>28</v>
+        <v>29.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="DL7" t="n">
-        <v>10.82</v>
+        <v>10.92</v>
       </c>
       <c r="DM7" t="n">
-        <v>10.73</v>
+        <v>11.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DT7" t="n">
-        <v>7.73</v>
+        <v>8.08</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.36</v>
+        <v>4.66</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="DW7" t="n">
-        <v>13.64</v>
+        <v>14.42</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="8">
@@ -5400,16 +5400,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.67</v>
+        <v>51.83</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.67</v>
+        <v>11.83</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.67</v>
+        <v>8.83</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
@@ -5418,7 +5418,7 @@
         <v>16.83</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF12" t="n">
         <v>2.17</v>
@@ -5613,16 +5613,16 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>55.09</v>
+        <v>55.18</v>
       </c>
       <c r="DS12" t="n">
         <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>13</v>
+        <v>13.09</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.82</v>
+        <v>8.91</v>
       </c>
       <c r="DV12" t="n">
         <v>4.18</v>
@@ -5631,7 +5631,7 @@
         <v>17.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DY12" t="n">
         <v>2.37</v>
@@ -6468,7 +6468,7 @@
         <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
         <v>9.83</v>
@@ -6492,16 +6492,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.67</v>
+        <v>55.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.5</v>
+        <v>15.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.17</v>
+        <v>10.5</v>
       </c>
       <c r="AB15" t="n">
         <v>5.33</v>
@@ -6510,7 +6510,7 @@
         <v>17.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
         <v>2.67</v>
@@ -6768,7 +6768,7 @@
         <v>1.55</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.63</v>
+        <v>10.73</v>
       </c>
       <c r="DM15" t="n">
         <v>8.449999999999999</v>
@@ -6786,16 +6786,16 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>53.82</v>
+        <v>53.73</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>13.91</v>
+        <v>14.09</v>
       </c>
       <c r="DU15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="DV15" t="n">
         <v>5.27</v>
@@ -6804,7 +6804,7 @@
         <v>14.46</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DY15" t="n">
         <v>2.73</v>
@@ -7208,94 +7208,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="H17" t="n">
-        <v>84.17</v>
+        <v>84.14</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="M17" t="n">
-        <v>26.67</v>
+        <v>27.57</v>
       </c>
       <c r="N17" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="P17" t="n">
-        <v>10.17</v>
+        <v>11.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.67</v>
+        <v>51.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>10.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.83</v>
+        <v>7.29</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.33</v>
+        <v>19.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7379,49 +7379,49 @@
         <v>2.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU17" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7430,13 +7430,13 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>2.32</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>2.4</v>
       </c>
       <c r="CA17" t="n">
         <v>3.28</v>
@@ -7451,145 +7451,145 @@
         <v>6.46</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CL17" t="n">
         <v>2.17</v>
       </c>
-      <c r="CK17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>2.19</v>
-      </c>
       <c r="CM17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CV17" t="n">
         <v>1.91</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="DD17" t="n">
-        <v>81.18000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="DI17" t="n">
-        <v>26.18</v>
+        <v>26.75</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="DL17" t="n">
-        <v>9.73</v>
+        <v>10.33</v>
       </c>
       <c r="DM17" t="n">
-        <v>8.460000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.73</v>
+        <v>5.66</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>48.37</v>
+        <v>48.83</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT17" t="n">
-        <v>10.09</v>
+        <v>10.42</v>
       </c>
       <c r="DU17" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DW17" t="n">
-        <v>17.54</v>
+        <v>17.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="18">
@@ -7599,94 +7599,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F18" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="G18" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="H18" t="n">
-        <v>80.67</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J18" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="K18" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.67</v>
       </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE18" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7770,70 +7770,70 @@
         <v>3.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BR18" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC18" t="n">
         <v>2.67</v>
@@ -7848,22 +7848,22 @@
         <v>3.03</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI18" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK18" t="n">
         <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM18" t="n">
         <v>2.1</v>
@@ -7875,16 +7875,16 @@
         <v>1.38</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ18" t="n">
         <v>3.98</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CT18" t="n">
         <v>1.85</v>
@@ -7902,85 +7902,85 @@
         <v>1.4</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="DD18" t="n">
-        <v>76.81999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="DG18" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DI18" t="n">
-        <v>24.27</v>
+        <v>26</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DL18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="DN18" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>46.55</v>
+        <v>46.75</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>15.46</v>
+        <v>15.83</v>
       </c>
       <c r="DU18" t="n">
-        <v>10.54</v>
+        <v>10.75</v>
       </c>
       <c r="DV18" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="DW18" t="n">
-        <v>16.73</v>
+        <v>16.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,61 +1351,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>48.75</v>
+        <v>43.4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>12.5</v>
+        <v>13.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.25</v>
+        <v>13.8</v>
       </c>
       <c r="R2" t="n">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.75</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.75</v>
+        <v>8.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.75</v>
+        <v>19.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1522,70 +1522,70 @@
         <v>2.17</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC2" t="n">
         <v>5.84</v>
@@ -1594,58 +1594,58 @@
         <v>6.9</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CG2" t="n">
         <v>2.52</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI2" t="n">
         <v>1.64</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CO2" t="n">
         <v>1.41</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="CR2" t="n">
         <v>1.66</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CU2" t="n">
         <v>1.9</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CW2" t="n">
         <v>1.82</v>
@@ -1654,52 +1654,52 @@
         <v>1.44</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DB2" t="n">
         <v>2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DD2" t="n">
-        <v>79.90000000000001</v>
+        <v>77.91</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
         <v>3</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DI2" t="n">
-        <v>32.9</v>
+        <v>31.91</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DL2" t="n">
-        <v>10.6</v>
+        <v>11.18</v>
       </c>
       <c r="DM2" t="n">
-        <v>11.9</v>
+        <v>11.55</v>
       </c>
       <c r="DN2" t="n">
-        <v>6.9</v>
+        <v>7.27</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>47.4</v>
+        <v>46.36</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT2" t="n">
-        <v>11.4</v>
+        <v>11.09</v>
       </c>
       <c r="DU2" t="n">
-        <v>8.6</v>
+        <v>8.18</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="DW2" t="n">
-        <v>18.3</v>
+        <v>18.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="3">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -2145,49 +2145,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
-        <v>103</v>
+        <v>105.67</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>40.2</v>
+        <v>44.17</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>14.6</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="R4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2199,28 +2199,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>53.8</v>
+        <v>55.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.6</v>
+        <v>14.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.4</v>
+        <v>10.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.6</v>
+        <v>16.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2307,67 +2307,67 @@
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.4</v>
+        <v>7.82</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="BR4" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BS4" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="CA4" t="n">
         <v>3.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CC4" t="n">
         <v>2.65</v>
@@ -2376,49 +2376,49 @@
         <v>2.6</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN4" t="n">
         <v>1.61</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CT4" t="n">
         <v>1.83</v>
@@ -2433,55 +2433,55 @@
         <v>1.88</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>97.7</v>
+        <v>99.64</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.3</v>
+        <v>4.73</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="DI4" t="n">
-        <v>35.3</v>
+        <v>37.91</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="DL4" t="n">
-        <v>11.8</v>
+        <v>11.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>52.4</v>
+        <v>53.36</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.4</v>
+        <v>12.37</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="DW4" t="n">
-        <v>15.9</v>
+        <v>16.54</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="5">
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0.4</v>
@@ -3004,49 +3004,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>59.8</v>
+        <v>61.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.4</v>
+        <v>14.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3058,82 +3058,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37.8</v>
+        <v>36.83</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>11.8</v>
+        <v>12.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BF6" t="n">
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.9</v>
+        <v>7.73</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BJ6" t="n">
         <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY6" t="n">
         <v>3.44</v>
@@ -3145,19 +3145,19 @@
         <v>3.78</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.35</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.87</v>
+        <v>10.58</v>
       </c>
       <c r="CE6" t="n">
         <v>1.47</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CG6" t="n">
         <v>2.5</v>
@@ -3169,28 +3169,28 @@
         <v>1.57</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CR6" t="n">
         <v>1.57</v>
@@ -3199,67 +3199,67 @@
         <v>2.45</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CU6" t="n">
         <v>1.91</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CW6" t="n">
         <v>1.82</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DD6" t="n">
-        <v>74.59999999999999</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="DI6" t="n">
-        <v>17.7</v>
+        <v>18.55</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="DL6" t="n">
-        <v>12.6</v>
+        <v>12.64</v>
       </c>
       <c r="DM6" t="n">
-        <v>11.9</v>
+        <v>12.09</v>
       </c>
       <c r="DN6" t="n">
-        <v>5.7</v>
+        <v>6.18</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
@@ -3271,28 +3271,28 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>45.8</v>
+        <v>44.54</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DT6" t="n">
-        <v>9.5</v>
+        <v>8.82</v>
       </c>
       <c r="DU6" t="n">
-        <v>6.6</v>
+        <v>6.18</v>
       </c>
       <c r="DV6" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="DW6" t="n">
-        <v>10.2</v>
+        <v>10.63</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>112.5</v>
+        <v>109.6</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3720,67 +3720,67 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M8" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.75</v>
+        <v>63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.25</v>
+        <v>14.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3867,67 +3867,67 @@
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.5</v>
+        <v>9.91</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT8" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CC8" t="n">
         <v>3.29</v>
@@ -3936,13 +3936,13 @@
         <v>3.86</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CH8" t="n">
         <v>1.3</v>
@@ -3954,40 +3954,40 @@
         <v>2.07</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="CR8" t="n">
         <v>1.77</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CT8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CU8" t="n">
         <v>1.8</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
         <v>1.92</v>
@@ -3996,85 +3996,85 @@
         <v>1.43</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DD8" t="n">
-        <v>88.3</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="DG8" t="n">
-        <v>5.2</v>
+        <v>4.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DI8" t="n">
-        <v>32.4</v>
+        <v>30.64</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="DL8" t="n">
-        <v>11.5</v>
+        <v>11.63</v>
       </c>
       <c r="DM8" t="n">
-        <v>8.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DN8" t="n">
-        <v>5.9</v>
+        <v>6.09</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>52.1</v>
+        <v>53.55</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DT8" t="n">
         <v>12</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.7</v>
+        <v>7.63</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="DW8" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="9">
@@ -4084,94 +4084,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="H9" t="n">
-        <v>99.67</v>
+        <v>95.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="K9" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>28.67</v>
+        <v>30.43</v>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>13.67</v>
+        <v>13.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>55.67</v>
+        <v>54.57</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.17</v>
+        <v>13.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.83</v>
+        <v>17.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4255,67 +4255,67 @@
         <v>2.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.91</v>
+        <v>10.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.27</v>
+        <v>3.83</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>2.25</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>2.27</v>
-      </c>
       <c r="CA9" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CB9" t="n">
         <v>3.14</v>
@@ -4333,22 +4333,22 @@
         <v>3.2</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI9" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK9" t="n">
         <v>1.67</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CM9" t="n">
         <v>2.09</v>
@@ -4366,10 +4366,10 @@
         <v>4.22</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
@@ -4384,88 +4384,88 @@
         <v>1.83</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="DD9" t="n">
-        <v>91.81999999999999</v>
+        <v>89.83</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="DI9" t="n">
-        <v>28.64</v>
+        <v>29.67</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.55</v>
+        <v>13.58</v>
       </c>
       <c r="DM9" t="n">
-        <v>10.09</v>
+        <v>9.75</v>
       </c>
       <c r="DN9" t="n">
-        <v>7.09</v>
+        <v>6.83</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>51.46</v>
+        <v>51.17</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.37</v>
+        <v>12.5</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.369999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DV9" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="DW9" t="n">
-        <v>16.73</v>
+        <v>16.67</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="10">
@@ -4475,94 +4475,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>91.33</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K10" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="L10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M10" t="n">
-        <v>45.67</v>
+        <v>45.71</v>
       </c>
       <c r="N10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="P10" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5</v>
+        <v>6.71</v>
       </c>
       <c r="S10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>50.33</v>
+        <v>52.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.5</v>
+        <v>13.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.67</v>
+        <v>18.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4646,70 +4646,70 @@
         <v>3.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.91</v>
+        <v>7.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="CC10" t="n">
         <v>4.27</v>
@@ -4718,49 +4718,49 @@
         <v>4.51</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN10" t="n">
         <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.83</v>
+        <v>4.76</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CT10" t="n">
         <v>1.92</v>
@@ -4771,88 +4771,88 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.96</v>
+        <v>4.91</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DD10" t="n">
-        <v>89.27</v>
+        <v>87.33</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DI10" t="n">
-        <v>38.37</v>
+        <v>39</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DK10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>8.91</v>
+        <v>9.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>10.73</v>
+        <v>10.84</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.91</v>
+        <v>5.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>50.91</v>
+        <v>52.34</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DT10" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="DU10" t="n">
-        <v>8.82</v>
+        <v>9.17</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DW10" t="n">
-        <v>16.46</v>
+        <v>16.58</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4862,13 +4862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4955,136 +4955,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>63.4</v>
+        <v>61.83</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>6.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.6</v>
+        <v>40.17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>12</v>
+        <v>13.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BH11" t="n">
-        <v>6.3</v>
+        <v>7.09</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY11" t="n">
         <v>3.24</v>
@@ -5093,28 +5093,28 @@
         <v>3.39</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="CC11" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="CD11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI11" t="n">
         <v>1.67</v>
@@ -5123,13 +5123,13 @@
         <v>2.16</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL11" t="n">
         <v>2.35</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
         <v>1.63</v>
@@ -5141,13 +5141,13 @@
         <v>2.2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CR11" t="n">
         <v>1.68</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CT11" t="n">
         <v>1.82</v>
@@ -5162,88 +5162,88 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="DD11" t="n">
-        <v>64.3</v>
+        <v>63.36</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DI11" t="n">
-        <v>15.8</v>
+        <v>15.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.6</v>
+        <v>10.36</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.7</v>
+        <v>7.18</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.4</v>
+        <v>6.37</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>44.7</v>
+        <v>43.18</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DU11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="DW11" t="n">
-        <v>13.5</v>
+        <v>14.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="12">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
@@ -5346,136 +5346,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>88.67</v>
+        <v>88.14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.83</v>
+        <v>30.29</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.67</v>
+        <v>10.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.83</v>
+        <v>11.57</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51.83</v>
+        <v>49</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.83</v>
+        <v>11.43</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BP12" t="n">
         <v>3</v>
       </c>
-      <c r="BD12" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>3.09</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY12" t="n">
         <v>1.94</v>
@@ -5484,157 +5484,157 @@
         <v>2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CB12" t="n">
         <v>3.4</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.36</v>
+        <v>4.51</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.18</v>
+        <v>5.27</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CK12" t="n">
         <v>1.51</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CL12" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO12" t="n">
         <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CS12" t="n">
         <v>2.16</v>
       </c>
       <c r="CT12" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="CU12" t="n">
         <v>1.94</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="CW12" t="n">
         <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DD12" t="n">
-        <v>102.18</v>
+        <v>100.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>33.54</v>
+        <v>31.5</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DK12" t="n">
         <v>2.09</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.640000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.91</v>
+        <v>11.25</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>55.18</v>
+        <v>53.25</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>13.09</v>
+        <v>12.75</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="DV12" t="n">
-        <v>4.18</v>
+        <v>3.83</v>
       </c>
       <c r="DW12" t="n">
-        <v>17.18</v>
+        <v>17.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13">
@@ -5644,94 +5644,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>109.5</v>
+        <v>103</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>46</v>
+        <v>43.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>8.75</v>
+        <v>10.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>64.25</v>
+        <v>59.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.25</v>
+        <v>20.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>14.75</v>
+        <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5815,49 +5815,49 @@
         <v>2.83</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.6</v>
+        <v>9.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BR13" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU13" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5866,19 +5866,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="CC13" t="n">
         <v>2.53</v>
@@ -5887,28 +5887,28 @@
         <v>2.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
         <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
@@ -5917,19 +5917,19 @@
         <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CS13" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CT13" t="n">
         <v>1.81</v>
@@ -5944,88 +5944,88 @@
         <v>1.76</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.98</v>
+        <v>3.87</v>
       </c>
       <c r="DA13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DB13" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>91.40000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DG13" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DI13" t="n">
-        <v>31.4</v>
+        <v>31.64</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DL13" t="n">
-        <v>9.6</v>
+        <v>10.18</v>
       </c>
       <c r="DM13" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="DN13" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>54.4</v>
+        <v>53.18</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT13" t="n">
-        <v>14.9</v>
+        <v>15.18</v>
       </c>
       <c r="DU13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="DV13" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="DW13" t="n">
-        <v>14.6</v>
+        <v>15.27</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="14">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6128,136 +6128,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>68.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.4</v>
+        <v>22.33</v>
       </c>
       <c r="AO14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL14" t="n">
         <v>1</v>
       </c>
-      <c r="AP14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BM14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>3.02</v>
@@ -6266,124 +6266,124 @@
         <v>3.19</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB14" t="n">
         <v>3.4</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.46</v>
+        <v>5.35</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.04</v>
+        <v>5.84</v>
       </c>
       <c r="CE14" t="n">
         <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK14" t="n">
         <v>1.75</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="CM14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO14" t="n">
         <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CT14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CU14" t="n">
         <v>1.85</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW14" t="n">
         <v>1.88</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DD14" t="n">
-        <v>66.64</v>
+        <v>70.33</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.18</v>
+        <v>4.34</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="DI14" t="n">
-        <v>18.55</v>
+        <v>20.5</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DK14" t="n">
         <v>1</v>
       </c>
       <c r="DL14" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="DM14" t="n">
-        <v>11.55</v>
+        <v>12</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
@@ -6395,28 +6395,28 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>44.46</v>
+        <v>46.08</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>9.27</v>
+        <v>9.67</v>
       </c>
       <c r="DU14" t="n">
-        <v>6.18</v>
+        <v>6.66</v>
       </c>
       <c r="DV14" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DW14" t="n">
-        <v>10.45</v>
+        <v>11</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="15">
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6516,118 +6516,118 @@
         <v>2.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>27.4</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>8.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>51.6</v>
+        <v>52.83</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>7.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.2</v>
+        <v>4.67</v>
       </c>
       <c r="BD15" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.27</v>
+        <v>9.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BP15" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6636,19 +6636,19 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY15" t="n">
         <v>1.87</v>
@@ -6657,61 +6657,61 @@
         <v>1.95</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CC15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.64</v>
+        <v>3.92</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK15" t="n">
         <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CS15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CT15" t="n">
         <v>1.75</v>
@@ -6726,88 +6726,88 @@
         <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DD15" t="n">
-        <v>95.18000000000001</v>
+        <v>95.42</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="DG15" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="DV15" t="n">
         <v>5</v>
       </c>
-      <c r="DH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>53.73</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>5.27</v>
-      </c>
       <c r="DW15" t="n">
-        <v>14.46</v>
+        <v>14.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -6829,82 +6829,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="H16" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>22.6</v>
+        <v>24.33</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>10.2</v>
+        <v>9.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="R16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.4</v>
+        <v>55.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>13.8</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0.33</v>
@@ -6988,70 +6988,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.91</v>
+        <v>9.42</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="BR16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="CC16" t="n">
         <v>4.7</v>
@@ -7060,16 +7060,16 @@
         <v>4.46</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
         <v>2.81</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="CI16" t="n">
         <v>1.65</v>
@@ -7078,127 +7078,127 @@
         <v>2.11</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CO16" t="n">
         <v>1.34</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CT16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CU16" t="n">
         <v>1.88</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.85</v>
+        <v>4.73</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="DD16" t="n">
-        <v>86.18000000000001</v>
+        <v>89.84</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.36</v>
+        <v>4.92</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="DI16" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>12.91</v>
+        <v>12.25</v>
       </c>
       <c r="DM16" t="n">
-        <v>9.09</v>
+        <v>8.58</v>
       </c>
       <c r="DN16" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="DO16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>45.73</v>
+        <v>47.92</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>11.37</v>
+        <v>12.58</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.18</v>
+        <v>8.08</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.18</v>
+        <v>4.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>16</v>
+        <v>16.66</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="DY16" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17">
@@ -7990,13 +7990,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0.5</v>
@@ -8080,118 +8080,118 @@
         <v>2.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.40000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>35.6</v>
+        <v>33.33</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.6</v>
+        <v>12.67</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>45</v>
+        <v>43.67</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.2</v>
+        <v>5.83</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="BD19" t="n">
-        <v>13.2</v>
+        <v>12.67</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.55</v>
+        <v>10.67</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.73</v>
+        <v>3.33</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.82</v>
+        <v>5.25</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8200,19 +8200,19 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY19" t="n">
         <v>1.81</v>
@@ -8224,58 +8224,58 @@
         <v>3.24</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH19" t="n">
         <v>1.32</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN19" t="n">
         <v>1.73</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.96</v>
+        <v>3.87</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CS19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
@@ -8290,88 +8290,88 @@
         <v>1.86</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CZ19" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DC19" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="DD19" t="n">
-        <v>89</v>
+        <v>88.16</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.91</v>
+        <v>5.66</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="DI19" t="n">
-        <v>40.73</v>
+        <v>39.16</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DK19" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="DL19" t="n">
-        <v>9.82</v>
+        <v>9.75</v>
       </c>
       <c r="DM19" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="DN19" t="n">
-        <v>5.27</v>
+        <v>5.66</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>52.27</v>
+        <v>51</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>14.09</v>
+        <v>13.84</v>
       </c>
       <c r="DU19" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="DV19" t="n">
-        <v>6.18</v>
+        <v>5.83</v>
       </c>
       <c r="DW19" t="n">
-        <v>11.45</v>
+        <v>11.34</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="20">
@@ -8772,13 +8772,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>0.2</v>
@@ -8865,49 +8865,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>101</v>
+        <v>94.5</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.2</v>
+        <v>5.83</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN21" t="n">
-        <v>27.2</v>
+        <v>26.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.4</v>
+        <v>9.67</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -8919,73 +8919,73 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>45</v>
+        <v>46.17</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>13.4</v>
+        <v>12.67</v>
       </c>
       <c r="BB21" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="BD21" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BF21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.1</v>
+        <v>8.73</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU21" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY21" t="n">
         <v>1.92</v>
@@ -9003,58 +9003,58 @@
         <v>2.03</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CC21" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="CD21" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP21" t="n">
         <v>2.26</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CS21" t="n">
         <v>2.15</v>
@@ -9072,55 +9072,55 @@
         <v>1.83</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="DD21" t="n">
-        <v>95.59999999999999</v>
+        <v>92.55</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.2</v>
+        <v>5.54</v>
       </c>
       <c r="DH21" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DI21" t="n">
-        <v>30.8</v>
+        <v>30.09</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DK21" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="DL21" t="n">
-        <v>11.6</v>
+        <v>11.09</v>
       </c>
       <c r="DM21" t="n">
-        <v>7.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DN21" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>48.8</v>
+        <v>49.09</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT21" t="n">
-        <v>13.8</v>
+        <v>13.37</v>
       </c>
       <c r="DU21" t="n">
-        <v>8.6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DV21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.8</v>
+        <v>15.46</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,61 +1351,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>88.40000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>4.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>43.4</v>
+        <v>41.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>13.4</v>
+        <v>13.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.8</v>
+        <v>14.17</v>
       </c>
       <c r="R2" t="n">
-        <v>6.8</v>
+        <v>7.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51</v>
+        <v>49.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>11.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.6</v>
+        <v>7.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.2</v>
+        <v>18.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1522,70 +1522,70 @@
         <v>2.17</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP2" t="n">
         <v>3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="CC2" t="n">
         <v>5.84</v>
@@ -1597,46 +1597,46 @@
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CH2" t="n">
         <v>1.3</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL2" t="n">
         <v>2.2</v>
       </c>
-      <c r="CK2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.21</v>
-      </c>
       <c r="CM2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
         <v>1.41</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CR2" t="n">
         <v>1.66</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CT2" t="n">
         <v>1.81</v>
@@ -1648,91 +1648,91 @@
         <v>1.92</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX2" t="n">
         <v>1.44</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.49</v>
+        <v>4.52</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB2" t="n">
         <v>2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DD2" t="n">
-        <v>77.91</v>
+        <v>77.92</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="DV2" t="n">
         <v>3</v>
       </c>
-      <c r="DG2" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>2.91</v>
-      </c>
       <c r="DW2" t="n">
-        <v>18.18</v>
+        <v>18</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="3">
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1835,124 +1835,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>86.2</v>
+        <v>83.17</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP3" t="n">
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.8</v>
+        <v>14.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.2</v>
+        <v>12.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BF3" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.5</v>
+        <v>6.64</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY3" t="n">
         <v>1.76</v>
@@ -1973,49 +1973,49 @@
         <v>1.83</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CD3" t="n">
         <v>3.29</v>
       </c>
-      <c r="CB3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>3.46</v>
-      </c>
       <c r="CE3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL3" t="n">
         <v>2.27</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
         <v>2.31</v>
@@ -2027,103 +2027,103 @@
         <v>1.76</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CT3" t="n">
         <v>1.8</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CX3" t="n">
         <v>1.44</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DD3" t="n">
-        <v>91.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DI3" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DK3" t="n">
         <v>1</v>
       </c>
       <c r="DL3" t="n">
-        <v>15.6</v>
+        <v>14.82</v>
       </c>
       <c r="DM3" t="n">
-        <v>12.5</v>
+        <v>12.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.3</v>
+        <v>13.55</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DV3" t="n">
-        <v>5.1</v>
+        <v>4.73</v>
       </c>
       <c r="DW3" t="n">
-        <v>15</v>
+        <v>16.27</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="4">
@@ -2524,94 +2524,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="n">
-        <v>78.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>29.33</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="P5" t="n">
-        <v>10.4</v>
+        <v>9.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54</v>
+        <v>56.83</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.6</v>
+        <v>18.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.4</v>
+        <v>19.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2695,70 +2695,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.18</v>
+        <v>8.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="CC5" t="n">
         <v>2.05</v>
@@ -2770,138 +2770,138 @@
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="CR5" t="n">
         <v>1.89</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="DD5" t="n">
-        <v>81.55</v>
+        <v>84</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DI5" t="n">
-        <v>30.09</v>
+        <v>30.58</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.37</v>
+        <v>11</v>
       </c>
       <c r="DM5" t="n">
-        <v>11.09</v>
+        <v>11.16</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>55.36</v>
+        <v>56.66</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>15.36</v>
+        <v>15.92</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.27</v>
+        <v>9.67</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="DW5" t="n">
-        <v>15.82</v>
+        <v>16.92</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="6">
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4177,49 +4177,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>82.40000000000001</v>
+        <v>86.17</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.6</v>
+        <v>31</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.4</v>
+        <v>13.83</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.2</v>
+        <v>9.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4231,82 +4231,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.4</v>
+        <v>48.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.4</v>
+        <v>10.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.33</v>
+        <v>10.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY9" t="n">
         <v>2.24</v>
@@ -4315,22 +4315,22 @@
         <v>2.25</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="CE9" t="n">
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CG9" t="n">
         <v>2.45</v>
@@ -4345,25 +4345,25 @@
         <v>2</v>
       </c>
       <c r="CK9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CN9" t="n">
         <v>1.67</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.65</v>
       </c>
       <c r="CO9" t="n">
         <v>1.41</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CR9" t="n">
         <v>1.79</v>
@@ -4375,7 +4375,7 @@
         <v>1.89</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CV9" t="n">
         <v>1.84</v>
@@ -4387,52 +4387,52 @@
         <v>1.44</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="DA9" t="n">
         <v>0.08</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="DD9" t="n">
-        <v>89.83</v>
+        <v>91</v>
       </c>
       <c r="DE9" t="n">
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DI9" t="n">
-        <v>29.67</v>
+        <v>30.69</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="DM9" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="DN9" t="n">
-        <v>6.83</v>
+        <v>6.69</v>
       </c>
       <c r="DO9" t="n">
         <v>0.08</v>
@@ -4444,28 +4444,28 @@
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>51.17</v>
+        <v>51.85</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.5</v>
+        <v>12.08</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.25</v>
+        <v>8.08</v>
       </c>
       <c r="DV9" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="DW9" t="n">
-        <v>16.67</v>
+        <v>17.54</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -6907,52 +6907,52 @@
         <v>3.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>89.67</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.67</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.17</v>
+        <v>14.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>6.14</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -6964,82 +6964,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40.17</v>
+        <v>38.57</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.33</v>
+        <v>6.86</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.83</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
         <v>1.08</v>
       </c>
       <c r="BP16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY16" t="n">
         <v>2.5</v>
@@ -7048,124 +7048,124 @@
         <v>2.4</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.7</v>
+        <v>4.03</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.46</v>
+        <v>4.98</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CJ16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CL16" t="n">
         <v>2.11</v>
       </c>
-      <c r="CK16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>2.12</v>
-      </c>
       <c r="CM16" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CT16" t="n">
         <v>1.88</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CV16" t="n">
         <v>1.84</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.73</v>
+        <v>4.53</v>
       </c>
       <c r="DA16" t="n">
         <v>0.16</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="DD16" t="n">
-        <v>89.84</v>
+        <v>87.31</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="DH16" t="n">
         <v>0.08</v>
       </c>
       <c r="DI16" t="n">
-        <v>27.5</v>
+        <v>27.38</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DL16" t="n">
-        <v>12.25</v>
+        <v>12.23</v>
       </c>
       <c r="DM16" t="n">
-        <v>8.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DN16" t="n">
-        <v>6.58</v>
+        <v>7.08</v>
       </c>
       <c r="DO16" t="n">
         <v>0.08</v>
@@ -7177,28 +7177,28 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>47.92</v>
+        <v>46.46</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT16" t="n">
-        <v>12.58</v>
+        <v>12.46</v>
       </c>
       <c r="DU16" t="n">
-        <v>8.08</v>
+        <v>8.23</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.5</v>
+        <v>4.23</v>
       </c>
       <c r="DW16" t="n">
-        <v>16.66</v>
+        <v>16.85</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DY16" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="17">
@@ -7599,13 +7599,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0.29</v>
@@ -7692,136 +7692,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>72.2</v>
+        <v>70.17</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>24.6</v>
+        <v>22.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>41.8</v>
+        <v>40.17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>14.6</v>
+        <v>15.17</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>13.6</v>
+        <v>12.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.25</v>
+        <v>9.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
         <v>1.08</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="BR18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY18" t="n">
         <v>1.89</v>
@@ -7833,64 +7833,64 @@
         <v>3.21</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH18" t="n">
         <v>1.33</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CT18" t="n">
         <v>1.85</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CV18" t="n">
         <v>1.87</v>
@@ -7899,88 +7899,88 @@
         <v>1.82</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DD18" t="n">
-        <v>75.92</v>
+        <v>74.69</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="DG18" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DI18" t="n">
-        <v>26</v>
+        <v>24.92</v>
       </c>
       <c r="DJ18" t="n">
         <v>1.08</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>7.67</v>
+        <v>7.16</v>
       </c>
       <c r="DN18" t="n">
-        <v>6.08</v>
+        <v>6.46</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>46.75</v>
+        <v>45.62</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>15.83</v>
+        <v>16</v>
       </c>
       <c r="DU18" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="DV18" t="n">
-        <v>5.08</v>
+        <v>5.23</v>
       </c>
       <c r="DW18" t="n">
-        <v>16.08</v>
+        <v>15.54</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="19">
@@ -7990,94 +7990,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>100.71</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>45</v>
+        <v>41.43</v>
       </c>
       <c r="N19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="P19" t="n">
-        <v>10.67</v>
+        <v>9.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>4.43</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.33</v>
+        <v>59.71</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.17</v>
+        <v>10.86</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.33</v>
+        <v>6.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>10.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0.17</v>
@@ -8161,37 +8161,37 @@
         <v>3.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.67</v>
+        <v>10.46</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BJ19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM19" t="n">
         <v>0.92</v>
       </c>
-      <c r="BK19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BN19" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8200,28 +8200,28 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW19" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX19" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB19" t="n">
         <v>3.36</v>
@@ -8236,46 +8236,46 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CS19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
@@ -8287,91 +8287,91 @@
         <v>1.88</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CZ19" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DD19" t="n">
-        <v>88.16</v>
+        <v>90.84</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF19" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.66</v>
+        <v>5.54</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DI19" t="n">
-        <v>39.16</v>
+        <v>37.69</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="DK19" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="DL19" t="n">
-        <v>9.75</v>
+        <v>9.15</v>
       </c>
       <c r="DM19" t="n">
-        <v>8.83</v>
+        <v>8.23</v>
       </c>
       <c r="DN19" t="n">
-        <v>5.66</v>
+        <v>6</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>51</v>
+        <v>52.31</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>13.84</v>
+        <v>14.15</v>
       </c>
       <c r="DU19" t="n">
-        <v>8</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DV19" t="n">
-        <v>5.83</v>
+        <v>5.61</v>
       </c>
       <c r="DW19" t="n">
-        <v>11.34</v>
+        <v>11.61</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DY19" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="20">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>5</v>
@@ -8393,49 +8393,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>97.17</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>5.67</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M20" t="n">
-        <v>46.2</v>
+        <v>51.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>12.2</v>
+        <v>12.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>15.2</v>
+        <v>13.83</v>
       </c>
       <c r="R20" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8447,28 +8447,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>45.6</v>
+        <v>47.83</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>17</v>
+        <v>16.67</v>
       </c>
       <c r="AD20" t="n">
         <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8552,70 +8552,70 @@
         <v>2.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BR20" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS20" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT20" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU20" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV20" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CC20" t="n">
         <v>3.25</v>
@@ -8627,10 +8627,10 @@
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
@@ -8642,13 +8642,13 @@
         <v>2.03</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CN20" t="n">
         <v>1.69</v>
@@ -8657,10 +8657,10 @@
         <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CR20" t="n">
         <v>1.8</v>
@@ -8669,67 +8669,67 @@
         <v>2.02</v>
       </c>
       <c r="CT20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CX20" t="n">
         <v>1.43</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ20" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DG20" t="n">
         <v>4.46</v>
       </c>
-      <c r="DA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>86</v>
-      </c>
-      <c r="DE20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="DH20" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DI20" t="n">
-        <v>37.1</v>
+        <v>40.82</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DK20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DL20" t="n">
-        <v>10.2</v>
+        <v>10.45</v>
       </c>
       <c r="DM20" t="n">
-        <v>11.1</v>
+        <v>10.73</v>
       </c>
       <c r="DN20" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>45.9</v>
+        <v>47.09</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
@@ -8750,19 +8750,19 @@
         <v>12</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="DW20" t="n">
-        <v>16.6</v>
+        <v>16.46</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1579,13 +1579,13 @@
         <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="CA2" t="n">
         <v>3.49</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC2" t="n">
         <v>5.84</v>
@@ -1636,7 +1636,7 @@
         <v>1.66</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CT2" t="n">
         <v>1.81</v>
@@ -1651,13 +1651,13 @@
         <v>1.83</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="DA2" t="n">
         <v>0.08</v>
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2226,49 +2226,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>92.40000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>30.4</v>
+        <v>28.17</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>7.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2280,82 +2280,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51</v>
+        <v>49.33</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.2</v>
+        <v>10.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.82</v>
+        <v>8.33</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="BR4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY4" t="n">
         <v>1.82</v>
@@ -2364,40 +2364,40 @@
         <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="CE4" t="n">
         <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CK4" t="n">
         <v>1.73</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CM4" t="n">
         <v>2</v>
@@ -2406,19 +2406,19 @@
         <v>1.61</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CT4" t="n">
         <v>1.83</v>
@@ -2433,55 +2433,55 @@
         <v>1.88</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>99.64</v>
+        <v>98.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DI4" t="n">
-        <v>37.91</v>
+        <v>36.17</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DL4" t="n">
-        <v>11.55</v>
+        <v>11.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.73</v>
+        <v>7.16</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>53.36</v>
+        <v>52.33</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.37</v>
+        <v>12.42</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="DW4" t="n">
-        <v>16.54</v>
+        <v>16.16</v>
       </c>
       <c r="DX4" t="n">
         <v>1.32</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
@@ -2911,61 +2911,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="H6" t="n">
-        <v>89.40000000000001</v>
+        <v>86.17</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>14.6</v>
+        <v>14.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.4</v>
+        <v>8.83</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -2977,28 +2977,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53.8</v>
+        <v>51.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.8</v>
+        <v>9.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.2</v>
+        <v>6.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>10.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3082,70 +3082,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
         <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="CC6" t="n">
         <v>8.119999999999999</v>
@@ -3154,49 +3154,49 @@
         <v>10.58</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CO6" t="n">
         <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CT6" t="n">
         <v>1.86</v>
@@ -3217,49 +3217,49 @@
         <v>2.46</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="DD6" t="n">
-        <v>74.18000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DI6" t="n">
-        <v>18.55</v>
+        <v>19.5</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="DL6" t="n">
-        <v>12.64</v>
+        <v>12.58</v>
       </c>
       <c r="DM6" t="n">
-        <v>12.09</v>
+        <v>11.58</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.18</v>
+        <v>6.34</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
@@ -3271,28 +3271,28 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>44.54</v>
+        <v>44.16</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DT6" t="n">
-        <v>8.82</v>
+        <v>8.42</v>
       </c>
       <c r="DU6" t="n">
-        <v>6.18</v>
+        <v>5.83</v>
       </c>
       <c r="DV6" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DW6" t="n">
-        <v>10.63</v>
+        <v>11.5</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="7">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3395,115 +3395,115 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="AI7" t="n">
-        <v>85.17</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>33</v>
+        <v>37.29</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>11.71</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.17</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>48.17</v>
+        <v>49.86</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.17</v>
+        <v>9.57</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.83</v>
+        <v>4.71</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.83</v>
+        <v>17.86</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.25</v>
+        <v>10.69</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
         <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3512,19 +3512,19 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BY7" t="n">
         <v>2.77</v>
@@ -3533,40 +3533,40 @@
         <v>2.98</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.42</v>
+        <v>4.13</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.05</v>
+        <v>5.49</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM7" t="n">
         <v>1.84</v>
@@ -3581,13 +3581,13 @@
         <v>2.23</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CT7" t="n">
         <v>1.82</v>
@@ -3605,22 +3605,22 @@
         <v>1.39</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>74.5</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3629,61 +3629,61 @@
         <v>3.08</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.67</v>
+        <v>4.08</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DI7" t="n">
-        <v>29.08</v>
+        <v>31.7</v>
       </c>
       <c r="DJ7" t="n">
         <v>1</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>10.92</v>
+        <v>10.84</v>
       </c>
       <c r="DM7" t="n">
-        <v>11.25</v>
+        <v>10.77</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.75</v>
+        <v>9.31</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>46.92</v>
+        <v>47.93</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DT7" t="n">
-        <v>8.08</v>
+        <v>8.85</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.66</v>
+        <v>4.92</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.42</v>
+        <v>3.92</v>
       </c>
       <c r="DW7" t="n">
-        <v>14.42</v>
+        <v>14.69</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="8">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3783,52 +3783,52 @@
         <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.17</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>25.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.83</v>
+        <v>11.86</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3840,82 +3840,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.67</v>
+        <v>47.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.83</v>
+        <v>10.14</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.83</v>
+        <v>6.43</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.67</v>
+        <v>14.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.91</v>
+        <v>9.83</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY8" t="n">
         <v>1.93</v>
@@ -3924,25 +3924,25 @@
         <v>1.98</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.29</v>
+        <v>3.11</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="CE8" t="n">
         <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CH8" t="n">
         <v>1.3</v>
@@ -3951,31 +3951,31 @@
         <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CS8" t="n">
         <v>2.09</v>
@@ -3999,82 +3999,82 @@
         <v>2.36</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="DD8" t="n">
-        <v>89.18000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DI8" t="n">
-        <v>30.64</v>
+        <v>31.34</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DL8" t="n">
-        <v>11.63</v>
+        <v>11.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>8.460000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DN8" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>53.55</v>
+        <v>54.08</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DT8" t="n">
         <v>12</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.63</v>
+        <v>7.83</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.36</v>
+        <v>4.16</v>
       </c>
       <c r="DW8" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4318,13 +4318,13 @@
         <v>3.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CC9" t="n">
         <v>3.33</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="CE9" t="n">
         <v>1.48</v>
@@ -4366,10 +4366,10 @@
         <v>4.24</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
@@ -4381,16 +4381,16 @@
         <v>1.84</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.57</v>
+        <v>4.63</v>
       </c>
       <c r="DA9" t="n">
         <v>0.08</v>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0.29</v>
@@ -4568,136 +4568,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.8</v>
+        <v>84.17</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK10" t="n">
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>29.6</v>
+        <v>27.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.8</v>
+        <v>14.67</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY10" t="n">
         <v>2.67</v>
@@ -4706,22 +4706,22 @@
         <v>2.69</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB10" t="n">
         <v>3.19</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.51</v>
+        <v>4.24</v>
       </c>
       <c r="CE10" t="n">
         <v>1.54</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG10" t="n">
         <v>2.34</v>
@@ -4733,13 +4733,13 @@
         <v>1.67</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CM10" t="n">
         <v>1.91</v>
@@ -4754,13 +4754,13 @@
         <v>2.41</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CT10" t="n">
         <v>1.92</v>
@@ -4774,82 +4774,82 @@
         <v>1.49</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DB10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DC10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DD10" t="n">
-        <v>87.33</v>
+        <v>86.08</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.83</v>
+        <v>3.61</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DI10" t="n">
-        <v>39</v>
+        <v>37.46</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.33</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>10.84</v>
+        <v>11.46</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>52.34</v>
+        <v>51.77</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="DT10" t="n">
-        <v>13.33</v>
+        <v>13.08</v>
       </c>
       <c r="DU10" t="n">
-        <v>9.17</v>
+        <v>8.92</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="DW10" t="n">
-        <v>16.58</v>
+        <v>16.77</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DY10" t="n">
         <v>3</v>
@@ -4862,94 +4862,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H11" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5033,70 +5033,70 @@
         <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.09</v>
+        <v>7.83</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CC11" t="n">
         <v>7.38</v>
@@ -5105,10 +5105,10 @@
         <v>8.92</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CG11" t="n">
         <v>2.55</v>
@@ -5117,22 +5117,22 @@
         <v>1.32</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK11" t="n">
         <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
@@ -5141,13 +5141,13 @@
         <v>2.2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CT11" t="n">
         <v>1.82</v>
@@ -5162,88 +5162,88 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="DA11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="DD11" t="n">
-        <v>63.36</v>
+        <v>61.66</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="DI11" t="n">
-        <v>15.18</v>
+        <v>15.84</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.36</v>
+        <v>9.92</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.18</v>
+        <v>7.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>6.37</v>
+        <v>6.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>43.18</v>
+        <v>42.92</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="DU11" t="n">
         <v>5</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="DW11" t="n">
-        <v>14.09</v>
+        <v>14.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="12">
@@ -5253,94 +5253,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="H12" t="n">
-        <v>118.4</v>
+        <v>113.17</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M12" t="n">
-        <v>33.2</v>
+        <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>9.6</v>
+        <v>11.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="R12" t="n">
-        <v>4.8</v>
+        <v>5.67</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>59.2</v>
+        <v>58.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.6</v>
+        <v>13.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>8.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.6</v>
+        <v>19.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5424,70 +5424,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.42</v>
+        <v>7.31</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BP12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT12" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC12" t="n">
         <v>4.51</v>
@@ -5496,49 +5496,49 @@
         <v>5.27</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CH12" t="n">
         <v>1.2</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CK12" t="n">
         <v>1.52</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.51</v>
-      </c>
       <c r="CL12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM12" t="n">
         <v>1.93</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CT12" t="n">
         <v>1.86</v>
@@ -5553,88 +5553,88 @@
         <v>1.79</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CY12" t="n">
         <v>2.36</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="DA12" t="n">
         <v>0.08</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DD12" t="n">
-        <v>100.75</v>
+        <v>99.69</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="DH12" t="n">
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>31.5</v>
+        <v>32.46</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DL12" t="n">
-        <v>10.17</v>
+        <v>10.92</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.25</v>
+        <v>11.23</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.17</v>
+        <v>5.54</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>53.25</v>
+        <v>53.38</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>12.75</v>
+        <v>12.31</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.92</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="DW12" t="n">
-        <v>17.17</v>
+        <v>17.93</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5737,127 +5737,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>79.33</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.17</v>
+        <v>3.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="AN13" t="n">
-        <v>21.67</v>
+        <v>23.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>10.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.67</v>
+        <v>5.71</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.83</v>
+        <v>48.29</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BD13" t="n">
         <v>13</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
         <v>1.74</v>
@@ -5875,25 +5875,25 @@
         <v>1.92</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -5902,19 +5902,19 @@
         <v>1.79</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK13" t="n">
         <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.36</v>
@@ -5923,13 +5923,13 @@
         <v>2.12</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CS13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CT13" t="n">
         <v>1.81</v>
@@ -5947,85 +5947,85 @@
         <v>1.36</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="DD13" t="n">
-        <v>90.09</v>
+        <v>88.17</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="DI13" t="n">
-        <v>31.64</v>
+        <v>32</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="DL13" t="n">
-        <v>10.18</v>
+        <v>9.91</v>
       </c>
       <c r="DM13" t="n">
-        <v>9.82</v>
+        <v>10.42</v>
       </c>
       <c r="DN13" t="n">
-        <v>4.27</v>
+        <v>4.91</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>53.18</v>
+        <v>53</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>15.18</v>
+        <v>15</v>
       </c>
       <c r="DU13" t="n">
         <v>10</v>
       </c>
       <c r="DV13" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="DW13" t="n">
-        <v>15.27</v>
+        <v>15.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -6047,82 +6047,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="G14" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="H14" t="n">
-        <v>72.17</v>
+        <v>71.14</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="K14" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.33</v>
+        <v>-0.29</v>
       </c>
       <c r="M14" t="n">
-        <v>18.67</v>
+        <v>18.14</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>10.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.5</v>
+        <v>7.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.83</v>
+        <v>3.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.67</v>
+        <v>47.57</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.17</v>
+        <v>10.86</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>7.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6206,70 +6206,70 @@
         <v>3.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL14" t="n">
         <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC14" t="n">
         <v>5.35</v>
@@ -6284,7 +6284,7 @@
         <v>3.16</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
@@ -6293,130 +6293,130 @@
         <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK14" t="n">
         <v>1.75</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CR14" t="n">
         <v>1.74</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CT14" t="n">
         <v>1.83</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CV14" t="n">
         <v>1.9</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CX14" t="n">
         <v>1.41</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DD14" t="n">
-        <v>70.33</v>
+        <v>69.92</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="DH14" t="n">
         <v>-0.16</v>
       </c>
       <c r="DI14" t="n">
-        <v>20.5</v>
+        <v>20.07</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DK14" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DL14" t="n">
-        <v>10.25</v>
+        <v>9.92</v>
       </c>
       <c r="DM14" t="n">
-        <v>12</v>
+        <v>11.39</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.66</v>
+        <v>4.85</v>
       </c>
       <c r="DO14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>46.08</v>
+        <v>46.15</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>9.67</v>
+        <v>10.08</v>
       </c>
       <c r="DU14" t="n">
-        <v>6.66</v>
+        <v>7.15</v>
       </c>
       <c r="DV14" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DW14" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="15">
@@ -6426,94 +6426,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H15" t="n">
-        <v>95.83</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>41.67</v>
+        <v>40.57</v>
       </c>
       <c r="N15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O15" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>13.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.83</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.5</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.83</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.17</v>
+        <v>16.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6597,37 +6597,37 @@
         <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6636,31 +6636,31 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU15" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="CC15" t="n">
         <v>3.25</v>
@@ -6675,7 +6675,7 @@
         <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH15" t="n">
         <v>1.35</v>
@@ -6684,10 +6684,10 @@
         <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL15" t="n">
         <v>2.25</v>
@@ -6702,13 +6702,13 @@
         <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CS15" t="n">
         <v>1.97</v>
@@ -6729,85 +6729,85 @@
         <v>1.33</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="DD15" t="n">
-        <v>95.42</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DG15" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="DH15" t="n">
         <v>0.08</v>
       </c>
       <c r="DI15" t="n">
-        <v>35.34</v>
+        <v>35.23</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DL15" t="n">
-        <v>10.58</v>
+        <v>11.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>9.08</v>
+        <v>8.85</v>
       </c>
       <c r="DN15" t="n">
-        <v>4.92</v>
+        <v>5.15</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>54.16</v>
+        <v>54.54</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>13.83</v>
+        <v>13.54</v>
       </c>
       <c r="DU15" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="DV15" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="DW15" t="n">
-        <v>14.08</v>
+        <v>14.07</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="16">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8474,19 +8474,19 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI20" t="n">
-        <v>78</v>
+        <v>79.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL20" t="n">
         <v>3</v>
@@ -8495,28 +8495,28 @@
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>6.83</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>46.2</v>
+        <v>47.33</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -8537,73 +8537,73 @@
         <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>16.2</v>
+        <v>15.33</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BG20" t="n">
         <v>2</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BI20" t="n">
         <v>2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BR20" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS20" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU20" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY20" t="n">
         <v>1.81</v>
@@ -8612,16 +8612,16 @@
         <v>2.79</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CB20" t="n">
         <v>3.17</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
@@ -8630,7 +8630,7 @@
         <v>3.15</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
@@ -8639,16 +8639,16 @@
         <v>1.76</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK20" t="n">
         <v>1.66</v>
       </c>
       <c r="CL20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CM20" t="n">
         <v>2.13</v>
-      </c>
-      <c r="CM20" t="n">
-        <v>2.12</v>
       </c>
       <c r="CN20" t="n">
         <v>1.69</v>
@@ -8660,7 +8660,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="CR20" t="n">
         <v>1.8</v>
@@ -8672,13 +8672,13 @@
         <v>1.77</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CV20" t="n">
         <v>1.94</v>
       </c>
       <c r="CW20" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CX20" t="n">
         <v>1.43</v>
@@ -8687,49 +8687,49 @@
         <v>2.38</v>
       </c>
       <c r="CZ20" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="DD20" t="n">
-        <v>88.45999999999999</v>
+        <v>88.34</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>4.46</v>
+        <v>4.34</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DI20" t="n">
-        <v>40.82</v>
+        <v>39.25</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DK20" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="DL20" t="n">
-        <v>10.45</v>
+        <v>10</v>
       </c>
       <c r="DM20" t="n">
-        <v>10.73</v>
+        <v>10.25</v>
       </c>
       <c r="DN20" t="n">
-        <v>7.64</v>
+        <v>7.66</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8741,28 +8741,28 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>47.09</v>
+        <v>47.58</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="DW20" t="n">
-        <v>16.46</v>
+        <v>16</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -8772,61 +8772,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="H21" t="n">
-        <v>90.2</v>
+        <v>88.33</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="M21" t="n">
-        <v>34.4</v>
+        <v>32.83</v>
       </c>
       <c r="N21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="R21" t="n">
-        <v>6.6</v>
+        <v>7.67</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -8838,25 +8838,25 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.2</v>
+        <v>14.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.6</v>
+        <v>16.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -8943,49 +8943,49 @@
         <v>2.33</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.73</v>
+        <v>9</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP21" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT21" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU21" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8994,19 +8994,19 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC21" t="n">
         <v>2.86</v>
@@ -9015,34 +9015,34 @@
         <v>3.13</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.85</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL21" t="n">
         <v>2.16</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CO21" t="n">
         <v>1.26</v>
@@ -9051,13 +9051,13 @@
         <v>2.26</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CT21" t="n">
         <v>1.83</v>
@@ -9072,55 +9072,55 @@
         <v>1.83</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="DD21" t="n">
-        <v>92.55</v>
+        <v>91.42</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.54</v>
+        <v>5.58</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="DI21" t="n">
-        <v>30.09</v>
+        <v>29.67</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DK21" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="DL21" t="n">
-        <v>11.09</v>
+        <v>11.58</v>
       </c>
       <c r="DM21" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DN21" t="n">
-        <v>6</v>
+        <v>6.58</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>49.09</v>
+        <v>49.08</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT21" t="n">
-        <v>13.37</v>
+        <v>13.75</v>
       </c>
       <c r="DU21" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DV21" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.46</v>
+        <v>15.17</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1754,82 +1754,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>44.6</v>
+        <v>71.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="P3" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.8</v>
+        <v>12.33</v>
       </c>
       <c r="R3" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.4</v>
+        <v>60.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.2</v>
+        <v>18.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.8</v>
+        <v>13.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>17.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1913,46 +1913,46 @@
         <v>3.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.64</v>
+        <v>7.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.27</v>
+        <v>2.92</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,19 +1964,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>1.76</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="CA3" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CC3" t="n">
         <v>2.96</v>
@@ -1988,16 +1988,16 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.03</v>
@@ -2006,22 +2006,22 @@
         <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CR3" t="n">
         <v>1.76</v>
@@ -2042,88 +2042,88 @@
         <v>1.81</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="DD3" t="n">
-        <v>89</v>
+        <v>90.34</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="DI3" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>14.82</v>
+        <v>14.16</v>
       </c>
       <c r="DM3" t="n">
-        <v>12.54</v>
+        <v>12.33</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>56</v>
+        <v>56.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DT3" t="n">
-        <v>13.55</v>
+        <v>14.58</v>
       </c>
       <c r="DU3" t="n">
-        <v>8.82</v>
+        <v>9.92</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="DW3" t="n">
-        <v>16.27</v>
+        <v>17.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3395,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
         <v>0.86</v>
@@ -3407,7 +3407,7 @@
         <v>-0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL7" t="n">
         <v>4.14</v>
@@ -3470,7 +3470,7 @@
         <v>1.21</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="BG7" t="n">
         <v>3.46</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="DC7" t="n">
         <v>1.08</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DG7" t="n">
         <v>4.08</v>
@@ -3683,7 +3683,7 @@
         <v>1.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="8">
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
         <v>1.83</v>
@@ -4580,10 +4580,10 @@
         <v>0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AM10" t="n">
         <v>0.5</v>
@@ -4598,7 +4598,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.67</v>
+        <v>8.83</v>
       </c>
       <c r="AR10" t="n">
         <v>14.5</v>
@@ -4625,7 +4625,7 @@
         <v>50.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -4649,7 +4649,7 @@
         <v>2.69</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.62</v>
+        <v>7.69</v>
       </c>
       <c r="BI10" t="n">
         <v>2.69</v>
@@ -4783,7 +4783,7 @@
         <v>0.16</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DC10" t="n">
         <v>1.92</v>
@@ -4795,10 +4795,10 @@
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="DG10" t="n">
         <v>3.69</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>3.61</v>
       </c>
       <c r="DH10" t="n">
         <v>0.61</v>
@@ -4813,7 +4813,7 @@
         <v>1.77</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.390000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DM10" t="n">
         <v>11.46</v>
@@ -4834,7 +4834,7 @@
         <v>51.77</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="DT10" t="n">
         <v>13.08</v>
@@ -5325,10 +5325,10 @@
         <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
         <v>5.17</v>
@@ -5427,7 +5427,7 @@
         <v>2.62</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="BI12" t="n">
         <v>2.62</v>
@@ -5619,10 +5619,10 @@
         <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>12.31</v>
+        <v>12.23</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DV12" t="n">
         <v>3.77</v>
@@ -6468,7 +6468,7 @@
         <v>2.43</v>
       </c>
       <c r="P15" t="n">
-        <v>13.71</v>
+        <v>13.57</v>
       </c>
       <c r="Q15" t="n">
         <v>9.289999999999999</v>
@@ -6768,7 +6768,7 @@
         <v>1.92</v>
       </c>
       <c r="DL15" t="n">
-        <v>11.15</v>
+        <v>11.08</v>
       </c>
       <c r="DM15" t="n">
         <v>8.85</v>
@@ -7208,13 +7208,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7301,127 +7301,127 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>76</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="AO17" t="n">
         <v>1</v>
       </c>
-      <c r="AI17" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AP17" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>8.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>45.6</v>
+        <v>43.83</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>7.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.83</v>
+        <v>10.23</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT17" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY17" t="n">
         <v>2.26</v>
@@ -7439,25 +7439,25 @@
         <v>2.32</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.46</v>
+        <v>6.65</v>
       </c>
       <c r="CE17" t="n">
         <v>1.46</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH17" t="n">
         <v>1.3</v>
@@ -7472,10 +7472,10 @@
         <v>1.65</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN17" t="n">
         <v>1.69</v>
@@ -7484,16 +7484,16 @@
         <v>1.4</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="CR17" t="n">
         <v>1.72</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
@@ -7508,88 +7508,88 @@
         <v>1.84</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="DA17" t="n">
         <v>0.08</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="DD17" t="n">
-        <v>81.42</v>
+        <v>80.38</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="DI17" t="n">
-        <v>26.75</v>
+        <v>32.31</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DL17" t="n">
-        <v>10.33</v>
+        <v>10.3</v>
       </c>
       <c r="DM17" t="n">
-        <v>8.75</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.66</v>
+        <v>6.38</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>48.83</v>
+        <v>47.77</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT17" t="n">
-        <v>10.42</v>
+        <v>10.31</v>
       </c>
       <c r="DU17" t="n">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DW17" t="n">
-        <v>17.08</v>
+        <v>17</v>
       </c>
       <c r="DX17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1444,49 +1444,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>69.17</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.33</v>
+        <v>22.86</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1498,82 +1498,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.5</v>
+        <v>42.86</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.33</v>
+        <v>17.86</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN2" t="n">
         <v>1.08</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
         <v>3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT2" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY2" t="n">
         <v>2.08</v>
@@ -1582,22 +1582,22 @@
         <v>2.27</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.84</v>
+        <v>5.57</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.9</v>
+        <v>6.47</v>
       </c>
       <c r="CE2" t="n">
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CG2" t="n">
         <v>2.5</v>
@@ -1609,28 +1609,28 @@
         <v>1.65</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CK2" t="n">
         <v>1.66</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM2" t="n">
         <v>2.14</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="CR2" t="n">
         <v>1.66</v>
@@ -1654,52 +1654,52 @@
         <v>1.45</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="DA2" t="n">
         <v>0.08</v>
       </c>
       <c r="DB2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>77.92</v>
+        <v>76.23</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="DG2" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="DH2" t="n">
         <v>0.16</v>
       </c>
       <c r="DI2" t="n">
-        <v>31.92</v>
+        <v>31.46</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>11.33</v>
+        <v>11.15</v>
       </c>
       <c r="DM2" t="n">
         <v>11.92</v>
       </c>
       <c r="DN2" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>45.84</v>
+        <v>45.77</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DU2" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DV2" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DW2" t="n">
-        <v>18</v>
+        <v>18.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="3">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -2145,49 +2145,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>105.67</v>
+        <v>105.43</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>44.17</v>
+        <v>43.29</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>13.67</v>
+        <v>13.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.5</v>
+        <v>11.71</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>6.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2199,28 +2199,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>55.33</v>
+        <v>55.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.83</v>
+        <v>17.29</v>
       </c>
       <c r="AD4" t="n">
         <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2304,64 +2304,64 @@
         <v>1.83</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="BR4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CA4" t="n">
         <v>3.16</v>
@@ -2376,10 +2376,10 @@
         <v>2.76</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CG4" t="n">
         <v>2.42</v>
@@ -2394,19 +2394,19 @@
         <v>2.1</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL4" t="n">
         <v>2.39</v>
       </c>
       <c r="CM4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CP4" t="n">
         <v>2.42</v>
@@ -2436,52 +2436,52 @@
         <v>1.45</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DD4" t="n">
-        <v>98.67</v>
+        <v>99.08</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DG4" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DH4" t="n">
         <v>0.16</v>
       </c>
       <c r="DI4" t="n">
-        <v>36.17</v>
+        <v>36.31</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DL4" t="n">
-        <v>11.25</v>
+        <v>11.46</v>
       </c>
       <c r="DM4" t="n">
-        <v>10.25</v>
+        <v>10.92</v>
       </c>
       <c r="DN4" t="n">
-        <v>7.16</v>
+        <v>6.85</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>52.33</v>
+        <v>52.77</v>
       </c>
       <c r="DS4" t="n">
         <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.42</v>
+        <v>12.54</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="DW4" t="n">
-        <v>16.16</v>
+        <v>16.46</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="5">
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3004,49 +3004,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.5</v>
+        <v>65.14</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>21.43</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>12.71</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.33</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3058,82 +3058,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>36.83</v>
+        <v>40.71</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.33</v>
+        <v>6.57</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="BD6" t="n">
-        <v>12.33</v>
+        <v>12.14</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.83</v>
+        <v>7.62</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
         <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY6" t="n">
         <v>3.47</v>
@@ -3142,55 +3142,55 @@
         <v>3.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.119999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="CD6" t="n">
-        <v>10.58</v>
+        <v>9.83</v>
       </c>
       <c r="CE6" t="n">
         <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CK6" t="n">
         <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="CR6" t="n">
         <v>1.58</v>
@@ -3211,55 +3211,55 @@
         <v>1.82</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="DD6" t="n">
-        <v>73.83</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="DE6" t="n">
         <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="DI6" t="n">
-        <v>19.5</v>
+        <v>21.92</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="DL6" t="n">
-        <v>12.58</v>
+        <v>13.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>11.58</v>
+        <v>11.08</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.34</v>
+        <v>6.46</v>
       </c>
       <c r="DO6" t="n">
         <v>0</v>
@@ -3271,28 +3271,28 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>44.16</v>
+        <v>45.69</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT6" t="n">
-        <v>8.42</v>
+        <v>9.15</v>
       </c>
       <c r="DU6" t="n">
-        <v>5.83</v>
+        <v>6.46</v>
       </c>
       <c r="DV6" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DW6" t="n">
-        <v>11.5</v>
+        <v>11.46</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -3302,94 +3302,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>63.83</v>
+        <v>62.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="L7" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25.17</v>
+        <v>23.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="P7" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.17</v>
+        <v>12.86</v>
       </c>
       <c r="R7" t="n">
-        <v>7.33</v>
+        <v>8.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="T7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.67</v>
+        <v>44.29</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="Z7" t="n">
         <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>10.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3473,70 +3473,70 @@
         <v>2.29</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.69</v>
+        <v>10.29</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.62</v>
+        <v>3.29</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC7" t="n">
         <v>4.13</v>
@@ -3551,16 +3551,16 @@
         <v>2.89</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK7" t="n">
         <v>1.61</v>
@@ -3569,19 +3569,19 @@
         <v>2.17</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CR7" t="n">
         <v>1.82</v>
@@ -3605,85 +3605,85 @@
         <v>1.39</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="DD7" t="n">
-        <v>76.06999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="DI7" t="n">
-        <v>31.7</v>
+        <v>30.57</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="DL7" t="n">
-        <v>10.84</v>
+        <v>10.78</v>
       </c>
       <c r="DM7" t="n">
-        <v>10.77</v>
+        <v>10.78</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.31</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>47.93</v>
+        <v>47.08</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="DT7" t="n">
-        <v>8.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="DW7" t="n">
-        <v>14.69</v>
+        <v>14.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3705,82 +3705,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>109.6</v>
+        <v>108.83</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>39.8</v>
+        <v>42.17</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>4.83</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>63</v>
+        <v>63.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.6</v>
+        <v>16.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3864,70 +3864,70 @@
         <v>2.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BO8" t="n">
         <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.17</v>
+        <v>3.77</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="CC8" t="n">
         <v>3.11</v>
@@ -3939,40 +3939,40 @@
         <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CH8" t="n">
         <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="CR8" t="n">
         <v>1.76</v>
@@ -3996,85 +3996,85 @@
         <v>1.43</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="DA8" t="n">
         <v>0.08</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="DD8" t="n">
-        <v>89.25</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="DI8" t="n">
-        <v>31.34</v>
+        <v>33.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="DL8" t="n">
-        <v>11.17</v>
+        <v>10.85</v>
       </c>
       <c r="DM8" t="n">
-        <v>8.75</v>
+        <v>8.15</v>
       </c>
       <c r="DN8" t="n">
-        <v>6.17</v>
+        <v>5.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>54.08</v>
+        <v>54.92</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DT8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.83</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.16</v>
+        <v>4.54</v>
       </c>
       <c r="DW8" t="n">
-        <v>15.75</v>
+        <v>15.54</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -4084,94 +4084,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>95.14</v>
+        <v>94.88</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="K9" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>30.43</v>
+        <v>31.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>54.57</v>
+        <v>54</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.29</v>
+        <v>13.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.57</v>
+        <v>17.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4255,70 +4255,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT9" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU9" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="CC9" t="n">
         <v>3.33</v>
@@ -4330,7 +4330,7 @@
         <v>1.48</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CG9" t="n">
         <v>2.45</v>
@@ -4339,10 +4339,10 @@
         <v>1.31</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="CK9" t="n">
         <v>1.65</v>
@@ -4357,19 +4357,19 @@
         <v>1.67</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CT9" t="n">
         <v>1.89</v>
@@ -4387,85 +4387,85 @@
         <v>1.45</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DD9" t="n">
-        <v>91</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="DI9" t="n">
-        <v>30.69</v>
+        <v>31.07</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.77</v>
+        <v>13.64</v>
       </c>
       <c r="DM9" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DN9" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>51.85</v>
+        <v>51.72</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.08</v>
+        <v>12.36</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DV9" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="DW9" t="n">
-        <v>17.54</v>
+        <v>17.43</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="DY9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="10">
@@ -4862,13 +4862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -4955,136 +4955,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AI11" t="n">
-        <v>61.83</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AQ11" t="n">
         <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>5.43</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>40.17</v>
+        <v>41.57</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>13.33</v>
+        <v>15.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.83</v>
+        <v>7.69</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT11" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY11" t="n">
         <v>3.17</v>
@@ -5093,16 +5093,16 @@
         <v>3.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="CC11" t="n">
-        <v>7.38</v>
+        <v>7.61</v>
       </c>
       <c r="CD11" t="n">
-        <v>8.92</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="CE11" t="n">
         <v>1.46</v>
@@ -5117,37 +5117,37 @@
         <v>1.32</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL11" t="n">
         <v>2.33</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CT11" t="n">
         <v>1.82</v>
@@ -5165,52 +5165,52 @@
         <v>1.41</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="DA11" t="n">
         <v>0.08</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DD11" t="n">
-        <v>61.66</v>
+        <v>63.08</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DI11" t="n">
-        <v>15.84</v>
+        <v>15.77</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DL11" t="n">
-        <v>9.92</v>
+        <v>9.84</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.5</v>
+        <v>7.77</v>
       </c>
       <c r="DN11" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="DO11" t="n">
         <v>0.08</v>
@@ -5222,25 +5222,25 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>42.92</v>
+        <v>43.46</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DU11" t="n">
         <v>5</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="DW11" t="n">
-        <v>14.08</v>
+        <v>15</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="DY11" t="n">
         <v>2.08</v>
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6128,49 +6128,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AI14" t="n">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.33</v>
+        <v>21.71</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.5</v>
+        <v>14.29</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6182,82 +6182,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>44.5</v>
+        <v>43.14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.17</v>
+        <v>10.29</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.83</v>
+        <v>7.43</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.67</v>
+        <v>12.14</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>3.01</v>
@@ -6266,55 +6266,55 @@
         <v>3.12</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.35</v>
+        <v>5.67</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.84</v>
+        <v>6.51</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CL14" t="n">
         <v>2.45</v>
       </c>
       <c r="CM14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CR14" t="n">
         <v>1.74</v>
@@ -6338,85 +6338,85 @@
         <v>1.41</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="DD14" t="n">
-        <v>69.92</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.16</v>
+        <v>-0.22</v>
       </c>
       <c r="DI14" t="n">
-        <v>20.07</v>
+        <v>19.92</v>
       </c>
       <c r="DJ14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DK14" t="n">
         <v>1</v>
       </c>
-      <c r="DK14" t="n">
-        <v>1.15</v>
-      </c>
       <c r="DL14" t="n">
-        <v>9.92</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DM14" t="n">
-        <v>11.39</v>
+        <v>11.08</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.85</v>
+        <v>4.43</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>46.15</v>
+        <v>45.36</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>10.08</v>
+        <v>10.58</v>
       </c>
       <c r="DU14" t="n">
-        <v>7.15</v>
+        <v>7.43</v>
       </c>
       <c r="DV14" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="DW14" t="n">
-        <v>10.69</v>
+        <v>10.14</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="15">
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6516,139 +6516,139 @@
         <v>2.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>92.14</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BP15" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>1.91</v>
@@ -6657,16 +6657,16 @@
         <v>1.99</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
@@ -6681,22 +6681,22 @@
         <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL15" t="n">
         <v>2.25</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO15" t="n">
         <v>1.33</v>
@@ -6705,22 +6705,22 @@
         <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CS15" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CU15" t="n">
         <v>1.87</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CW15" t="n">
         <v>1.86</v>
@@ -6735,79 +6735,79 @@
         <v>3.68</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DD15" t="n">
-        <v>93.15000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DG15" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>35.23</v>
+        <v>34.43</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DL15" t="n">
-        <v>11.08</v>
+        <v>11.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>8.85</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DN15" t="n">
-        <v>5.15</v>
+        <v>5.64</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>54.54</v>
+        <v>54.14</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>13.54</v>
+        <v>13.07</v>
       </c>
       <c r="DU15" t="n">
-        <v>8.77</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DV15" t="n">
-        <v>4.77</v>
+        <v>4.72</v>
       </c>
       <c r="DW15" t="n">
         <v>14.07</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="16">
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -6829,82 +6829,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G16" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M16" t="n">
-        <v>24.33</v>
+        <v>29</v>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="P16" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.33</v>
+        <v>7.29</v>
       </c>
       <c r="R16" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.67</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>15.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.83</v>
+        <v>10.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AF16" t="n">
         <v>0.29</v>
@@ -6988,70 +6988,70 @@
         <v>2.43</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="BR16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
         <v>2.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CA16" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CC16" t="n">
         <v>4.03</v>
@@ -7060,58 +7060,58 @@
         <v>4.98</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CJ16" t="n">
         <v>2.07</v>
       </c>
-      <c r="CH16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>2.09</v>
-      </c>
       <c r="CK16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CO16" t="n">
         <v>1.33</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CT16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CU16" t="n">
         <v>1.92</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW16" t="n">
         <v>1.8</v>
@@ -7126,79 +7126,79 @@
         <v>4.53</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="DD16" t="n">
-        <v>87.31</v>
+        <v>88.22</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DI16" t="n">
-        <v>27.38</v>
+        <v>29.5</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DL16" t="n">
-        <v>12.23</v>
+        <v>11.78</v>
       </c>
       <c r="DM16" t="n">
-        <v>8.539999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DN16" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>46.46</v>
+        <v>46.78</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT16" t="n">
-        <v>12.46</v>
+        <v>13</v>
       </c>
       <c r="DU16" t="n">
-        <v>8.23</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="DW16" t="n">
-        <v>16.85</v>
+        <v>17.5</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="DY16" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="17">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -8393,49 +8393,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>97.17</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J20" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K20" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="L20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M20" t="n">
-        <v>51.5</v>
+        <v>49.43</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.83</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8447,28 +8447,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>47.83</v>
+        <v>48.86</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.5</v>
+        <v>14.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>11</v>
+        <v>10.43</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AC20" t="n">
-        <v>16.67</v>
+        <v>17.29</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8552,70 +8552,70 @@
         <v>2.17</v>
       </c>
       <c r="BG20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="BI20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="BR20" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS20" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BT20" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV20" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CC20" t="n">
         <v>3.14</v>
@@ -8627,7 +8627,7 @@
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CG20" t="n">
         <v>2.47</v>
@@ -8645,28 +8645,28 @@
         <v>1.66</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN20" t="n">
         <v>1.69</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CT20" t="n">
         <v>1.77</v>
@@ -8681,55 +8681,55 @@
         <v>1.82</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ20" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="DD20" t="n">
-        <v>88.34</v>
+        <v>89.31</v>
       </c>
       <c r="DE20" t="n">
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DG20" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DI20" t="n">
-        <v>39.25</v>
+        <v>39.08</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DK20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DL20" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>10.25</v>
+        <v>10.08</v>
       </c>
       <c r="DN20" t="n">
-        <v>7.66</v>
+        <v>7.84</v>
       </c>
       <c r="DO20" t="n">
         <v>0</v>
@@ -8741,28 +8741,28 @@
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>47.58</v>
+        <v>48.15</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>11.75</v>
+        <v>11.77</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DV20" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="DW20" t="n">
-        <v>16</v>
+        <v>16.39</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="21">
@@ -8772,13 +8772,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0.17</v>
@@ -8865,49 +8865,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AI21" t="n">
-        <v>94.5</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN21" t="n">
-        <v>26.5</v>
+        <v>28.14</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.5</v>
+        <v>10.14</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -8919,73 +8919,73 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>46.17</v>
+        <v>45.57</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.67</v>
+        <v>12.14</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.5</v>
+        <v>7.86</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="BD21" t="n">
-        <v>13.67</v>
+        <v>13.86</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BH21" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BP21" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BQ21" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT21" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU21" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BY21" t="n">
         <v>1.98</v>
@@ -9009,55 +9009,55 @@
         <v>3.31</v>
       </c>
       <c r="CC21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CF21" t="n">
         <v>2.86</v>
       </c>
-      <c r="CD21" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF21" t="n">
-        <v>2.83</v>
-      </c>
       <c r="CG21" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="CR21" t="n">
         <v>1.76</v>
       </c>
       <c r="CS21" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CT21" t="n">
         <v>1.83</v>
@@ -9078,49 +9078,49 @@
         <v>2.32</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="DA21" t="n">
         <v>0.08</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD21" t="n">
-        <v>91.42</v>
+        <v>91.61</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.58</v>
+        <v>5.53</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DI21" t="n">
-        <v>29.67</v>
+        <v>30.3</v>
       </c>
       <c r="DJ21" t="n">
         <v>1.08</v>
       </c>
       <c r="DK21" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="DL21" t="n">
-        <v>11.58</v>
+        <v>12.15</v>
       </c>
       <c r="DM21" t="n">
-        <v>8.33</v>
+        <v>8.77</v>
       </c>
       <c r="DN21" t="n">
-        <v>6.58</v>
+        <v>6.77</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>49.08</v>
+        <v>48.54</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DT21" t="n">
-        <v>13.75</v>
+        <v>13.38</v>
       </c>
       <c r="DU21" t="n">
-        <v>8.58</v>
+        <v>8.23</v>
       </c>
       <c r="DV21" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.17</v>
+        <v>15.16</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1835,124 +1835,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.17</v>
+        <v>79.86</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>32.5</v>
+        <v>31.86</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.33</v>
+        <v>11.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.17</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BF3" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.33</v>
+        <v>7.62</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT3" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY3" t="n">
         <v>1.74</v>
@@ -1973,43 +1973,43 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB3" t="n">
         <v>3.31</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
         <v>1.59</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CN3" t="n">
         <v>1.46</v>
@@ -2018,10 +2018,10 @@
         <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CR3" t="n">
         <v>1.76</v>
@@ -2030,7 +2030,7 @@
         <v>2.08</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CU3" t="n">
         <v>1.93</v>
@@ -2042,85 +2042,85 @@
         <v>1.81</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DD3" t="n">
-        <v>90.34</v>
+        <v>88</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="DH3" t="n">
         <v>0.08</v>
       </c>
       <c r="DI3" t="n">
-        <v>52</v>
+        <v>50.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="DL3" t="n">
         <v>14.16</v>
       </c>
       <c r="DM3" t="n">
-        <v>12.33</v>
+        <v>11.77</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.42</v>
+        <v>7.54</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>56.75</v>
+        <v>56.69</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.58</v>
+        <v>14.31</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.92</v>
+        <v>9.84</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="DW3" t="n">
-        <v>17.08</v>
+        <v>17.47</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="DY3" t="n">
         <v>3</v>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2617,136 +2617,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>84</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.83</v>
+        <v>30.71</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.33</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>10.14</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.5</v>
+        <v>55.14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.83</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.5</v>
+        <v>14.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="BG5" t="n">
         <v>2.92</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY5" t="n">
         <v>1.13</v>
@@ -2758,10 +2758,10 @@
         <v>3.28</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.09</v>
+        <v>4.02</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CD5" t="n">
         <v>2.42</v>
@@ -2770,40 +2770,40 @@
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.4</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK5" t="n">
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR5" t="n">
         <v>1.89</v>
@@ -2823,85 +2823,85 @@
         <v>1.29</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DD5" t="n">
-        <v>84</v>
+        <v>83.77</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.84</v>
+        <v>4.61</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DI5" t="n">
-        <v>30.58</v>
+        <v>30.07</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="DL5" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DM5" t="n">
-        <v>11.16</v>
+        <v>10.62</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.42</v>
+        <v>9.07</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>56.66</v>
+        <v>55.92</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT5" t="n">
-        <v>15.92</v>
+        <v>15.54</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.67</v>
+        <v>9.23</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="DW5" t="n">
         <v>16.92</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3019,7 @@
         <v>2.43</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.14</v>
@@ -3085,7 +3085,7 @@
         <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
       <c r="BI6" t="n">
         <v>2.38</v>
@@ -3151,7 +3151,7 @@
         <v>7.75</v>
       </c>
       <c r="CD6" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="CE6" t="n">
         <v>1.46</v>
@@ -3238,7 +3238,7 @@
         <v>2.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="DH6" t="n">
         <v>0.16</v>
@@ -3476,7 +3476,7 @@
         <v>3.29</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.29</v>
+        <v>10.21</v>
       </c>
       <c r="BI7" t="n">
         <v>3.29</v>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3705,82 +3705,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="H8" t="n">
-        <v>108.83</v>
+        <v>105.57</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="K8" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>42.17</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="P8" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>63.33</v>
+        <v>64</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.33</v>
+        <v>16.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>16.86</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3864,70 +3864,70 @@
         <v>2.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.85</v>
+        <v>9.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="BR8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CC8" t="n">
         <v>3.11</v>
@@ -3936,10 +3936,10 @@
         <v>3.6</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG8" t="n">
         <v>2.5</v>
@@ -3948,31 +3948,31 @@
         <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN8" t="n">
         <v>1.58</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CR8" t="n">
         <v>1.76</v>
@@ -3993,88 +3993,88 @@
         <v>1.92</v>
       </c>
       <c r="CX8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="DX8" t="n">
         <v>1.43</v>
       </c>
-      <c r="CY8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>90.45999999999999</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>5</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>13</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DY8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="9">
@@ -4318,7 +4318,7 @@
         <v>3.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CC9" t="n">
         <v>3.33</v>
@@ -4384,13 +4384,13 @@
         <v>1.84</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="DA9" t="n">
         <v>0.07000000000000001</v>
@@ -4475,94 +4475,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="M10" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.71</v>
       </c>
       <c r="P10" t="n">
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="R10" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.86</v>
+        <v>52.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.14</v>
+        <v>13.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.140000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.57</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4646,67 +4646,67 @@
         <v>3.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.69</v>
+        <v>7.79</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CB10" t="n">
         <v>3.19</v>
@@ -4718,43 +4718,43 @@
         <v>4.24</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN10" t="n">
         <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="CR10" t="n">
         <v>1.68</v>
@@ -4771,85 +4771,85 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DD10" t="n">
-        <v>86.08</v>
+        <v>85.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="DI10" t="n">
-        <v>37.46</v>
+        <v>37.71</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>11.46</v>
+        <v>10.93</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>51.77</v>
+        <v>51.86</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DT10" t="n">
-        <v>13.08</v>
+        <v>13.22</v>
       </c>
       <c r="DU10" t="n">
-        <v>8.92</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="DW10" t="n">
-        <v>16.77</v>
+        <v>16.57</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DY10" t="n">
         <v>3</v>
@@ -5096,13 +5096,13 @@
         <v>3.64</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC11" t="n">
         <v>7.61</v>
       </c>
       <c r="CD11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="CE11" t="n">
         <v>1.46</v>
@@ -5165,10 +5165,10 @@
         <v>1.41</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="DA11" t="n">
         <v>0.08</v>
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5346,136 +5346,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>88.14</v>
+        <v>87.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.29</v>
+        <v>29.88</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.57</v>
+        <v>11.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.43</v>
+        <v>6.25</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49</v>
+        <v>49.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.43</v>
+        <v>11.25</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.86</v>
+        <v>16</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.38</v>
+        <v>7.93</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.69</v>
+        <v>3.36</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY12" t="n">
         <v>1.97</v>
@@ -5484,40 +5484,40 @@
         <v>2.1</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.51</v>
+        <v>4.75</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.27</v>
+        <v>5.53</v>
       </c>
       <c r="CE12" t="n">
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CM12" t="n">
         <v>1.93</v>
@@ -5529,10 +5529,10 @@
         <v>1.3</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="CR12" t="n">
         <v>1.72</v>
@@ -5544,97 +5544,97 @@
         <v>1.86</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CV12" t="n">
         <v>1.86</v>
       </c>
       <c r="CW12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DC12" t="n">
         <v>1.79</v>
       </c>
-      <c r="CX12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>2</v>
-      </c>
       <c r="DD12" t="n">
-        <v>99.69</v>
+        <v>98.64</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>32.46</v>
+        <v>32.07</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DK12" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="DL12" t="n">
         <v>10.92</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.23</v>
+        <v>11.07</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.54</v>
+        <v>6</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>53.38</v>
+        <v>53.21</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>12.23</v>
+        <v>12.07</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>17.93</v>
+        <v>17.36</v>
       </c>
       <c r="DX12" t="n">
         <v>1.28</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13">
@@ -5644,94 +5644,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="n">
-        <v>103</v>
+        <v>100.33</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M13" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>10.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.8</v>
+        <v>9.67</v>
       </c>
       <c r="R13" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>59.6</v>
+        <v>57</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.6</v>
+        <v>20.17</v>
       </c>
       <c r="AA13" t="n">
         <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5815,49 +5815,49 @@
         <v>3.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="CA13" t="n">
         <v>3.12</v>
@@ -5887,28 +5887,28 @@
         <v>2.67</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK13" t="n">
         <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
@@ -5917,13 +5917,13 @@
         <v>1.62</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CR13" t="n">
         <v>1.91</v>
@@ -5932,13 +5932,13 @@
         <v>1.92</v>
       </c>
       <c r="CT13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CU13" t="n">
         <v>1.95</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW13" t="n">
         <v>1.76</v>
@@ -5950,82 +5950,82 @@
         <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="DA13" t="n">
         <v>0.08</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DD13" t="n">
-        <v>88.17</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="DG13" t="n">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DI13" t="n">
-        <v>32</v>
+        <v>32.38</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="DL13" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
       <c r="DM13" t="n">
-        <v>10.42</v>
+        <v>9.92</v>
       </c>
       <c r="DN13" t="n">
-        <v>4.91</v>
+        <v>5.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>53</v>
+        <v>52.31</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT13" t="n">
-        <v>15</v>
+        <v>15.23</v>
       </c>
       <c r="DU13" t="n">
-        <v>10</v>
+        <v>10.31</v>
       </c>
       <c r="DV13" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="DW13" t="n">
-        <v>15.08</v>
+        <v>15.54</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="14">
@@ -6275,7 +6275,7 @@
         <v>5.67</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.51</v>
+        <v>6.31</v>
       </c>
       <c r="CE14" t="n">
         <v>1.46</v>
@@ -6335,13 +6335,13 @@
         <v>1.83</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>3.37</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CC15" t="n">
         <v>3.14</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
@@ -6714,13 +6714,13 @@
         <v>1.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CU15" t="n">
         <v>1.87</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
         <v>1.86</v>
@@ -6732,7 +6732,7 @@
         <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="DA15" t="n">
         <v>0.14</v>
@@ -7045,13 +7045,13 @@
         <v>2.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="CA16" t="n">
         <v>3.01</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC16" t="n">
         <v>4.03</v>
@@ -7105,25 +7105,25 @@
         <v>2.07</v>
       </c>
       <c r="CT16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CU16" t="n">
         <v>1.92</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW16" t="n">
         <v>1.8</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="DA16" t="n">
         <v>0.14</v>
@@ -7208,94 +7208,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>84.14</v>
+        <v>91.12</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K17" t="n">
-        <v>5.14</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>27.57</v>
+        <v>34.62</v>
       </c>
       <c r="N17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O17" t="n">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>11.14</v>
+        <v>11.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="R17" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51.14</v>
+        <v>51.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.14</v>
+        <v>18.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7379,49 +7379,49 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.23</v>
+        <v>10.14</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7430,19 +7430,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC17" t="n">
         <v>6.3</v>
@@ -7451,145 +7451,145 @@
         <v>6.65</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN17" t="n">
         <v>1.69</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CT17" t="n">
         <v>1.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CV17" t="n">
         <v>1.91</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="DD17" t="n">
-        <v>80.38</v>
+        <v>84.64</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>32.31</v>
+        <v>36</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DK17" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>10.3</v>
+        <v>10.35</v>
       </c>
       <c r="DM17" t="n">
-        <v>8.609999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DN17" t="n">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>47.77</v>
+        <v>48.07</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT17" t="n">
-        <v>10.31</v>
+        <v>10.35</v>
       </c>
       <c r="DU17" t="n">
-        <v>7.31</v>
+        <v>7.21</v>
       </c>
       <c r="DV17" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DW17" t="n">
-        <v>17</v>
+        <v>16.64</v>
       </c>
       <c r="DX17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="18">
@@ -7599,94 +7599,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F18" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>78.56999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>6.14</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="M18" t="n">
-        <v>27</v>
+        <v>31.25</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>10.86</v>
+        <v>10.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.86</v>
+        <v>7.38</v>
       </c>
       <c r="R18" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.29</v>
+        <v>50.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.71</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.71</v>
+        <v>10.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.86</v>
+        <v>18.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7770,70 +7770,70 @@
         <v>3.17</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.15</v>
+        <v>9.57</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.92</v>
+        <v>3.57</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.54</v>
+        <v>3.21</v>
       </c>
       <c r="BR18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="CC18" t="n">
         <v>2.7</v>
@@ -7845,16 +7845,16 @@
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
         <v>2.01</v>
@@ -7863,22 +7863,22 @@
         <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="CR18" t="n">
         <v>1.8</v>
@@ -7890,97 +7890,97 @@
         <v>1.85</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CV18" t="n">
         <v>1.87</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="DD18" t="n">
-        <v>74.69</v>
+        <v>74.36</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="DG18" t="n">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>24.92</v>
+        <v>27.5</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.38</v>
+        <v>10.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>7.16</v>
+        <v>7.43</v>
       </c>
       <c r="DN18" t="n">
-        <v>6.46</v>
+        <v>6.57</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>45.62</v>
+        <v>45.86</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT18" t="n">
-        <v>16</v>
+        <v>15.93</v>
       </c>
       <c r="DU18" t="n">
-        <v>10.77</v>
+        <v>10.78</v>
       </c>
       <c r="DV18" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="DW18" t="n">
-        <v>15.54</v>
+        <v>16.07</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="19">
@@ -7990,13 +7990,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.43</v>
@@ -8080,118 +8080,118 @@
         <v>2.71</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.33</v>
+        <v>83.14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.33</v>
+        <v>36.71</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.83</v>
+        <v>8.43</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.67</v>
+        <v>12.43</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.67</v>
+        <v>44.29</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.67</v>
+        <v>12.86</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.46</v>
+        <v>10.36</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.31</v>
+        <v>5.14</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8200,19 +8200,19 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV19" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW19" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX19" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY19" t="n">
         <v>1.9</v>
@@ -8221,43 +8221,43 @@
         <v>1.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.66</v>
+        <v>3.46</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK19" t="n">
         <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN19" t="n">
         <v>1.74</v>
@@ -8266,16 +8266,16 @@
         <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="CR19" t="n">
         <v>1.9</v>
       </c>
       <c r="CS19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CT19" t="n">
         <v>1.84</v>
@@ -8287,88 +8287,88 @@
         <v>1.88</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX19" t="n">
         <v>1.35</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CZ19" t="n">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="DD19" t="n">
-        <v>90.84</v>
+        <v>91.92</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
         <v>3.07</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.54</v>
+        <v>5.22</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DI19" t="n">
-        <v>37.69</v>
+        <v>39.07</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DK19" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DL19" t="n">
-        <v>9.15</v>
+        <v>8.93</v>
       </c>
       <c r="DM19" t="n">
-        <v>8.23</v>
+        <v>8.43</v>
       </c>
       <c r="DN19" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>52.31</v>
+        <v>52</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>14.15</v>
+        <v>13.64</v>
       </c>
       <c r="DU19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DV19" t="n">
-        <v>5.61</v>
+        <v>5.36</v>
       </c>
       <c r="DW19" t="n">
-        <v>11.61</v>
+        <v>11.78</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="DY19" t="n">
         <v>3.07</v>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8474,19 +8474,19 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="n">
         <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.5</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL20" t="n">
         <v>3</v>
@@ -8495,115 +8495,115 @@
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>27</v>
+        <v>27.14</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP20" t="n">
         <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>47.33</v>
+        <v>45.14</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>8.57</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BD20" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.69</v>
+        <v>8.43</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="BR20" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS20" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT20" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU20" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
         <v>1.85</v>
@@ -8612,25 +8612,25 @@
         <v>2.69</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
@@ -8654,13 +8654,13 @@
         <v>1.69</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CR20" t="n">
         <v>1.79</v>
@@ -8684,85 +8684,85 @@
         <v>1.42</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CZ20" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="DA20" t="n">
         <v>0</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DD20" t="n">
-        <v>89.31</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DI20" t="n">
-        <v>39.08</v>
+        <v>38.29</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DK20" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DL20" t="n">
-        <v>10.16</v>
+        <v>10.5</v>
       </c>
       <c r="DM20" t="n">
-        <v>10.08</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DN20" t="n">
-        <v>7.84</v>
+        <v>7.92</v>
       </c>
       <c r="DO20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DQ20" t="n">
         <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>48.15</v>
+        <v>47</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>11.77</v>
+        <v>11.36</v>
       </c>
       <c r="DU20" t="n">
-        <v>8.619999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DV20" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="DW20" t="n">
-        <v>16.39</v>
+        <v>16.29</v>
       </c>
       <c r="DX20" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="DY20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1351,61 +1351,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="H2" t="n">
-        <v>86.67</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="K2" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>41.5</v>
+        <v>40.71</v>
       </c>
       <c r="N2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="P2" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.17</v>
+        <v>14.43</v>
       </c>
       <c r="R2" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1417,25 +1417,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.17</v>
+        <v>48.86</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.67</v>
+        <v>18.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -1522,70 +1522,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC2" t="n">
         <v>5.57</v>
@@ -1594,13 +1594,13 @@
         <v>6.47</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CH2" t="n">
         <v>1.3</v>
@@ -1612,25 +1612,25 @@
         <v>2.17</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN2" t="n">
         <v>1.68</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="CR2" t="n">
         <v>1.66</v>
@@ -1654,52 +1654,52 @@
         <v>1.45</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DD2" t="n">
-        <v>76.23</v>
+        <v>77.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DI2" t="n">
-        <v>31.46</v>
+        <v>31.78</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>11.15</v>
+        <v>11.36</v>
       </c>
       <c r="DM2" t="n">
-        <v>11.92</v>
+        <v>12.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>7.69</v>
+        <v>7.42</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
@@ -1711,28 +1711,28 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>45.77</v>
+        <v>45.86</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="DU2" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="DW2" t="n">
-        <v>18.23</v>
+        <v>18.14</v>
       </c>
       <c r="DX2" t="n">
         <v>1.1</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1754,82 +1754,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="H3" t="n">
-        <v>97.5</v>
+        <v>96.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>71.5</v>
+        <v>66.14</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>13.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60.33</v>
+        <v>59.57</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.67</v>
+        <v>18.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.67</v>
+        <v>18.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="AR3" t="n">
         <v>11.29</v>
@@ -1913,46 +1913,46 @@
         <v>3.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,19 +1964,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY3" t="n">
         <v>1.74</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CA3" t="n">
         <v>3.3</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC3" t="n">
         <v>2.94</v>
@@ -1985,43 +1985,43 @@
         <v>3.27</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI3" t="n">
         <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CR3" t="n">
         <v>1.76</v>
@@ -2030,13 +2030,13 @@
         <v>2.08</v>
       </c>
       <c r="CT3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CU3" t="n">
         <v>1.93</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW3" t="n">
         <v>1.81</v>
@@ -2054,76 +2054,76 @@
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DD3" t="n">
         <v>88</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>50.16</v>
+        <v>49</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DK3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DL3" t="n">
-        <v>14.16</v>
+        <v>13.93</v>
       </c>
       <c r="DM3" t="n">
-        <v>11.77</v>
+        <v>11.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.54</v>
+        <v>7.43</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>56.69</v>
+        <v>56.57</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.31</v>
+        <v>14.43</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.84</v>
+        <v>9.92</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>17.47</v>
+        <v>17.79</v>
       </c>
       <c r="DX3" t="n">
         <v>1.58</v>
       </c>
       <c r="DY3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="4">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2226,136 +2226,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.67</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN4" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BL4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BR4" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>1.83</v>
@@ -2364,25 +2364,25 @@
         <v>1.87</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CB4" t="n">
         <v>3.21</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CH4" t="n">
         <v>1.28</v>
@@ -2391,28 +2391,28 @@
         <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO4" t="n">
         <v>1.46</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="CR4" t="n">
         <v>1.73</v>
@@ -2421,67 +2421,67 @@
         <v>2.13</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CU4" t="n">
         <v>1.84</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW4" t="n">
         <v>1.88</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CY4" t="n">
         <v>2.42</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD4" t="n">
-        <v>99.08</v>
+        <v>99.86</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.84</v>
+        <v>4.71</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DI4" t="n">
-        <v>36.31</v>
+        <v>36.57</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DL4" t="n">
-        <v>11.46</v>
+        <v>11.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>10.92</v>
+        <v>10.78</v>
       </c>
       <c r="DN4" t="n">
-        <v>6.85</v>
+        <v>7.07</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
@@ -2493,28 +2493,28 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>52.77</v>
+        <v>52.21</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.54</v>
+        <v>12.36</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DV4" t="n">
         <v>3.92</v>
       </c>
       <c r="DW4" t="n">
-        <v>16.46</v>
+        <v>16.93</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DY4" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -2524,94 +2524,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>84</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>29.33</v>
+        <v>36.29</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O5" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.83</v>
+        <v>58.14</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.33</v>
+        <v>19.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>11.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.83</v>
+        <v>7.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.33</v>
+        <v>19.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2695,70 +2695,70 @@
         <v>3.43</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BZ5" t="n">
         <v>1.41</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="CC5" t="n">
         <v>2.08</v>
@@ -2767,19 +2767,19 @@
         <v>2.42</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.91</v>
@@ -2788,22 +2788,22 @@
         <v>1.62</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM5" t="n">
         <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="CR5" t="n">
         <v>1.89</v>
@@ -2813,11 +2813,11 @@
       </c>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CX5" t="n">
         <v>1.29</v>
@@ -2829,79 +2829,79 @@
         <v>3.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DD5" t="n">
-        <v>83.77</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.61</v>
+        <v>4.71</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DI5" t="n">
-        <v>30.07</v>
+        <v>33.5</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.62</v>
+        <v>10.07</v>
       </c>
       <c r="DN5" t="n">
-        <v>9.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>55.92</v>
+        <v>56.64</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>15.54</v>
+        <v>16.14</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.23</v>
+        <v>9.92</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.31</v>
+        <v>6.21</v>
       </c>
       <c r="DW5" t="n">
-        <v>16.92</v>
+        <v>17</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="6">
@@ -2911,61 +2911,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="H6" t="n">
-        <v>86.17</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="K6" t="n">
-        <v>3.83</v>
+        <v>4.43</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>22.5</v>
+        <v>25.43</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="P6" t="n">
-        <v>14.17</v>
+        <v>14.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.83</v>
+        <v>9.43</v>
       </c>
       <c r="R6" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="S6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -2977,28 +2977,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.5</v>
+        <v>52.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.67</v>
+        <v>11.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.33</v>
+        <v>7.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.67</v>
+        <v>11.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3082,70 +3082,70 @@
         <v>2.29</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.97</v>
+        <v>3.68</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CC6" t="n">
         <v>7.75</v>
@@ -3157,7 +3157,7 @@
         <v>1.46</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG6" t="n">
         <v>2.52</v>
@@ -3169,16 +3169,16 @@
         <v>1.6</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
         <v>1.59</v>
@@ -3190,7 +3190,7 @@
         <v>2.34</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="CR6" t="n">
         <v>1.58</v>
@@ -3214,85 +3214,85 @@
         <v>1.46</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>74.84999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="DV6" t="n">
         <v>2.92</v>
       </c>
-      <c r="DG6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>2.69</v>
-      </c>
       <c r="DW6" t="n">
-        <v>11.46</v>
+        <v>11.78</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="7">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3395,136 +3395,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>86.56999999999999</v>
+        <v>82.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>37.29</v>
+        <v>34.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.71</v>
+        <v>10.62</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>11.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49.86</v>
+        <v>47.88</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.71</v>
+        <v>4.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.86</v>
+        <v>17.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.21</v>
+        <v>10.07</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY7" t="n">
         <v>2.61</v>
@@ -3533,34 +3533,34 @@
         <v>2.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.13</v>
+        <v>4.7</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.49</v>
+        <v>5.72</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
         <v>1.61</v>
@@ -3569,19 +3569,19 @@
         <v>2.17</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="CR7" t="n">
         <v>1.82</v>
@@ -3593,13 +3593,13 @@
         <v>1.82</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CV7" t="n">
         <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CX7" t="n">
         <v>1.39</v>
@@ -3614,76 +3614,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DD7" t="n">
-        <v>74.5</v>
+        <v>73.27</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DI7" t="n">
-        <v>30.57</v>
+        <v>29.67</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DL7" t="n">
-        <v>10.78</v>
+        <v>10.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.720000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>47.08</v>
+        <v>46.2</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DT7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DU7" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.78</v>
+        <v>3.53</v>
       </c>
       <c r="DW7" t="n">
-        <v>14.22</v>
+        <v>14.27</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4568,136 +4568,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.17</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.83</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>5.71</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>50.5</v>
+        <v>50.86</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.67</v>
+        <v>14.86</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.79</v>
+        <v>8.07</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY10" t="n">
         <v>2.71</v>
@@ -4706,55 +4706,55 @@
         <v>2.72</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CG10" t="n">
         <v>2.36</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI10" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK10" t="n">
         <v>1.77</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
         <v>1.45</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="CR10" t="n">
         <v>1.68</v>
@@ -4771,85 +4771,85 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DB10" t="n">
         <v>2.07</v>
       </c>
       <c r="DC10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DD10" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DI10" t="n">
-        <v>37.71</v>
+        <v>38.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DK10" t="n">
         <v>1.93</v>
       </c>
       <c r="DL10" t="n">
-        <v>9.5</v>
+        <v>9.93</v>
       </c>
       <c r="DM10" t="n">
-        <v>10.93</v>
+        <v>11.13</v>
       </c>
       <c r="DN10" t="n">
-        <v>5.64</v>
+        <v>6.13</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>51.86</v>
+        <v>51.94</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DT10" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="DU10" t="n">
-        <v>9.289999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DV10" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DW10" t="n">
-        <v>16.57</v>
+        <v>16.53</v>
       </c>
       <c r="DX10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DY10" t="n">
         <v>3</v>
@@ -4862,13 +4862,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -4955,136 +4955,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>64.43000000000001</v>
+        <v>61.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>13.12</v>
       </c>
       <c r="AO11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM11" t="n">
         <v>0.86</v>
       </c>
-      <c r="AP11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.92</v>
-      </c>
       <c r="BN11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS11" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>3.17</v>
@@ -5093,28 +5093,28 @@
         <v>3.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CC11" t="n">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="CD11" t="n">
-        <v>9.220000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="CE11" t="n">
         <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG11" t="n">
         <v>2.55</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
         <v>1.66</v>
@@ -5126,10 +5126,10 @@
         <v>1.69</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN11" t="n">
         <v>1.63</v>
@@ -5141,7 +5141,7 @@
         <v>2.19</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CR11" t="n">
         <v>1.68</v>
@@ -5162,88 +5162,88 @@
         <v>1.8</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.18</v>
+        <v>4.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DD11" t="n">
-        <v>63.08</v>
+        <v>61.57</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="DI11" t="n">
-        <v>15.77</v>
+        <v>16.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DL11" t="n">
-        <v>9.84</v>
+        <v>10.07</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.77</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DN11" t="n">
-        <v>6.77</v>
+        <v>7.64</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>43.46</v>
+        <v>43.5</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.69</v>
+        <v>8.35</v>
       </c>
       <c r="DU11" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="DW11" t="n">
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="12">
@@ -5427,7 +5427,7 @@
         <v>2.71</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="BI12" t="n">
         <v>2.71</v>
@@ -5644,13 +5644,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5737,127 +5737,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1.14</v>
       </c>
-      <c r="AH13" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>77.56999999999999</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BP13" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BR13" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY13" t="n">
         <v>1.84</v>
@@ -5878,52 +5878,52 @@
         <v>3.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CM13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
         <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.91</v>
@@ -5935,97 +5935,97 @@
         <v>1.8</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CV13" t="n">
         <v>1.93</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CX13" t="n">
         <v>1.36</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DC13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>88.06999999999999</v>
+        <v>87.92</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DF13" t="n">
         <v>3.07</v>
       </c>
       <c r="DG13" t="n">
-        <v>5.77</v>
+        <v>5.71</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>32.38</v>
+        <v>33.07</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DK13" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="DL13" t="n">
-        <v>9.92</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DM13" t="n">
-        <v>9.92</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DN13" t="n">
-        <v>5.15</v>
+        <v>5.36</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>52.31</v>
+        <v>51.86</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT13" t="n">
-        <v>15.23</v>
+        <v>15.28</v>
       </c>
       <c r="DU13" t="n">
-        <v>10.31</v>
+        <v>10.43</v>
       </c>
       <c r="DV13" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="DW13" t="n">
-        <v>15.54</v>
+        <v>15.64</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DY13" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6047,82 +6047,82 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>71.14</v>
+        <v>68.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.57</v>
+        <v>5.12</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>18.14</v>
+        <v>18.38</v>
       </c>
       <c r="N14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="R14" t="n">
-        <v>3.43</v>
+        <v>4.62</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.57</v>
+        <v>47</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6206,70 +6206,70 @@
         <v>3.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.07</v>
+        <v>8.93</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL14" t="n">
         <v>1.07</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="CA14" t="n">
         <v>3.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CC14" t="n">
         <v>5.67</v>
@@ -6281,40 +6281,40 @@
         <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CK14" t="n">
         <v>1.76</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN14" t="n">
         <v>1.59</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.15</v>
+        <v>4.08</v>
       </c>
       <c r="CR14" t="n">
         <v>1.74</v>
@@ -6335,88 +6335,88 @@
         <v>1.83</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CZ14" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="DG14" t="n">
         <v>4.2</v>
       </c>
-      <c r="DA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>4.35</v>
-      </c>
       <c r="DH14" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="DI14" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="DJ14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DK14" t="n">
         <v>0.93</v>
       </c>
-      <c r="DK14" t="n">
-        <v>1</v>
-      </c>
       <c r="DL14" t="n">
-        <v>9.279999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DM14" t="n">
-        <v>11.08</v>
+        <v>10.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>45.36</v>
+        <v>45.2</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>10.58</v>
+        <v>10.73</v>
       </c>
       <c r="DU14" t="n">
-        <v>7.43</v>
+        <v>7.53</v>
       </c>
       <c r="DV14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DY14" t="n">
         <v>3.14</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>3.22</v>
       </c>
     </row>
     <row r="15">
@@ -7208,13 +7208,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7301,127 +7301,127 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AI17" t="n">
-        <v>76</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.33</v>
+        <v>-0.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>37.83</v>
+        <v>35.57</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.33</v>
+        <v>8.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.83</v>
+        <v>42</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.33</v>
+        <v>6.71</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="BD17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BF17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG17" t="n">
         <v>2</v>
       </c>
-      <c r="BG17" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BH17" t="n">
-        <v>10.14</v>
+        <v>10.53</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN17" t="n">
         <v>1.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="BQ17" t="n">
-        <v>2.93</v>
+        <v>3.47</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY17" t="n">
         <v>2.63</v>
@@ -7439,55 +7439,55 @@
         <v>2.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="CC17" t="n">
-        <v>6.3</v>
+        <v>6.06</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.65</v>
+        <v>6.82</v>
       </c>
       <c r="CE17" t="n">
         <v>1.45</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK17" t="n">
         <v>1.64</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="CR17" t="n">
         <v>1.73</v>
@@ -7499,97 +7499,97 @@
         <v>1.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CV17" t="n">
         <v>1.91</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CZ17" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="DD17" t="n">
-        <v>84.64</v>
+        <v>83.73</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="DH17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>36</v>
+        <v>35.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="DK17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>10.35</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DM17" t="n">
-        <v>8.43</v>
+        <v>8.26</v>
       </c>
       <c r="DN17" t="n">
-        <v>6.28</v>
+        <v>6.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>48.07</v>
+        <v>46.93</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT17" t="n">
-        <v>10.35</v>
+        <v>10.13</v>
       </c>
       <c r="DU17" t="n">
-        <v>7.21</v>
+        <v>6.93</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="DW17" t="n">
-        <v>16.64</v>
+        <v>16.27</v>
       </c>
       <c r="DX17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DY17" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="18">
@@ -7599,13 +7599,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.25</v>
@@ -7626,7 +7626,7 @@
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="L18" t="n">
         <v>-0.12</v>
@@ -7671,10 +7671,10 @@
         <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="AB18" t="n">
         <v>5.75</v>
@@ -7683,7 +7683,7 @@
         <v>18.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -7692,136 +7692,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>70.17</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.5</v>
+        <v>27.86</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>40.17</v>
+        <v>42.57</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>15.17</v>
+        <v>14.86</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="BD18" t="n">
-        <v>12.83</v>
+        <v>15.43</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BR18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY18" t="n">
         <v>1.85</v>
@@ -7830,55 +7830,55 @@
         <v>1.76</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB18" t="n">
         <v>3.58</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH18" t="n">
         <v>1.34</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO18" t="n">
         <v>1.36</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CR18" t="n">
         <v>1.8</v>
@@ -7887,100 +7887,100 @@
         <v>2.07</v>
       </c>
       <c r="CT18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CU18" t="n">
         <v>1.91</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CW18" t="n">
         <v>1.81</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CZ18" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DB18" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="DC18" t="n">
         <v>2.07</v>
       </c>
       <c r="DD18" t="n">
-        <v>74.36</v>
+        <v>78</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="DG18" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="DH18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>27.5</v>
+        <v>29.67</v>
       </c>
       <c r="DJ18" t="n">
         <v>1.07</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="DL18" t="n">
-        <v>10.28</v>
+        <v>10.06</v>
       </c>
       <c r="DM18" t="n">
-        <v>7.43</v>
+        <v>7.2</v>
       </c>
       <c r="DN18" t="n">
-        <v>6.57</v>
+        <v>6.4</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>45.86</v>
+        <v>46.6</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>15.93</v>
+        <v>16</v>
       </c>
       <c r="DU18" t="n">
-        <v>10.78</v>
+        <v>10.73</v>
       </c>
       <c r="DV18" t="n">
-        <v>5.14</v>
+        <v>5.26</v>
       </c>
       <c r="DW18" t="n">
-        <v>16.07</v>
+        <v>17.07</v>
       </c>
       <c r="DX18" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DY18" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -7990,94 +7990,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F19" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
-        <v>100.71</v>
+        <v>98</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="K19" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>41.43</v>
+        <v>40.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O19" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>4.88</v>
       </c>
       <c r="S19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>59.71</v>
+        <v>59</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.57</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.71</v>
+        <v>6</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.71</v>
+        <v>12.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF19" t="n">
         <v>0.29</v>
@@ -8161,37 +8161,37 @@
         <v>3.43</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.36</v>
+        <v>10.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.43</v>
+        <v>3.53</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
@@ -8200,31 +8200,31 @@
         <v>100</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC19" t="n">
         <v>3.08</v>
@@ -8233,43 +8233,43 @@
         <v>3.46</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK19" t="n">
         <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM19" t="n">
         <v>2.19</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="CR19" t="n">
         <v>1.9</v>
@@ -8290,85 +8290,85 @@
         <v>1.86</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ19" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DB19" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>91.92</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF19" t="n">
         <v>3.07</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.22</v>
+        <v>5.07</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DI19" t="n">
-        <v>39.07</v>
+        <v>38.73</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DK19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DL19" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DM19" t="n">
-        <v>8.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DN19" t="n">
-        <v>6.21</v>
+        <v>6.54</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>52</v>
+        <v>52.14</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>13.64</v>
+        <v>13.6</v>
       </c>
       <c r="DU19" t="n">
-        <v>8.279999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DV19" t="n">
-        <v>5.36</v>
+        <v>5.07</v>
       </c>
       <c r="DW19" t="n">
-        <v>11.78</v>
+        <v>12.6</v>
       </c>
       <c r="DX19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DY19" t="n">
         <v>3.07</v>
@@ -8772,61 +8772,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.17</v>
+        <v>2.29</v>
       </c>
       <c r="H21" t="n">
-        <v>88.33</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J21" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="K21" t="n">
-        <v>5.33</v>
+        <v>6.29</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>32.83</v>
+        <v>36</v>
       </c>
       <c r="N21" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="P21" t="n">
-        <v>13.5</v>
+        <v>12.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.17</v>
+        <v>6.57</v>
       </c>
       <c r="R21" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -8838,25 +8838,25 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>54.43</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.83</v>
+        <v>14.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.17</v>
+        <v>5.71</v>
       </c>
       <c r="AC21" t="n">
-        <v>16.67</v>
+        <v>17.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -8943,49 +8943,49 @@
         <v>2.43</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.92</v>
+        <v>9.43</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP21" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="BQ21" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU21" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8994,19 +8994,19 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="CC21" t="n">
         <v>3.02</v>
@@ -9018,40 +9018,40 @@
         <v>1.35</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CI21" t="n">
         <v>1.61</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CK21" t="n">
         <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CO21" t="n">
         <v>1.27</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="CR21" t="n">
         <v>1.76</v>
@@ -9063,64 +9063,64 @@
         <v>1.83</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CV21" t="n">
         <v>1.9</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX21" t="n">
         <v>1.41</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DC21" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="DD21" t="n">
-        <v>91.61</v>
+        <v>92.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF21" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DG21" t="n">
-        <v>5.53</v>
+        <v>6</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DI21" t="n">
-        <v>30.3</v>
+        <v>32.07</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DK21" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="DL21" t="n">
-        <v>12.15</v>
+        <v>11.72</v>
       </c>
       <c r="DM21" t="n">
-        <v>8.77</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DN21" t="n">
-        <v>6.77</v>
+        <v>6.93</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>48.54</v>
+        <v>50</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT21" t="n">
-        <v>13.38</v>
+        <v>13.28</v>
       </c>
       <c r="DU21" t="n">
-        <v>8.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DV21" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.16</v>
+        <v>15.86</v>
       </c>
       <c r="DX21" t="n">
         <v>1.43</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -1916,7 +1916,7 @@
         <v>2.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="BI3" t="n">
         <v>2.07</v>
@@ -2241,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.29</v>
+        <v>4.43</v>
       </c>
       <c r="AM4" t="n">
         <v>0.43</v>
@@ -2256,7 +2256,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>9.859999999999999</v>
@@ -2286,19 +2286,19 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.57</v>
+        <v>10.86</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.71</v>
+        <v>3.86</v>
       </c>
       <c r="BD4" t="n">
         <v>16.57</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
@@ -2307,7 +2307,7 @@
         <v>2.07</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.07</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI4" t="n">
         <v>2.07</v>
@@ -2460,7 +2460,7 @@
         <v>2.72</v>
       </c>
       <c r="DG4" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="DH4" t="n">
         <v>0.14</v>
@@ -2475,7 +2475,7 @@
         <v>1.93</v>
       </c>
       <c r="DL4" t="n">
-        <v>11.5</v>
+        <v>11.42</v>
       </c>
       <c r="DM4" t="n">
         <v>10.78</v>
@@ -2499,19 +2499,19 @@
         <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>12.36</v>
+        <v>12.5</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DW4" t="n">
         <v>16.93</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DY4" t="n">
         <v>2.5</v>
@@ -2566,7 +2566,7 @@
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
         <v>8.140000000000001</v>
@@ -2596,19 +2596,19 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
         <v>11.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.43</v>
+        <v>7.29</v>
       </c>
       <c r="AC5" t="n">
         <v>19.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AE5" t="n">
         <v>2.43</v>
@@ -2862,7 +2862,7 @@
         <v>1.79</v>
       </c>
       <c r="DL5" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DM5" t="n">
         <v>10.07</v>
@@ -2886,19 +2886,19 @@
         <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.14</v>
+        <v>16.07</v>
       </c>
       <c r="DU5" t="n">
         <v>9.92</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.21</v>
+        <v>6.14</v>
       </c>
       <c r="DW5" t="n">
         <v>17</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DY5" t="n">
         <v>2.93</v>
@@ -2923,7 +2923,7 @@
         <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
         <v>1.57</v>
@@ -2935,7 +2935,7 @@
         <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.43</v>
+        <v>3.57</v>
       </c>
       <c r="K6" t="n">
         <v>4.43</v>
@@ -2998,7 +2998,7 @@
         <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>0.14</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="DC6" t="n">
         <v>0.78</v>
@@ -3235,7 +3235,7 @@
         <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DG6" t="n">
         <v>3</v>
@@ -3292,7 +3292,7 @@
         <v>1.02</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="7">
@@ -3455,10 +3455,10 @@
         <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="BC7" t="n">
         <v>4.12</v>
@@ -3467,7 +3467,7 @@
         <v>17.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BF7" t="n">
         <v>2.12</v>
@@ -3668,10 +3668,10 @@
         <v>0.47</v>
       </c>
       <c r="DT7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="DV7" t="n">
         <v>3.53</v>
@@ -3680,7 +3680,7 @@
         <v>14.27</v>
       </c>
       <c r="DX7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="DY7" t="n">
         <v>2.4</v>
@@ -3693,67 +3693,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>105.57</v>
+        <v>103.38</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>39.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="R8" t="n">
-        <v>5.29</v>
+        <v>6.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -3762,25 +3762,25 @@
         <v>64</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.71</v>
+        <v>16.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.86</v>
+        <v>17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3864,70 +3864,70 @@
         <v>2.71</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
         <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.36</v>
+        <v>3.07</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="CA8" t="n">
         <v>3.27</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CC8" t="n">
         <v>3.11</v>
@@ -3942,37 +3942,37 @@
         <v>3.11</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK8" t="n">
         <v>1.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CR8" t="n">
         <v>1.76</v>
@@ -3993,88 +3993,88 @@
         <v>1.92</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.23</v>
+        <v>4.27</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>90.14</v>
+        <v>90</v>
       </c>
       <c r="DE8" t="n">
         <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="DG8" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="DI8" t="n">
-        <v>33.14</v>
+        <v>33</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="DL8" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>8.640000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DN8" t="n">
-        <v>5.79</v>
+        <v>6.2</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>55.86</v>
+        <v>56.4</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DT8" t="n">
-        <v>13.42</v>
+        <v>13.53</v>
       </c>
       <c r="DU8" t="n">
-        <v>8.640000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.79</v>
+        <v>4.73</v>
       </c>
       <c r="DW8" t="n">
-        <v>15.58</v>
+        <v>15.74</v>
       </c>
       <c r="DX8" t="n">
         <v>1.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4177,136 +4177,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>81</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP9" t="n">
         <v>2</v>
       </c>
-      <c r="AI9" t="n">
-        <v>86.17</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AQ9" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF9" t="n">
         <v>3</v>
       </c>
-      <c r="AL9" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BG9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.859999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.79</v>
+        <v>4.07</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT9" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
         <v>2.13</v>
@@ -4315,25 +4315,25 @@
         <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.12</v>
+        <v>3.37</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH9" t="n">
         <v>1.31</v>
@@ -4342,28 +4342,28 @@
         <v>1.74</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO9" t="n">
         <v>1.4</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CR9" t="n">
         <v>1.76</v>
@@ -4384,88 +4384,88 @@
         <v>1.84</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="DD9" t="n">
-        <v>91.15000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.22</v>
+        <v>5.13</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DI9" t="n">
-        <v>31.07</v>
+        <v>30.6</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DL9" t="n">
-        <v>13.64</v>
+        <v>13.93</v>
       </c>
       <c r="DM9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>6.57</v>
+        <v>6.46</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>51.72</v>
+        <v>50.27</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT9" t="n">
-        <v>12.36</v>
+        <v>12.46</v>
       </c>
       <c r="DU9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DV9" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="DW9" t="n">
-        <v>17.43</v>
+        <v>17</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="10">
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
         <v>0.12</v>
@@ -4967,7 +4967,7 @@
         <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
         <v>1.38</v>
@@ -5015,10 +5015,10 @@
         <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.12</v>
+        <v>7.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BC11" t="n">
         <v>2.88</v>
@@ -5027,10 +5027,10 @@
         <v>15</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
         <v>2.71</v>
@@ -5174,7 +5174,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DC11" t="n">
         <v>0.42</v>
@@ -5186,7 +5186,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DG11" t="n">
         <v>1.93</v>
@@ -5228,10 +5228,10 @@
         <v>0.28</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.35</v>
+        <v>8.43</v>
       </c>
       <c r="DU11" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="DV11" t="n">
         <v>3.43</v>
@@ -5243,7 +5243,7 @@
         <v>0.89</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="12">
@@ -5253,94 +5253,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F12" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="H12" t="n">
-        <v>113.17</v>
+        <v>110</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="K12" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
       <c r="L12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P12" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>5.67</v>
+        <v>6.14</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.5</v>
+        <v>57.43</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.17</v>
+        <v>12.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.17</v>
+        <v>4.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.17</v>
+        <v>19.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5424,70 +5424,70 @@
         <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CC12" t="n">
         <v>4.75</v>
@@ -5499,7 +5499,7 @@
         <v>1.36</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG12" t="n">
         <v>2.34</v>
@@ -5508,22 +5508,22 @@
         <v>1.22</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.97</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL12" t="n">
         <v>2.2</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CO12" t="n">
         <v>1.3</v>
@@ -5532,7 +5532,7 @@
         <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="CR12" t="n">
         <v>1.72</v>
@@ -5544,7 +5544,7 @@
         <v>1.86</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CV12" t="n">
         <v>1.86</v>
@@ -5559,82 +5559,82 @@
         <v>2.33</v>
       </c>
       <c r="CZ12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="DA12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="DE12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DB12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>98.64</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DF12" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.22</v>
+        <v>4.07</v>
       </c>
       <c r="DH12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>32.07</v>
+        <v>31.34</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DK12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>10.92</v>
+        <v>10.73</v>
       </c>
       <c r="DM12" t="n">
-        <v>11.07</v>
+        <v>10.53</v>
       </c>
       <c r="DN12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>53.21</v>
+        <v>53.07</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="DU12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="DW12" t="n">
-        <v>17.36</v>
+        <v>17.8</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -5800,16 +5800,16 @@
         <v>11.62</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.75</v>
+        <v>7.88</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="BD13" t="n">
         <v>13.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF13" t="n">
         <v>3.12</v>
@@ -6013,16 +6013,16 @@
         <v>15.28</v>
       </c>
       <c r="DU13" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="DV13" t="n">
-        <v>4.86</v>
+        <v>4.79</v>
       </c>
       <c r="DW13" t="n">
         <v>15.64</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DY13" t="n">
         <v>2.64</v>
@@ -6426,94 +6426,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>91.56999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>40.57</v>
+        <v>42.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O15" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>13.57</v>
+        <v>12.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.289999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="R15" t="n">
-        <v>5.57</v>
+        <v>6.62</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56</v>
+        <v>57.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.71</v>
+        <v>17.88</v>
       </c>
       <c r="AD15" t="n">
         <v>1.58</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6597,70 +6597,70 @@
         <v>2.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.710000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CA15" t="n">
         <v>3.37</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC15" t="n">
         <v>3.14</v>
@@ -6669,7 +6669,7 @@
         <v>3.86</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
         <v>2.87</v>
@@ -6684,16 +6684,16 @@
         <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN15" t="n">
         <v>1.68</v>
@@ -6705,7 +6705,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CR15" t="n">
         <v>1.89</v>
@@ -6726,88 +6726,88 @@
         <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CY15" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="DD15" t="n">
-        <v>91.86</v>
+        <v>93.27</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.93</v>
+        <v>5.33</v>
       </c>
       <c r="DH15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>34.43</v>
+        <v>36</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="DL15" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="DM15" t="n">
-        <v>8.640000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DN15" t="n">
-        <v>5.64</v>
+        <v>6.2</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>54.14</v>
+        <v>55.2</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
         <v>13.07</v>
       </c>
       <c r="DU15" t="n">
-        <v>8.359999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DV15" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="DW15" t="n">
-        <v>14.07</v>
+        <v>14.87</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -6907,49 +6907,49 @@
         <v>3.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>32.12</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.71</v>
+        <v>13.88</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.43</v>
+        <v>9.25</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
         <v>1</v>
@@ -6964,82 +6964,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>38.57</v>
+        <v>39.88</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.29</v>
+        <v>11.12</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.86</v>
+        <v>7.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO16" t="n">
         <v>1.07</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1</v>
       </c>
       <c r="BP16" t="n">
         <v>3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="BR16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS16" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>2.5</v>
@@ -7051,43 +7051,43 @@
         <v>3.01</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.98</v>
+        <v>4.65</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL16" t="n">
         <v>2.12</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CO16" t="n">
         <v>1.33</v>
@@ -7096,7 +7096,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="CR16" t="n">
         <v>1.77</v>
@@ -7108,64 +7108,64 @@
         <v>1.86</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CV16" t="n">
         <v>1.86</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CY16" t="n">
         <v>2.35</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>88.22</v>
+        <v>88.27</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DI16" t="n">
-        <v>29.5</v>
+        <v>30.66</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DL16" t="n">
-        <v>11.78</v>
+        <v>11.54</v>
       </c>
       <c r="DM16" t="n">
-        <v>8.859999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="DN16" t="n">
-        <v>7.07</v>
+        <v>7.2</v>
       </c>
       <c r="DO16" t="n">
         <v>0.07000000000000001</v>
@@ -7177,28 +7177,28 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>46.78</v>
+        <v>46.94</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT16" t="n">
-        <v>13</v>
+        <v>13.26</v>
       </c>
       <c r="DU16" t="n">
-        <v>8.640000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.36</v>
+        <v>4.54</v>
       </c>
       <c r="DW16" t="n">
-        <v>17.5</v>
+        <v>17.93</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DY16" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -7331,7 +7331,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.43</v>
+        <v>9.43</v>
       </c>
       <c r="AR17" t="n">
         <v>7.71</v>
@@ -7550,7 +7550,7 @@
         <v>1.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>9.859999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="DM17" t="n">
         <v>8.26</v>
@@ -8772,13 +8772,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0.14</v>
@@ -8814,7 +8814,7 @@
         <v>1.71</v>
       </c>
       <c r="P21" t="n">
-        <v>12.43</v>
+        <v>13.43</v>
       </c>
       <c r="Q21" t="n">
         <v>6.57</v>
@@ -8844,10 +8844,10 @@
         <v>0.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.43</v>
+        <v>14.29</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.710000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="AB21" t="n">
         <v>5.71</v>
@@ -8856,7 +8856,7 @@
         <v>17.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -8865,49 +8865,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>94.43000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>28.14</v>
+        <v>28.12</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -8919,73 +8919,73 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>45.57</v>
+        <v>44.38</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.14</v>
+        <v>12.88</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.86</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.43</v>
+        <v>9.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="BP21" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT21" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU21" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY21" t="n">
         <v>1.9</v>
@@ -9003,55 +9003,55 @@
         <v>2.02</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="CD21" t="n">
         <v>3.37</v>
-      </c>
-      <c r="CC21" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="CD21" t="n">
-        <v>3.33</v>
       </c>
       <c r="CE21" t="n">
         <v>1.35</v>
       </c>
       <c r="CF21" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI21" t="n">
         <v>1.61</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK21" t="n">
         <v>1.55</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN21" t="n">
         <v>1.55</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="CR21" t="n">
         <v>1.76</v>
@@ -9075,52 +9075,52 @@
         <v>1.41</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CZ21" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="DA21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="DD21" t="n">
-        <v>92.5</v>
+        <v>91</v>
       </c>
       <c r="DE21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF21" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DG21" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="DI21" t="n">
-        <v>32.07</v>
+        <v>31.8</v>
       </c>
       <c r="DJ21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DK21" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="DL21" t="n">
-        <v>11.72</v>
+        <v>11.8</v>
       </c>
       <c r="DM21" t="n">
-        <v>8.359999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="DN21" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>50</v>
+        <v>49.07</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT21" t="n">
-        <v>13.28</v>
+        <v>13.54</v>
       </c>
       <c r="DU21" t="n">
-        <v>8.279999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DV21" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DW21" t="n">
-        <v>15.86</v>
+        <v>15.53</v>
       </c>
       <c r="DX21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DY21" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Colombia_P" displayName="AveragesTable_Colombia_P" ref="A1:DY21" headerRowCount="1">
-  <autoFilter ref="A1:DY21"/>
-  <tableColumns count="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Colombia_P" displayName="AveragesTable_Colombia_P" ref="A1:EA21" headerRowCount="1">
+  <autoFilter ref="A1:EA21"/>
+  <tableColumns count="131">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
     <tableColumn id="3" name="home_games"/>
@@ -235,40 +235,42 @@
     <tableColumn id="93" name="avg_odds_ft_over15"/>
     <tableColumn id="94" name="avg_odds_ft_over25"/>
     <tableColumn id="95" name="avg_odds_ft_over35"/>
-    <tableColumn id="96" name="avg_pinnacle_btts_no_odd"/>
-    <tableColumn id="97" name="avg_pinnacle_btts_yes_odd"/>
-    <tableColumn id="98" name="avg_pinnacle_corners_over_85_odd"/>
-    <tableColumn id="99" name="avg_pinnacle_corners_over_95_odd"/>
-    <tableColumn id="100" name="avg_pinnacle_corners_under_85_odd"/>
-    <tableColumn id="101" name="avg_pinnacle_corners_under_95_odd"/>
-    <tableColumn id="102" name="avg_pinnacle_ft_over15_odd"/>
-    <tableColumn id="103" name="avg_pinnacle_ft_over25_odd"/>
-    <tableColumn id="104" name="avg_pinnacle_ft_over35_odd"/>
-    <tableColumn id="105" name="total_avg_0_10_min_goals"/>
-    <tableColumn id="106" name="total_avg_2h_cards"/>
-    <tableColumn id="107" name="total_avg_2h_corners"/>
-    <tableColumn id="108" name="total_avg_attacks"/>
-    <tableColumn id="109" name="total_avg_cards_0_10_min"/>
-    <tableColumn id="110" name="total_avg_cards_num"/>
-    <tableColumn id="111" name="total_avg_corners"/>
-    <tableColumn id="112" name="total_avg_corners_0_10_min"/>
-    <tableColumn id="113" name="total_avg_dangerous_attacks"/>
-    <tableColumn id="114" name="total_avg_fh_cards"/>
-    <tableColumn id="115" name="total_avg_fh_corners"/>
-    <tableColumn id="116" name="total_avg_fouls"/>
-    <tableColumn id="117" name="total_avg_freekicks"/>
-    <tableColumn id="118" name="total_avg_goalkicks"/>
-    <tableColumn id="119" name="total_avg_penalties_won"/>
-    <tableColumn id="120" name="total_avg_penalty_goals"/>
-    <tableColumn id="121" name="total_avg_penalty_missed"/>
-    <tableColumn id="122" name="total_avg_possession"/>
-    <tableColumn id="123" name="total_avg_red_cards"/>
-    <tableColumn id="124" name="total_avg_shots"/>
-    <tableColumn id="125" name="total_avg_shotsOffTarget"/>
-    <tableColumn id="126" name="total_avg_shotsOnTarget"/>
-    <tableColumn id="127" name="total_avg_throwins"/>
-    <tableColumn id="128" name="total_avg_xg"/>
-    <tableColumn id="129" name="total_avg_yellow_cards"/>
+    <tableColumn id="96" name="avg_pinnacle_1st_half_over15_odd"/>
+    <tableColumn id="97" name="avg_pinnacle_1st_half_under15_odd"/>
+    <tableColumn id="98" name="avg_pinnacle_btts_no_odd"/>
+    <tableColumn id="99" name="avg_pinnacle_btts_yes_odd"/>
+    <tableColumn id="100" name="avg_pinnacle_corners_over_85_odd"/>
+    <tableColumn id="101" name="avg_pinnacle_corners_over_95_odd"/>
+    <tableColumn id="102" name="avg_pinnacle_corners_under_85_odd"/>
+    <tableColumn id="103" name="avg_pinnacle_corners_under_95_odd"/>
+    <tableColumn id="104" name="avg_pinnacle_ft_over15_odd"/>
+    <tableColumn id="105" name="avg_pinnacle_ft_over25_odd"/>
+    <tableColumn id="106" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="107" name="total_avg_0_10_min_goals"/>
+    <tableColumn id="108" name="total_avg_2h_cards"/>
+    <tableColumn id="109" name="total_avg_2h_corners"/>
+    <tableColumn id="110" name="total_avg_attacks"/>
+    <tableColumn id="111" name="total_avg_cards_0_10_min"/>
+    <tableColumn id="112" name="total_avg_cards_num"/>
+    <tableColumn id="113" name="total_avg_corners"/>
+    <tableColumn id="114" name="total_avg_corners_0_10_min"/>
+    <tableColumn id="115" name="total_avg_dangerous_attacks"/>
+    <tableColumn id="116" name="total_avg_fh_cards"/>
+    <tableColumn id="117" name="total_avg_fh_corners"/>
+    <tableColumn id="118" name="total_avg_fouls"/>
+    <tableColumn id="119" name="total_avg_freekicks"/>
+    <tableColumn id="120" name="total_avg_goalkicks"/>
+    <tableColumn id="121" name="total_avg_penalties_won"/>
+    <tableColumn id="122" name="total_avg_penalty_goals"/>
+    <tableColumn id="123" name="total_avg_penalty_missed"/>
+    <tableColumn id="124" name="total_avg_possession"/>
+    <tableColumn id="125" name="total_avg_red_cards"/>
+    <tableColumn id="126" name="total_avg_shots"/>
+    <tableColumn id="127" name="total_avg_shotsOffTarget"/>
+    <tableColumn id="128" name="total_avg_shotsOnTarget"/>
+    <tableColumn id="129" name="total_avg_throwins"/>
+    <tableColumn id="130" name="total_avg_xg"/>
+    <tableColumn id="131" name="total_avg_yellow_cards"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -563,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY21"/>
+  <dimension ref="A1:EA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.8" customWidth="1" min="1" max="1"/>
@@ -661,40 +663,42 @@
     <col width="24" customWidth="1" min="93" max="93"/>
     <col width="24" customWidth="1" min="94" max="94"/>
     <col width="24" customWidth="1" min="95" max="95"/>
-    <col width="31.2" customWidth="1" min="96" max="96"/>
-    <col width="32.4" customWidth="1" min="97" max="97"/>
-    <col width="40.8" customWidth="1" min="98" max="98"/>
-    <col width="40.8" customWidth="1" min="99" max="99"/>
-    <col width="42" customWidth="1" min="100" max="100"/>
-    <col width="42" customWidth="1" min="101" max="101"/>
-    <col width="33.6" customWidth="1" min="102" max="102"/>
-    <col width="33.6" customWidth="1" min="103" max="103"/>
+    <col width="40.8" customWidth="1" min="96" max="96"/>
+    <col width="42" customWidth="1" min="97" max="97"/>
+    <col width="31.2" customWidth="1" min="98" max="98"/>
+    <col width="32.4" customWidth="1" min="99" max="99"/>
+    <col width="40.8" customWidth="1" min="100" max="100"/>
+    <col width="40.8" customWidth="1" min="101" max="101"/>
+    <col width="42" customWidth="1" min="102" max="102"/>
+    <col width="42" customWidth="1" min="103" max="103"/>
     <col width="33.6" customWidth="1" min="104" max="104"/>
-    <col width="31.2" customWidth="1" min="105" max="105"/>
-    <col width="24" customWidth="1" min="106" max="106"/>
-    <col width="26.4" customWidth="1" min="107" max="107"/>
-    <col width="22.8" customWidth="1" min="108" max="108"/>
-    <col width="31.2" customWidth="1" min="109" max="109"/>
-    <col width="25.2" customWidth="1" min="110" max="110"/>
-    <col width="22.8" customWidth="1" min="111" max="111"/>
-    <col width="33.6" customWidth="1" min="112" max="112"/>
-    <col width="34.8" customWidth="1" min="113" max="113"/>
-    <col width="24" customWidth="1" min="114" max="114"/>
-    <col width="26.4" customWidth="1" min="115" max="115"/>
-    <col width="20.4" customWidth="1" min="116" max="116"/>
-    <col width="25.2" customWidth="1" min="117" max="117"/>
-    <col width="25.2" customWidth="1" min="118" max="118"/>
-    <col width="30" customWidth="1" min="119" max="119"/>
-    <col width="30" customWidth="1" min="120" max="120"/>
-    <col width="31.2" customWidth="1" min="121" max="121"/>
-    <col width="26.4" customWidth="1" min="122" max="122"/>
-    <col width="25.2" customWidth="1" min="123" max="123"/>
-    <col width="20.4" customWidth="1" min="124" max="124"/>
-    <col width="31.2" customWidth="1" min="125" max="125"/>
-    <col width="30" customWidth="1" min="126" max="126"/>
-    <col width="24" customWidth="1" min="127" max="127"/>
-    <col width="16.8" customWidth="1" min="128" max="128"/>
-    <col width="28.8" customWidth="1" min="129" max="129"/>
+    <col width="33.6" customWidth="1" min="105" max="105"/>
+    <col width="33.6" customWidth="1" min="106" max="106"/>
+    <col width="31.2" customWidth="1" min="107" max="107"/>
+    <col width="24" customWidth="1" min="108" max="108"/>
+    <col width="26.4" customWidth="1" min="109" max="109"/>
+    <col width="22.8" customWidth="1" min="110" max="110"/>
+    <col width="31.2" customWidth="1" min="111" max="111"/>
+    <col width="25.2" customWidth="1" min="112" max="112"/>
+    <col width="22.8" customWidth="1" min="113" max="113"/>
+    <col width="33.6" customWidth="1" min="114" max="114"/>
+    <col width="34.8" customWidth="1" min="115" max="115"/>
+    <col width="24" customWidth="1" min="116" max="116"/>
+    <col width="26.4" customWidth="1" min="117" max="117"/>
+    <col width="20.4" customWidth="1" min="118" max="118"/>
+    <col width="25.2" customWidth="1" min="119" max="119"/>
+    <col width="25.2" customWidth="1" min="120" max="120"/>
+    <col width="30" customWidth="1" min="121" max="121"/>
+    <col width="30" customWidth="1" min="122" max="122"/>
+    <col width="31.2" customWidth="1" min="123" max="123"/>
+    <col width="26.4" customWidth="1" min="124" max="124"/>
+    <col width="25.2" customWidth="1" min="125" max="125"/>
+    <col width="20.4" customWidth="1" min="126" max="126"/>
+    <col width="31.2" customWidth="1" min="127" max="127"/>
+    <col width="30" customWidth="1" min="128" max="128"/>
+    <col width="24" customWidth="1" min="129" max="129"/>
+    <col width="16.8" customWidth="1" min="130" max="130"/>
+    <col width="28.8" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,170 +1179,180 @@
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
+          <t>avg_pinnacle_1st_half_over15_odd</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>avg_pinnacle_1st_half_under15_odd</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1351,13 +1365,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1444,136 +1458,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>67.29000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.86</v>
+        <v>23.12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.71</v>
+        <v>7.62</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.86</v>
+        <v>42.62</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.86</v>
+        <v>18.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1</v>
       </c>
-      <c r="BO2" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BP2" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="BQ2" t="n">
         <v>4</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
         <v>2.17</v>
@@ -1582,28 +1596,28 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.57</v>
+        <v>5.16</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.47</v>
+        <v>5.95</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI2" t="n">
         <v>1.65</v>
@@ -1615,10 +1629,10 @@
         <v>1.67</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN2" t="n">
         <v>1.68</v>
@@ -1627,112 +1641,114 @@
         <v>1.43</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="CR2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="n">
         <v>1.66</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CU2" t="n">
         <v>2.28</v>
       </c>
-      <c r="CT2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CW2" t="n">
         <v>1.9</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CX2" t="n">
         <v>1.92</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CY2" t="n">
         <v>1.83</v>
       </c>
-      <c r="CX2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>2.43</v>
-      </c>
       <c r="CZ2" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="DA2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="DC2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DD2" t="n">
-        <v>77.86</v>
+        <v>2.07</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>1.67</v>
       </c>
       <c r="DF2" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DH2" t="n">
         <v>2.86</v>
       </c>
-      <c r="DG2" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DI2" t="n">
-        <v>31.78</v>
+        <v>4.33</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="DK2" t="n">
-        <v>1.86</v>
+        <v>31.33</v>
       </c>
       <c r="DL2" t="n">
-        <v>11.36</v>
+        <v>0.73</v>
       </c>
       <c r="DM2" t="n">
-        <v>12.22</v>
+        <v>1.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>7.42</v>
+        <v>11.47</v>
       </c>
       <c r="DO2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DR2" t="n">
-        <v>45.86</v>
+        <v>0.06</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>10.57</v>
+        <v>45.53</v>
       </c>
       <c r="DU2" t="n">
-        <v>7.79</v>
+        <v>0.27</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.79</v>
+        <v>10.6</v>
       </c>
       <c r="DW2" t="n">
-        <v>18.14</v>
+        <v>7.66</v>
       </c>
       <c r="DX2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>1.1</v>
       </c>
-      <c r="DY2" t="n">
-        <v>2.5</v>
+      <c r="EA2" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="3">
@@ -1742,13 +1758,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1835,124 +1851,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>79.86</v>
+        <v>82.38</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.86</v>
+        <v>32.75</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.43</v>
+        <v>14.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.29</v>
+        <v>11.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.57</v>
+        <v>54.88</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.57</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.71</v>
+        <v>7.62</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.29</v>
+        <v>16.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="BG3" t="n">
         <v>2.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="BI3" t="n">
         <v>2.07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1964,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
         <v>1.74</v>
@@ -1973,34 +1989,34 @@
         <v>1.78</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
         <v>1.61</v>
@@ -2009,10 +2025,10 @@
         <v>2.29</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CO3" t="n">
         <v>1.3</v>
@@ -2021,109 +2037,111 @@
         <v>2.28</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="CR3" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="n">
         <v>1.76</v>
       </c>
-      <c r="CS3" t="n">
+      <c r="CU3" t="n">
         <v>2.08</v>
       </c>
-      <c r="CT3" t="n">
+      <c r="CV3" t="n">
         <v>1.8</v>
       </c>
-      <c r="CU3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CV3" t="n">
+      <c r="CW3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CX3" t="n">
         <v>1.92</v>
       </c>
-      <c r="CW3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CX3" t="n">
+      <c r="CY3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CZ3" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY3" t="n">
+      <c r="DA3" t="n">
         <v>2.33</v>
       </c>
-      <c r="CZ3" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>0</v>
-      </c>
       <c r="DB3" t="n">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>88</v>
+        <v>2.47</v>
       </c>
       <c r="DE3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="DG3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>3.78</v>
-      </c>
       <c r="DH3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="DJ3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DI3" t="n">
-        <v>49</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="DK3" t="n">
-        <v>1.08</v>
+        <v>48.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>13.93</v>
+        <v>1.13</v>
       </c>
       <c r="DM3" t="n">
-        <v>11.64</v>
+        <v>1.27</v>
       </c>
       <c r="DN3" t="n">
-        <v>7.43</v>
+        <v>13.87</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.28</v>
+        <v>11.6</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.28</v>
+        <v>7.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="DR3" t="n">
-        <v>56.57</v>
+        <v>0.26</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>14.43</v>
+        <v>57.07</v>
       </c>
       <c r="DU3" t="n">
-        <v>9.92</v>
+        <v>0.33</v>
       </c>
       <c r="DV3" t="n">
-        <v>4.5</v>
+        <v>14.67</v>
       </c>
       <c r="DW3" t="n">
-        <v>17.79</v>
+        <v>10.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.58</v>
+        <v>4.47</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.14</v>
+        <v>17.34</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="4">
@@ -2414,106 +2432,108 @@
       <c r="CQ4" t="n">
         <v>4.43</v>
       </c>
-      <c r="CR4" t="n">
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="n">
         <v>1.73</v>
       </c>
-      <c r="CS4" t="n">
+      <c r="CU4" t="n">
         <v>2.13</v>
       </c>
-      <c r="CT4" t="n">
+      <c r="CV4" t="n">
         <v>1.84</v>
       </c>
-      <c r="CU4" t="n">
+      <c r="CW4" t="n">
         <v>1.84</v>
       </c>
-      <c r="CV4" t="n">
+      <c r="CX4" t="n">
         <v>1.89</v>
       </c>
-      <c r="CW4" t="n">
+      <c r="CY4" t="n">
         <v>1.88</v>
       </c>
-      <c r="CX4" t="n">
+      <c r="CZ4" t="n">
         <v>1.44</v>
       </c>
-      <c r="CY4" t="n">
+      <c r="DA4" t="n">
         <v>2.42</v>
       </c>
-      <c r="CZ4" t="n">
+      <c r="DB4" t="n">
         <v>4.6</v>
       </c>
-      <c r="DA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="n">
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
         <v>1.93</v>
       </c>
-      <c r="DC4" t="n">
+      <c r="DE4" t="n">
         <v>1.86</v>
       </c>
-      <c r="DD4" t="n">
+      <c r="DF4" t="n">
         <v>99.86</v>
       </c>
-      <c r="DE4" t="n">
+      <c r="DG4" t="n">
         <v>0.14</v>
       </c>
-      <c r="DF4" t="n">
+      <c r="DH4" t="n">
         <v>2.72</v>
       </c>
-      <c r="DG4" t="n">
+      <c r="DI4" t="n">
         <v>4.78</v>
       </c>
-      <c r="DH4" t="n">
+      <c r="DJ4" t="n">
         <v>0.14</v>
       </c>
-      <c r="DI4" t="n">
+      <c r="DK4" t="n">
         <v>36.57</v>
       </c>
-      <c r="DJ4" t="n">
+      <c r="DL4" t="n">
         <v>0.71</v>
       </c>
-      <c r="DK4" t="n">
+      <c r="DM4" t="n">
         <v>1.93</v>
       </c>
-      <c r="DL4" t="n">
+      <c r="DN4" t="n">
         <v>11.42</v>
       </c>
-      <c r="DM4" t="n">
+      <c r="DO4" t="n">
         <v>10.78</v>
       </c>
-      <c r="DN4" t="n">
+      <c r="DP4" t="n">
         <v>7.07</v>
       </c>
-      <c r="DO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>0</v>
-      </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="n">
         <v>52.21</v>
       </c>
-      <c r="DS4" t="n">
+      <c r="DU4" t="n">
         <v>0.14</v>
       </c>
-      <c r="DT4" t="n">
+      <c r="DV4" t="n">
         <v>12.5</v>
       </c>
-      <c r="DU4" t="n">
+      <c r="DW4" t="n">
         <v>8.5</v>
       </c>
-      <c r="DV4" t="n">
+      <c r="DX4" t="n">
         <v>4</v>
       </c>
-      <c r="DW4" t="n">
+      <c r="DY4" t="n">
         <v>16.93</v>
       </c>
-      <c r="DX4" t="n">
+      <c r="DZ4" t="n">
         <v>1.34</v>
       </c>
-      <c r="DY4" t="n">
+      <c r="EA4" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2524,94 +2544,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="H5" t="n">
-        <v>95.29000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="K5" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>36.29</v>
+        <v>35.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="R5" t="n">
-        <v>7.43</v>
+        <v>7.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.14</v>
+        <v>57.25</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>19.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.71</v>
+        <v>12</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.14</v>
+        <v>19.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2695,70 +2715,70 @@
         <v>3.43</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BL5" t="n">
         <v>1.07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP5" t="n">
         <v>3.07</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
         <v>1.16</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.06</v>
+        <v>4.19</v>
       </c>
       <c r="CC5" t="n">
         <v>2.08</v>
@@ -2767,141 +2787,147 @@
         <v>2.42</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI5" t="n">
         <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="CR5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CT5" t="n">
         <v>1.89</v>
       </c>
-      <c r="CS5" t="n">
+      <c r="CU5" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="n">
-        <v>1.89</v>
       </c>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="n">
         <v>1.84</v>
       </c>
-      <c r="CX5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="CZ5" t="n">
-        <v>3.27</v>
+        <v>1.28</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.14</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.72</v>
+        <v>3.18</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.93</v>
+        <v>0.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>89.43000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.28</v>
+        <v>90.53</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.71</v>
+        <v>0.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.14</v>
+        <v>3.2</v>
       </c>
       <c r="DI5" t="n">
-        <v>33.5</v>
+        <v>4.66</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.43</v>
+        <v>0.27</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.79</v>
+        <v>33.26</v>
       </c>
       <c r="DL5" t="n">
-        <v>11.07</v>
+        <v>1.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>10.07</v>
+        <v>1.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>8.779999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.22</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DR5" t="n">
-        <v>56.64</v>
+        <v>0.2</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>16.07</v>
+        <v>56.27</v>
       </c>
       <c r="DU5" t="n">
-        <v>9.92</v>
+        <v>0.2</v>
       </c>
       <c r="DV5" t="n">
-        <v>6.14</v>
+        <v>16.33</v>
       </c>
       <c r="DW5" t="n">
-        <v>17</v>
+        <v>10.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.68</v>
+        <v>6.13</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.93</v>
+        <v>17.27</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="6">
@@ -3192,106 +3218,108 @@
       <c r="CQ6" t="n">
         <v>4.33</v>
       </c>
-      <c r="CR6" t="n">
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="n">
         <v>1.58</v>
       </c>
-      <c r="CS6" t="n">
+      <c r="CU6" t="n">
         <v>2.42</v>
       </c>
-      <c r="CT6" t="n">
+      <c r="CV6" t="n">
         <v>1.86</v>
       </c>
-      <c r="CU6" t="n">
+      <c r="CW6" t="n">
         <v>1.91</v>
       </c>
-      <c r="CV6" t="n">
+      <c r="CX6" t="n">
         <v>1.87</v>
       </c>
-      <c r="CW6" t="n">
+      <c r="CY6" t="n">
         <v>1.82</v>
       </c>
-      <c r="CX6" t="n">
+      <c r="CZ6" t="n">
         <v>1.46</v>
       </c>
-      <c r="CY6" t="n">
+      <c r="DA6" t="n">
         <v>2.45</v>
       </c>
-      <c r="CZ6" t="n">
+      <c r="DB6" t="n">
         <v>4.68</v>
       </c>
-      <c r="DA6" t="n">
+      <c r="DC6" t="n">
         <v>0.14</v>
       </c>
-      <c r="DB6" t="n">
+      <c r="DD6" t="n">
         <v>1.43</v>
       </c>
-      <c r="DC6" t="n">
+      <c r="DE6" t="n">
         <v>0.78</v>
       </c>
-      <c r="DD6" t="n">
+      <c r="DF6" t="n">
         <v>76.28</v>
       </c>
-      <c r="DE6" t="n">
+      <c r="DG6" t="n">
         <v>0.22</v>
       </c>
-      <c r="DF6" t="n">
+      <c r="DH6" t="n">
         <v>3</v>
       </c>
-      <c r="DG6" t="n">
+      <c r="DI6" t="n">
         <v>3</v>
       </c>
-      <c r="DH6" t="n">
+      <c r="DJ6" t="n">
         <v>0.14</v>
       </c>
-      <c r="DI6" t="n">
+      <c r="DK6" t="n">
         <v>23.43</v>
       </c>
-      <c r="DJ6" t="n">
+      <c r="DL6" t="n">
         <v>1.5</v>
       </c>
-      <c r="DK6" t="n">
+      <c r="DM6" t="n">
         <v>1.43</v>
       </c>
-      <c r="DL6" t="n">
+      <c r="DN6" t="n">
         <v>13.5</v>
       </c>
-      <c r="DM6" t="n">
+      <c r="DO6" t="n">
         <v>11.22</v>
       </c>
-      <c r="DN6" t="n">
+      <c r="DP6" t="n">
         <v>6.42</v>
       </c>
-      <c r="DO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>0</v>
-      </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
         <v>46.42</v>
       </c>
-      <c r="DS6" t="n">
+      <c r="DU6" t="n">
         <v>0.28</v>
       </c>
-      <c r="DT6" t="n">
+      <c r="DV6" t="n">
         <v>10.14</v>
       </c>
-      <c r="DU6" t="n">
+      <c r="DW6" t="n">
         <v>7.22</v>
       </c>
-      <c r="DV6" t="n">
+      <c r="DX6" t="n">
         <v>2.92</v>
       </c>
-      <c r="DW6" t="n">
+      <c r="DY6" t="n">
         <v>11.78</v>
       </c>
-      <c r="DX6" t="n">
+      <c r="DZ6" t="n">
         <v>1.02</v>
       </c>
-      <c r="DY6" t="n">
+      <c r="EA6" t="n">
         <v>2.64</v>
       </c>
     </row>
@@ -3302,94 +3330,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="H7" t="n">
-        <v>62.43</v>
+        <v>61.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="K7" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>23.86</v>
+        <v>23.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="O7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="P7" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.86</v>
+        <v>12.75</v>
       </c>
       <c r="R7" t="n">
-        <v>8.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.29</v>
+        <v>43.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="AD7" t="n">
         <v>0.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3473,70 +3501,70 @@
         <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="CA7" t="n">
         <v>3.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CC7" t="n">
         <v>4.7</v>
@@ -3545,16 +3573,16 @@
         <v>5.72</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI7" t="n">
         <v>1.76</v>
@@ -3566,124 +3594,126 @@
         <v>1.61</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>2.01</v>
-      </c>
+        <v>3.63</v>
+      </c>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
       <c r="CT7" t="n">
         <v>1.82</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="CV7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CX7" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CX7" t="n">
+      <c r="CY7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CZ7" t="n">
         <v>1.39</v>
       </c>
-      <c r="CY7" t="n">
+      <c r="DA7" t="n">
         <v>2.23</v>
       </c>
-      <c r="CZ7" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DB7" t="n">
-        <v>1.67</v>
+        <v>4.09</v>
       </c>
       <c r="DC7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>72</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="DZ7" t="n">
         <v>1</v>
       </c>
-      <c r="DD7" t="n">
-        <v>73.27</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>14.27</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>2.4</v>
+      <c r="EA7" t="n">
+        <v>2.44</v>
       </c>
     </row>
     <row r="8">
@@ -3708,7 +3738,7 @@
         <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
         <v>103.38</v>
@@ -3723,7 +3753,7 @@
         <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="M8" t="n">
         <v>39.75</v>
@@ -3732,7 +3762,7 @@
         <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
         <v>9.25</v>
@@ -3867,7 +3897,7 @@
         <v>2.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BI8" t="n">
         <v>2.47</v>
@@ -3891,10 +3921,10 @@
         <v>1.13</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="BR8" t="n">
         <v>86.67</v>
@@ -3974,106 +4004,108 @@
       <c r="CQ8" t="n">
         <v>4.25</v>
       </c>
-      <c r="CR8" t="n">
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="n">
         <v>1.76</v>
       </c>
-      <c r="CS8" t="n">
+      <c r="CU8" t="n">
         <v>2.09</v>
       </c>
-      <c r="CT8" t="n">
+      <c r="CV8" t="n">
         <v>1.84</v>
       </c>
-      <c r="CU8" t="n">
+      <c r="CW8" t="n">
         <v>1.8</v>
       </c>
-      <c r="CV8" t="n">
+      <c r="CX8" t="n">
         <v>1.89</v>
       </c>
-      <c r="CW8" t="n">
+      <c r="CY8" t="n">
         <v>1.92</v>
       </c>
-      <c r="CX8" t="n">
+      <c r="CZ8" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY8" t="n">
+      <c r="DA8" t="n">
         <v>2.32</v>
       </c>
-      <c r="CZ8" t="n">
+      <c r="DB8" t="n">
         <v>4.27</v>
       </c>
-      <c r="DA8" t="n">
+      <c r="DC8" t="n">
         <v>0.13</v>
       </c>
-      <c r="DB8" t="n">
+      <c r="DD8" t="n">
         <v>1.66</v>
       </c>
-      <c r="DC8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DD8" t="n">
+      <c r="DE8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF8" t="n">
         <v>90</v>
       </c>
-      <c r="DE8" t="n">
+      <c r="DG8" t="n">
         <v>0.14</v>
       </c>
-      <c r="DF8" t="n">
+      <c r="DH8" t="n">
         <v>3.27</v>
       </c>
-      <c r="DG8" t="n">
+      <c r="DI8" t="n">
         <v>4.8</v>
       </c>
-      <c r="DH8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DI8" t="n">
+      <c r="DJ8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DK8" t="n">
         <v>33</v>
       </c>
-      <c r="DJ8" t="n">
+      <c r="DL8" t="n">
         <v>1.2</v>
       </c>
-      <c r="DK8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DL8" t="n">
+      <c r="DM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN8" t="n">
         <v>10.47</v>
       </c>
-      <c r="DM8" t="n">
+      <c r="DO8" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="DN8" t="n">
+      <c r="DP8" t="n">
         <v>6.2</v>
       </c>
-      <c r="DO8" t="n">
+      <c r="DQ8" t="n">
         <v>0.2</v>
       </c>
-      <c r="DP8" t="n">
+      <c r="DR8" t="n">
         <v>0.2</v>
       </c>
-      <c r="DQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="n">
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
         <v>56.4</v>
       </c>
-      <c r="DS8" t="n">
+      <c r="DU8" t="n">
         <v>0.46</v>
       </c>
-      <c r="DT8" t="n">
+      <c r="DV8" t="n">
         <v>13.53</v>
       </c>
-      <c r="DU8" t="n">
+      <c r="DW8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="DV8" t="n">
+      <c r="DX8" t="n">
         <v>4.73</v>
       </c>
-      <c r="DW8" t="n">
+      <c r="DY8" t="n">
         <v>15.74</v>
       </c>
-      <c r="DX8" t="n">
+      <c r="DZ8" t="n">
         <v>1.43</v>
       </c>
-      <c r="DY8" t="n">
+      <c r="EA8" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -4365,106 +4397,108 @@
       <c r="CQ9" t="n">
         <v>4.17</v>
       </c>
-      <c r="CR9" t="n">
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="n">
         <v>1.76</v>
       </c>
-      <c r="CS9" t="n">
+      <c r="CU9" t="n">
         <v>2.11</v>
       </c>
-      <c r="CT9" t="n">
+      <c r="CV9" t="n">
         <v>1.89</v>
       </c>
-      <c r="CU9" t="n">
+      <c r="CW9" t="n">
         <v>1.89</v>
       </c>
-      <c r="CV9" t="n">
+      <c r="CX9" t="n">
         <v>1.84</v>
       </c>
-      <c r="CW9" t="n">
+      <c r="CY9" t="n">
         <v>1.84</v>
       </c>
-      <c r="CX9" t="n">
+      <c r="CZ9" t="n">
         <v>1.43</v>
       </c>
-      <c r="CY9" t="n">
+      <c r="DA9" t="n">
         <v>2.39</v>
       </c>
-      <c r="CZ9" t="n">
+      <c r="DB9" t="n">
         <v>4.49</v>
       </c>
-      <c r="DA9" t="n">
+      <c r="DC9" t="n">
         <v>0.06</v>
       </c>
-      <c r="DB9" t="n">
+      <c r="DD9" t="n">
         <v>1.66</v>
       </c>
-      <c r="DC9" t="n">
+      <c r="DE9" t="n">
         <v>2.33</v>
       </c>
-      <c r="DD9" t="n">
+      <c r="DF9" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="DE9" t="n">
+      <c r="DG9" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF9" t="n">
+      <c r="DH9" t="n">
         <v>3.4</v>
       </c>
-      <c r="DG9" t="n">
+      <c r="DI9" t="n">
         <v>5.13</v>
       </c>
-      <c r="DH9" t="n">
+      <c r="DJ9" t="n">
         <v>0.26</v>
       </c>
-      <c r="DI9" t="n">
+      <c r="DK9" t="n">
         <v>30.6</v>
       </c>
-      <c r="DJ9" t="n">
+      <c r="DL9" t="n">
         <v>1.67</v>
       </c>
-      <c r="DK9" t="n">
+      <c r="DM9" t="n">
         <v>1.8</v>
       </c>
-      <c r="DL9" t="n">
+      <c r="DN9" t="n">
         <v>13.93</v>
       </c>
-      <c r="DM9" t="n">
+      <c r="DO9" t="n">
         <v>9.66</v>
       </c>
-      <c r="DN9" t="n">
+      <c r="DP9" t="n">
         <v>6.46</v>
       </c>
-      <c r="DO9" t="n">
+      <c r="DQ9" t="n">
         <v>0.13</v>
       </c>
-      <c r="DP9" t="n">
+      <c r="DR9" t="n">
         <v>0.13</v>
       </c>
-      <c r="DQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR9" t="n">
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
         <v>50.27</v>
       </c>
-      <c r="DS9" t="n">
+      <c r="DU9" t="n">
         <v>0.27</v>
       </c>
-      <c r="DT9" t="n">
+      <c r="DV9" t="n">
         <v>12.46</v>
       </c>
-      <c r="DU9" t="n">
+      <c r="DW9" t="n">
         <v>8.33</v>
       </c>
-      <c r="DV9" t="n">
+      <c r="DX9" t="n">
         <v>4.13</v>
       </c>
-      <c r="DW9" t="n">
+      <c r="DY9" t="n">
         <v>17</v>
       </c>
-      <c r="DX9" t="n">
+      <c r="DZ9" t="n">
         <v>1.31</v>
       </c>
-      <c r="DY9" t="n">
+      <c r="EA9" t="n">
         <v>3.06</v>
       </c>
     </row>
@@ -4756,102 +4790,104 @@
       <c r="CQ10" t="n">
         <v>4.69</v>
       </c>
-      <c r="CR10" t="n">
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="n">
         <v>1.68</v>
       </c>
-      <c r="CS10" t="n">
+      <c r="CU10" t="n">
         <v>2.2</v>
       </c>
-      <c r="CT10" t="n">
+      <c r="CV10" t="n">
         <v>1.92</v>
-      </c>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="n">
-        <v>1.81</v>
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="n">
         <v>1.48</v>
       </c>
-      <c r="CY10" t="n">
+      <c r="DA10" t="n">
         <v>2.5</v>
       </c>
-      <c r="CZ10" t="n">
+      <c r="DB10" t="n">
         <v>4.83</v>
       </c>
-      <c r="DA10" t="n">
+      <c r="DC10" t="n">
         <v>0.13</v>
       </c>
-      <c r="DB10" t="n">
+      <c r="DD10" t="n">
         <v>2.07</v>
       </c>
-      <c r="DC10" t="n">
+      <c r="DE10" t="n">
         <v>2.06</v>
       </c>
-      <c r="DD10" t="n">
+      <c r="DF10" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="DE10" t="n">
+      <c r="DG10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF10" t="n">
+      <c r="DH10" t="n">
         <v>3.73</v>
       </c>
-      <c r="DG10" t="n">
+      <c r="DI10" t="n">
         <v>4</v>
       </c>
-      <c r="DH10" t="n">
+      <c r="DJ10" t="n">
         <v>0.73</v>
       </c>
-      <c r="DI10" t="n">
+      <c r="DK10" t="n">
         <v>38.06</v>
       </c>
-      <c r="DJ10" t="n">
+      <c r="DL10" t="n">
         <v>1.46</v>
       </c>
-      <c r="DK10" t="n">
+      <c r="DM10" t="n">
         <v>1.93</v>
       </c>
-      <c r="DL10" t="n">
+      <c r="DN10" t="n">
         <v>9.93</v>
       </c>
-      <c r="DM10" t="n">
+      <c r="DO10" t="n">
         <v>11.13</v>
       </c>
-      <c r="DN10" t="n">
+      <c r="DP10" t="n">
         <v>6.13</v>
       </c>
-      <c r="DO10" t="n">
+      <c r="DQ10" t="n">
         <v>0.27</v>
       </c>
-      <c r="DP10" t="n">
+      <c r="DR10" t="n">
         <v>0.27</v>
       </c>
-      <c r="DQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR10" t="n">
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
         <v>51.94</v>
       </c>
-      <c r="DS10" t="n">
+      <c r="DU10" t="n">
         <v>0.53</v>
       </c>
-      <c r="DT10" t="n">
+      <c r="DV10" t="n">
         <v>13.2</v>
       </c>
-      <c r="DU10" t="n">
+      <c r="DW10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="DV10" t="n">
+      <c r="DX10" t="n">
         <v>4</v>
       </c>
-      <c r="DW10" t="n">
+      <c r="DY10" t="n">
         <v>16.53</v>
       </c>
-      <c r="DX10" t="n">
+      <c r="DZ10" t="n">
         <v>1.39</v>
       </c>
-      <c r="DY10" t="n">
+      <c r="EA10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4862,91 +4898,91 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>61.5</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="K11" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>20.17</v>
+        <v>21.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O11" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="P11" t="n">
-        <v>10.83</v>
+        <v>10.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.67</v>
+        <v>47.57</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>10.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.83</v>
+        <v>6.29</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.83</v>
+        <v>15.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5033,70 +5069,70 @@
         <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.71</v>
+        <v>7.87</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY11" t="n">
         <v>3.17</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CC11" t="n">
         <v>7.06</v>
@@ -5108,10 +5144,10 @@
         <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CH11" t="n">
         <v>1.31</v>
@@ -5120,16 +5156,16 @@
         <v>1.66</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
         <v>1.63</v>
@@ -5138,112 +5174,114 @@
         <v>1.39</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="CR11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="n">
         <v>1.68</v>
       </c>
-      <c r="CS11" t="n">
+      <c r="CU11" t="n">
         <v>2.24</v>
       </c>
-      <c r="CT11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CU11" t="n">
+      <c r="CV11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CW11" t="n">
         <v>1.93</v>
       </c>
-      <c r="CV11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CW11" t="n">
+      <c r="CX11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CY11" t="n">
         <v>1.8</v>
       </c>
-      <c r="CX11" t="n">
+      <c r="CZ11" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>4.27</v>
-      </c>
       <c r="DA11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="DC11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DB11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>0.42</v>
-      </c>
       <c r="DD11" t="n">
-        <v>61.57</v>
+        <v>1.73</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.64</v>
+        <v>62.93</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.93</v>
+        <v>0.06</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.14</v>
+        <v>2.6</v>
       </c>
       <c r="DI11" t="n">
-        <v>16.14</v>
+        <v>2.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.79</v>
+        <v>-0.13</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.21</v>
+        <v>17.13</v>
       </c>
       <c r="DL11" t="n">
-        <v>10.07</v>
+        <v>0.74</v>
       </c>
       <c r="DM11" t="n">
-        <v>8.279999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="DN11" t="n">
-        <v>7.64</v>
+        <v>10.06</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.07000000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="DR11" t="n">
-        <v>43.5</v>
+        <v>0.13</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>8.43</v>
+        <v>44.54</v>
       </c>
       <c r="DU11" t="n">
-        <v>5</v>
+        <v>0.26</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.43</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DW11" t="n">
-        <v>14.93</v>
+        <v>5.27</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.89</v>
+        <v>3.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.22</v>
+        <v>15.14</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -5534,106 +5572,108 @@
       <c r="CQ12" t="n">
         <v>3.82</v>
       </c>
-      <c r="CR12" t="n">
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="n">
         <v>1.72</v>
       </c>
-      <c r="CS12" t="n">
+      <c r="CU12" t="n">
         <v>2.15</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.95</v>
       </c>
       <c r="CV12" t="n">
         <v>1.86</v>
       </c>
       <c r="CW12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CY12" t="n">
         <v>1.77</v>
       </c>
-      <c r="CX12" t="n">
+      <c r="CZ12" t="n">
         <v>1.43</v>
       </c>
-      <c r="CY12" t="n">
+      <c r="DA12" t="n">
         <v>2.33</v>
       </c>
-      <c r="CZ12" t="n">
+      <c r="DB12" t="n">
         <v>4.32</v>
       </c>
-      <c r="DA12" t="n">
+      <c r="DC12" t="n">
         <v>0.14</v>
       </c>
-      <c r="DB12" t="n">
+      <c r="DD12" t="n">
         <v>1.8</v>
       </c>
-      <c r="DC12" t="n">
+      <c r="DE12" t="n">
         <v>1.66</v>
       </c>
-      <c r="DD12" t="n">
+      <c r="DF12" t="n">
         <v>98.13</v>
       </c>
-      <c r="DE12" t="n">
+      <c r="DG12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF12" t="n">
+      <c r="DH12" t="n">
         <v>2.47</v>
       </c>
-      <c r="DG12" t="n">
+      <c r="DI12" t="n">
         <v>4.07</v>
       </c>
-      <c r="DH12" t="n">
+      <c r="DJ12" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="DI12" t="n">
+      <c r="DK12" t="n">
         <v>31.34</v>
       </c>
-      <c r="DJ12" t="n">
+      <c r="DL12" t="n">
         <v>0.6</v>
       </c>
-      <c r="DK12" t="n">
+      <c r="DM12" t="n">
         <v>1.8</v>
       </c>
-      <c r="DL12" t="n">
+      <c r="DN12" t="n">
         <v>10.73</v>
       </c>
-      <c r="DM12" t="n">
+      <c r="DO12" t="n">
         <v>10.53</v>
       </c>
-      <c r="DN12" t="n">
+      <c r="DP12" t="n">
         <v>6.2</v>
       </c>
-      <c r="DO12" t="n">
+      <c r="DQ12" t="n">
         <v>0.2</v>
       </c>
-      <c r="DP12" t="n">
+      <c r="DR12" t="n">
         <v>0.2</v>
       </c>
-      <c r="DQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR12" t="n">
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
         <v>53.07</v>
       </c>
-      <c r="DS12" t="n">
+      <c r="DU12" t="n">
         <v>0.2</v>
       </c>
-      <c r="DT12" t="n">
+      <c r="DV12" t="n">
         <v>11.93</v>
       </c>
-      <c r="DU12" t="n">
+      <c r="DW12" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="DV12" t="n">
+      <c r="DX12" t="n">
         <v>3.8</v>
       </c>
-      <c r="DW12" t="n">
+      <c r="DY12" t="n">
         <v>17.8</v>
       </c>
-      <c r="DX12" t="n">
+      <c r="DZ12" t="n">
         <v>1.26</v>
       </c>
-      <c r="DY12" t="n">
+      <c r="EA12" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -5925,106 +5965,108 @@
       <c r="CQ13" t="n">
         <v>3.78</v>
       </c>
-      <c r="CR13" t="n">
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>1.8</v>
       </c>
       <c r="CU13" t="n">
         <v>1.92</v>
       </c>
       <c r="CV13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CX13" t="n">
         <v>1.93</v>
       </c>
-      <c r="CW13" t="n">
+      <c r="CY13" t="n">
         <v>1.81</v>
       </c>
-      <c r="CX13" t="n">
+      <c r="CZ13" t="n">
         <v>1.36</v>
       </c>
-      <c r="CY13" t="n">
+      <c r="DA13" t="n">
         <v>2.13</v>
       </c>
-      <c r="CZ13" t="n">
+      <c r="DB13" t="n">
         <v>3.82</v>
       </c>
-      <c r="DA13" t="n">
+      <c r="DC13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DB13" t="n">
+      <c r="DD13" t="n">
         <v>1.36</v>
       </c>
-      <c r="DC13" t="n">
+      <c r="DE13" t="n">
         <v>1.93</v>
       </c>
-      <c r="DD13" t="n">
+      <c r="DF13" t="n">
         <v>87.92</v>
       </c>
-      <c r="DE13" t="n">
+      <c r="DG13" t="n">
         <v>0.29</v>
       </c>
-      <c r="DF13" t="n">
+      <c r="DH13" t="n">
         <v>3.07</v>
       </c>
-      <c r="DG13" t="n">
+      <c r="DI13" t="n">
         <v>5.71</v>
       </c>
-      <c r="DH13" t="n">
+      <c r="DJ13" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="DI13" t="n">
+      <c r="DK13" t="n">
         <v>33.07</v>
       </c>
-      <c r="DJ13" t="n">
+      <c r="DL13" t="n">
         <v>1.57</v>
       </c>
-      <c r="DK13" t="n">
+      <c r="DM13" t="n">
         <v>1.57</v>
       </c>
-      <c r="DL13" t="n">
+      <c r="DN13" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="DM13" t="n">
+      <c r="DO13" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="DN13" t="n">
+      <c r="DP13" t="n">
         <v>5.36</v>
       </c>
-      <c r="DO13" t="n">
+      <c r="DQ13" t="n">
         <v>0.21</v>
       </c>
-      <c r="DP13" t="n">
+      <c r="DR13" t="n">
         <v>0.21</v>
       </c>
-      <c r="DQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR13" t="n">
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
         <v>51.86</v>
       </c>
-      <c r="DS13" t="n">
+      <c r="DU13" t="n">
         <v>0.29</v>
       </c>
-      <c r="DT13" t="n">
+      <c r="DV13" t="n">
         <v>15.28</v>
       </c>
-      <c r="DU13" t="n">
+      <c r="DW13" t="n">
         <v>10.5</v>
       </c>
-      <c r="DV13" t="n">
+      <c r="DX13" t="n">
         <v>4.79</v>
       </c>
-      <c r="DW13" t="n">
+      <c r="DY13" t="n">
         <v>15.64</v>
       </c>
-      <c r="DX13" t="n">
+      <c r="DZ13" t="n">
         <v>1.54</v>
       </c>
-      <c r="DY13" t="n">
+      <c r="EA13" t="n">
         <v>2.64</v>
       </c>
     </row>
@@ -6035,13 +6077,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6128,49 +6170,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>21.71</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.29</v>
+        <v>13.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.43</v>
+        <v>6.38</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6182,82 +6224,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>43.14</v>
+        <v>43.88</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.29</v>
+        <v>10.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="BD14" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.93</v>
+        <v>8.75</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>3.1</v>
@@ -6266,157 +6308,163 @@
         <v>3.28</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.37</v>
+        <v>3.54</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.67</v>
+        <v>6.18</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.31</v>
+        <v>6.87</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.08</v>
+        <v>3.95</v>
       </c>
       <c r="CR14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CT14" t="n">
         <v>1.74</v>
       </c>
-      <c r="CS14" t="n">
+      <c r="CU14" t="n">
         <v>2.11</v>
       </c>
-      <c r="CT14" t="n">
+      <c r="CV14" t="n">
         <v>1.83</v>
       </c>
-      <c r="CU14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CV14" t="n">
+      <c r="CW14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CX14" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.39</v>
-      </c>
       <c r="CY14" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="CZ14" t="n">
-        <v>4.14</v>
+        <v>1.37</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="DB14" t="n">
-        <v>2.4</v>
+        <v>3.99</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>68.27</v>
+        <v>2.31</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="DF14" t="n">
-        <v>3.47</v>
+        <v>68</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.2</v>
+        <v>3.38</v>
       </c>
       <c r="DI14" t="n">
-        <v>19.93</v>
+        <v>4.06</v>
       </c>
       <c r="DJ14" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="DL14" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="DK14" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>9.470000000000001</v>
-      </c>
       <c r="DM14" t="n">
-        <v>10.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DN14" t="n">
-        <v>5</v>
+        <v>9.25</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.13</v>
+        <v>10.38</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.13</v>
+        <v>5.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>45.2</v>
+        <v>0.12</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
-        <v>10.73</v>
+        <v>45.44</v>
       </c>
       <c r="DU14" t="n">
-        <v>7.53</v>
+        <v>0.19</v>
       </c>
       <c r="DV14" t="n">
-        <v>3.2</v>
+        <v>10.68</v>
       </c>
       <c r="DW14" t="n">
-        <v>10.2</v>
+        <v>7.62</v>
       </c>
       <c r="DX14" t="n">
-        <v>1.05</v>
+        <v>3.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.14</v>
+        <v>10.12</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>3.06</v>
       </c>
     </row>
     <row r="15">
@@ -6707,106 +6755,108 @@
       <c r="CQ15" t="n">
         <v>3.65</v>
       </c>
-      <c r="CR15" t="n">
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="n">
         <v>1.89</v>
       </c>
-      <c r="CS15" t="n">
+      <c r="CU15" t="n">
         <v>1.95</v>
       </c>
-      <c r="CT15" t="n">
+      <c r="CV15" t="n">
         <v>1.76</v>
       </c>
-      <c r="CU15" t="n">
+      <c r="CW15" t="n">
         <v>1.87</v>
       </c>
-      <c r="CV15" t="n">
+      <c r="CX15" t="n">
         <v>1.97</v>
       </c>
-      <c r="CW15" t="n">
+      <c r="CY15" t="n">
         <v>1.86</v>
       </c>
-      <c r="CX15" t="n">
+      <c r="CZ15" t="n">
         <v>1.34</v>
       </c>
-      <c r="CY15" t="n">
+      <c r="DA15" t="n">
         <v>2.07</v>
       </c>
-      <c r="CZ15" t="n">
+      <c r="DB15" t="n">
         <v>3.68</v>
       </c>
-      <c r="DA15" t="n">
+      <c r="DC15" t="n">
         <v>0.13</v>
       </c>
-      <c r="DB15" t="n">
+      <c r="DD15" t="n">
         <v>1.6</v>
       </c>
-      <c r="DC15" t="n">
+      <c r="DE15" t="n">
         <v>1.6</v>
       </c>
-      <c r="DD15" t="n">
+      <c r="DF15" t="n">
         <v>93.27</v>
       </c>
-      <c r="DE15" t="n">
+      <c r="DG15" t="n">
         <v>0.13</v>
       </c>
-      <c r="DF15" t="n">
+      <c r="DH15" t="n">
         <v>2.67</v>
       </c>
-      <c r="DG15" t="n">
+      <c r="DI15" t="n">
         <v>5.33</v>
       </c>
-      <c r="DH15" t="n">
+      <c r="DJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DI15" t="n">
+      <c r="DK15" t="n">
         <v>36</v>
       </c>
-      <c r="DJ15" t="n">
+      <c r="DL15" t="n">
         <v>1</v>
       </c>
-      <c r="DK15" t="n">
+      <c r="DM15" t="n">
         <v>2.14</v>
       </c>
-      <c r="DL15" t="n">
+      <c r="DN15" t="n">
         <v>11</v>
       </c>
-      <c r="DM15" t="n">
+      <c r="DO15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="DN15" t="n">
+      <c r="DP15" t="n">
         <v>6.2</v>
       </c>
-      <c r="DO15" t="n">
+      <c r="DQ15" t="n">
         <v>0.33</v>
       </c>
-      <c r="DP15" t="n">
+      <c r="DR15" t="n">
         <v>0.33</v>
       </c>
-      <c r="DQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR15" t="n">
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
         <v>55.2</v>
       </c>
-      <c r="DS15" t="n">
+      <c r="DU15" t="n">
         <v>0.06</v>
       </c>
-      <c r="DT15" t="n">
+      <c r="DV15" t="n">
         <v>13.07</v>
       </c>
-      <c r="DU15" t="n">
+      <c r="DW15" t="n">
         <v>8.4</v>
       </c>
-      <c r="DV15" t="n">
+      <c r="DX15" t="n">
         <v>4.67</v>
       </c>
-      <c r="DW15" t="n">
+      <c r="DY15" t="n">
         <v>14.87</v>
       </c>
-      <c r="DX15" t="n">
+      <c r="DZ15" t="n">
         <v>1.42</v>
       </c>
-      <c r="DY15" t="n">
+      <c r="EA15" t="n">
         <v>2.53</v>
       </c>
     </row>
@@ -7098,106 +7148,108 @@
       <c r="CQ16" t="n">
         <v>3.83</v>
       </c>
-      <c r="CR16" t="n">
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="n">
         <v>1.77</v>
       </c>
-      <c r="CS16" t="n">
+      <c r="CU16" t="n">
         <v>2.07</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>1.93</v>
       </c>
       <c r="CV16" t="n">
         <v>1.86</v>
       </c>
       <c r="CW16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CY16" t="n">
         <v>1.79</v>
       </c>
-      <c r="CX16" t="n">
+      <c r="CZ16" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY16" t="n">
+      <c r="DA16" t="n">
         <v>2.35</v>
       </c>
-      <c r="CZ16" t="n">
+      <c r="DB16" t="n">
         <v>4.43</v>
       </c>
-      <c r="DA16" t="n">
+      <c r="DC16" t="n">
         <v>0.2</v>
       </c>
-      <c r="DB16" t="n">
+      <c r="DD16" t="n">
         <v>1.47</v>
       </c>
-      <c r="DC16" t="n">
+      <c r="DE16" t="n">
         <v>1.6</v>
       </c>
-      <c r="DD16" t="n">
+      <c r="DF16" t="n">
         <v>88.27</v>
       </c>
-      <c r="DE16" t="n">
+      <c r="DG16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF16" t="n">
+      <c r="DH16" t="n">
         <v>2.73</v>
       </c>
-      <c r="DG16" t="n">
+      <c r="DI16" t="n">
         <v>4.8</v>
       </c>
-      <c r="DH16" t="n">
+      <c r="DJ16" t="n">
         <v>0.13</v>
       </c>
-      <c r="DI16" t="n">
+      <c r="DK16" t="n">
         <v>30.66</v>
       </c>
-      <c r="DJ16" t="n">
+      <c r="DL16" t="n">
         <v>1.2</v>
       </c>
-      <c r="DK16" t="n">
+      <c r="DM16" t="n">
         <v>1.33</v>
       </c>
-      <c r="DL16" t="n">
+      <c r="DN16" t="n">
         <v>11.54</v>
       </c>
-      <c r="DM16" t="n">
+      <c r="DO16" t="n">
         <v>8.34</v>
       </c>
-      <c r="DN16" t="n">
+      <c r="DP16" t="n">
         <v>7.2</v>
       </c>
-      <c r="DO16" t="n">
+      <c r="DQ16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DP16" t="n">
+      <c r="DR16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR16" t="n">
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
         <v>46.94</v>
       </c>
-      <c r="DS16" t="n">
+      <c r="DU16" t="n">
         <v>0.06</v>
       </c>
-      <c r="DT16" t="n">
+      <c r="DV16" t="n">
         <v>13.26</v>
       </c>
-      <c r="DU16" t="n">
+      <c r="DW16" t="n">
         <v>8.73</v>
       </c>
-      <c r="DV16" t="n">
+      <c r="DX16" t="n">
         <v>4.54</v>
       </c>
-      <c r="DW16" t="n">
+      <c r="DY16" t="n">
         <v>17.93</v>
       </c>
-      <c r="DX16" t="n">
+      <c r="DZ16" t="n">
         <v>1.38</v>
       </c>
-      <c r="DY16" t="n">
+      <c r="EA16" t="n">
         <v>2.6</v>
       </c>
     </row>
@@ -7489,106 +7541,108 @@
       <c r="CQ17" t="n">
         <v>4.07</v>
       </c>
-      <c r="CR17" t="n">
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="n">
         <v>1.73</v>
       </c>
-      <c r="CS17" t="n">
+      <c r="CU17" t="n">
         <v>2.13</v>
       </c>
-      <c r="CT17" t="n">
+      <c r="CV17" t="n">
         <v>1.82</v>
       </c>
-      <c r="CU17" t="n">
+      <c r="CW17" t="n">
         <v>1.88</v>
       </c>
-      <c r="CV17" t="n">
+      <c r="CX17" t="n">
         <v>1.91</v>
       </c>
-      <c r="CW17" t="n">
+      <c r="CY17" t="n">
         <v>1.84</v>
       </c>
-      <c r="CX17" t="n">
+      <c r="CZ17" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY17" t="n">
+      <c r="DA17" t="n">
         <v>2.35</v>
       </c>
-      <c r="CZ17" t="n">
+      <c r="DB17" t="n">
         <v>4.39</v>
       </c>
-      <c r="DA17" t="n">
+      <c r="DC17" t="n">
         <v>0.06</v>
       </c>
-      <c r="DB17" t="n">
+      <c r="DD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="DC17" t="n">
+      <c r="DE17" t="n">
         <v>0.67</v>
       </c>
-      <c r="DD17" t="n">
+      <c r="DF17" t="n">
         <v>83.73</v>
       </c>
-      <c r="DE17" t="n">
+      <c r="DG17" t="n">
         <v>0.27</v>
       </c>
-      <c r="DF17" t="n">
+      <c r="DH17" t="n">
         <v>2.67</v>
       </c>
-      <c r="DG17" t="n">
+      <c r="DI17" t="n">
         <v>4.6</v>
       </c>
-      <c r="DH17" t="n">
+      <c r="DJ17" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="DI17" t="n">
+      <c r="DK17" t="n">
         <v>35.06</v>
       </c>
-      <c r="DJ17" t="n">
+      <c r="DL17" t="n">
         <v>1.13</v>
       </c>
-      <c r="DK17" t="n">
+      <c r="DM17" t="n">
         <v>1.4</v>
       </c>
-      <c r="DL17" t="n">
+      <c r="DN17" t="n">
         <v>10.33</v>
       </c>
-      <c r="DM17" t="n">
+      <c r="DO17" t="n">
         <v>8.26</v>
       </c>
-      <c r="DN17" t="n">
+      <c r="DP17" t="n">
         <v>6.6</v>
       </c>
-      <c r="DO17" t="n">
+      <c r="DQ17" t="n">
         <v>0.27</v>
       </c>
-      <c r="DP17" t="n">
+      <c r="DR17" t="n">
         <v>0.27</v>
       </c>
-      <c r="DQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR17" t="n">
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
         <v>46.93</v>
       </c>
-      <c r="DS17" t="n">
+      <c r="DU17" t="n">
         <v>0.27</v>
       </c>
-      <c r="DT17" t="n">
+      <c r="DV17" t="n">
         <v>10.13</v>
       </c>
-      <c r="DU17" t="n">
+      <c r="DW17" t="n">
         <v>6.93</v>
       </c>
-      <c r="DV17" t="n">
+      <c r="DX17" t="n">
         <v>3.2</v>
       </c>
-      <c r="DW17" t="n">
+      <c r="DY17" t="n">
         <v>16.27</v>
       </c>
-      <c r="DX17" t="n">
+      <c r="DZ17" t="n">
         <v>1.12</v>
       </c>
-      <c r="DY17" t="n">
+      <c r="EA17" t="n">
         <v>2.27</v>
       </c>
     </row>
@@ -7880,106 +7934,108 @@
       <c r="CQ18" t="n">
         <v>3.78</v>
       </c>
-      <c r="CR18" t="n">
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="n">
         <v>1.8</v>
       </c>
-      <c r="CS18" t="n">
+      <c r="CU18" t="n">
         <v>2.07</v>
       </c>
-      <c r="CT18" t="n">
+      <c r="CV18" t="n">
         <v>1.82</v>
       </c>
-      <c r="CU18" t="n">
+      <c r="CW18" t="n">
         <v>1.91</v>
       </c>
-      <c r="CV18" t="n">
+      <c r="CX18" t="n">
         <v>1.91</v>
       </c>
-      <c r="CW18" t="n">
+      <c r="CY18" t="n">
         <v>1.81</v>
       </c>
-      <c r="CX18" t="n">
+      <c r="CZ18" t="n">
         <v>1.37</v>
       </c>
-      <c r="CY18" t="n">
+      <c r="DA18" t="n">
         <v>2.18</v>
       </c>
-      <c r="CZ18" t="n">
+      <c r="DB18" t="n">
         <v>3.93</v>
       </c>
-      <c r="DA18" t="n">
+      <c r="DC18" t="n">
         <v>0.13</v>
       </c>
-      <c r="DB18" t="n">
+      <c r="DD18" t="n">
         <v>2.13</v>
       </c>
-      <c r="DC18" t="n">
+      <c r="DE18" t="n">
         <v>2.07</v>
       </c>
-      <c r="DD18" t="n">
+      <c r="DF18" t="n">
         <v>78</v>
       </c>
-      <c r="DE18" t="n">
+      <c r="DG18" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF18" t="n">
+      <c r="DH18" t="n">
         <v>3.33</v>
       </c>
-      <c r="DG18" t="n">
+      <c r="DI18" t="n">
         <v>5.6</v>
       </c>
-      <c r="DH18" t="n">
+      <c r="DJ18" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DI18" t="n">
+      <c r="DK18" t="n">
         <v>29.67</v>
       </c>
-      <c r="DJ18" t="n">
+      <c r="DL18" t="n">
         <v>1.07</v>
       </c>
-      <c r="DK18" t="n">
+      <c r="DM18" t="n">
         <v>1.53</v>
       </c>
-      <c r="DL18" t="n">
+      <c r="DN18" t="n">
         <v>10.06</v>
       </c>
-      <c r="DM18" t="n">
+      <c r="DO18" t="n">
         <v>7.2</v>
       </c>
-      <c r="DN18" t="n">
+      <c r="DP18" t="n">
         <v>6.4</v>
       </c>
-      <c r="DO18" t="n">
+      <c r="DQ18" t="n">
         <v>0.13</v>
       </c>
-      <c r="DP18" t="n">
+      <c r="DR18" t="n">
         <v>0.13</v>
       </c>
-      <c r="DQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR18" t="n">
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
         <v>46.6</v>
       </c>
-      <c r="DS18" t="n">
+      <c r="DU18" t="n">
         <v>0.2</v>
       </c>
-      <c r="DT18" t="n">
+      <c r="DV18" t="n">
         <v>16</v>
       </c>
-      <c r="DU18" t="n">
+      <c r="DW18" t="n">
         <v>10.73</v>
       </c>
-      <c r="DV18" t="n">
+      <c r="DX18" t="n">
         <v>5.26</v>
       </c>
-      <c r="DW18" t="n">
+      <c r="DY18" t="n">
         <v>17.07</v>
       </c>
-      <c r="DX18" t="n">
+      <c r="DZ18" t="n">
         <v>1.59</v>
       </c>
-      <c r="DY18" t="n">
+      <c r="EA18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8271,106 +8327,108 @@
       <c r="CQ19" t="n">
         <v>3.65</v>
       </c>
-      <c r="CR19" t="n">
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="n">
         <v>1.9</v>
       </c>
-      <c r="CS19" t="n">
+      <c r="CU19" t="n">
         <v>1.92</v>
       </c>
-      <c r="CT19" t="n">
+      <c r="CV19" t="n">
         <v>1.84</v>
       </c>
-      <c r="CU19" t="n">
+      <c r="CW19" t="n">
         <v>1.87</v>
       </c>
-      <c r="CV19" t="n">
+      <c r="CX19" t="n">
         <v>1.88</v>
       </c>
-      <c r="CW19" t="n">
+      <c r="CY19" t="n">
         <v>1.86</v>
       </c>
-      <c r="CX19" t="n">
+      <c r="CZ19" t="n">
         <v>1.34</v>
       </c>
-      <c r="CY19" t="n">
+      <c r="DA19" t="n">
         <v>2.11</v>
       </c>
-      <c r="CZ19" t="n">
+      <c r="DB19" t="n">
         <v>3.74</v>
       </c>
-      <c r="DA19" t="n">
+      <c r="DC19" t="n">
         <v>0.34</v>
       </c>
-      <c r="DB19" t="n">
+      <c r="DD19" t="n">
         <v>2.2</v>
       </c>
-      <c r="DC19" t="n">
+      <c r="DE19" t="n">
         <v>2.67</v>
       </c>
-      <c r="DD19" t="n">
+      <c r="DF19" t="n">
         <v>91.06999999999999</v>
       </c>
-      <c r="DE19" t="n">
+      <c r="DG19" t="n">
         <v>0.13</v>
       </c>
-      <c r="DF19" t="n">
+      <c r="DH19" t="n">
         <v>3.07</v>
       </c>
-      <c r="DG19" t="n">
+      <c r="DI19" t="n">
         <v>5.07</v>
       </c>
-      <c r="DH19" t="n">
+      <c r="DJ19" t="n">
         <v>0.27</v>
       </c>
-      <c r="DI19" t="n">
+      <c r="DK19" t="n">
         <v>38.73</v>
       </c>
-      <c r="DJ19" t="n">
+      <c r="DL19" t="n">
         <v>0.87</v>
       </c>
-      <c r="DK19" t="n">
+      <c r="DM19" t="n">
         <v>1.6</v>
       </c>
-      <c r="DL19" t="n">
+      <c r="DN19" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="DM19" t="n">
+      <c r="DO19" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="DN19" t="n">
+      <c r="DP19" t="n">
         <v>6.54</v>
       </c>
-      <c r="DO19" t="n">
+      <c r="DQ19" t="n">
         <v>0.2</v>
       </c>
-      <c r="DP19" t="n">
+      <c r="DR19" t="n">
         <v>0.2</v>
       </c>
-      <c r="DQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR19" t="n">
+      <c r="DS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="n">
         <v>52.14</v>
       </c>
-      <c r="DS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT19" t="n">
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
         <v>13.6</v>
       </c>
-      <c r="DU19" t="n">
+      <c r="DW19" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="DV19" t="n">
+      <c r="DX19" t="n">
         <v>5.07</v>
       </c>
-      <c r="DW19" t="n">
+      <c r="DY19" t="n">
         <v>12.6</v>
       </c>
-      <c r="DX19" t="n">
+      <c r="DZ19" t="n">
         <v>1.5</v>
       </c>
-      <c r="DY19" t="n">
+      <c r="EA19" t="n">
         <v>3.07</v>
       </c>
     </row>
@@ -8662,106 +8720,108 @@
       <c r="CQ20" t="n">
         <v>4.28</v>
       </c>
-      <c r="CR20" t="n">
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="inlineStr"/>
+      <c r="CT20" t="n">
         <v>1.79</v>
       </c>
-      <c r="CS20" t="n">
+      <c r="CU20" t="n">
         <v>2.04</v>
       </c>
-      <c r="CT20" t="n">
+      <c r="CV20" t="n">
         <v>1.77</v>
       </c>
-      <c r="CU20" t="n">
+      <c r="CW20" t="n">
         <v>1.91</v>
       </c>
-      <c r="CV20" t="n">
+      <c r="CX20" t="n">
         <v>1.94</v>
       </c>
-      <c r="CW20" t="n">
+      <c r="CY20" t="n">
         <v>1.82</v>
       </c>
-      <c r="CX20" t="n">
+      <c r="CZ20" t="n">
         <v>1.42</v>
       </c>
-      <c r="CY20" t="n">
+      <c r="DA20" t="n">
         <v>2.35</v>
       </c>
-      <c r="CZ20" t="n">
+      <c r="DB20" t="n">
         <v>4.41</v>
       </c>
-      <c r="DA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB20" t="n">
+      <c r="DC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD20" t="n">
         <v>1.86</v>
       </c>
-      <c r="DC20" t="n">
+      <c r="DE20" t="n">
         <v>2.43</v>
       </c>
-      <c r="DD20" t="n">
+      <c r="DF20" t="n">
         <v>87.70999999999999</v>
       </c>
-      <c r="DE20" t="n">
+      <c r="DG20" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF20" t="n">
+      <c r="DH20" t="n">
         <v>2.5</v>
       </c>
-      <c r="DG20" t="n">
+      <c r="DI20" t="n">
         <v>4.28</v>
       </c>
-      <c r="DH20" t="n">
+      <c r="DJ20" t="n">
         <v>0.36</v>
       </c>
-      <c r="DI20" t="n">
+      <c r="DK20" t="n">
         <v>38.29</v>
       </c>
-      <c r="DJ20" t="n">
+      <c r="DL20" t="n">
         <v>0.64</v>
       </c>
-      <c r="DK20" t="n">
+      <c r="DM20" t="n">
         <v>1.86</v>
       </c>
-      <c r="DL20" t="n">
+      <c r="DN20" t="n">
         <v>10.5</v>
       </c>
-      <c r="DM20" t="n">
+      <c r="DO20" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="DN20" t="n">
+      <c r="DP20" t="n">
         <v>7.92</v>
       </c>
-      <c r="DO20" t="n">
+      <c r="DQ20" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DP20" t="n">
+      <c r="DR20" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR20" t="n">
+      <c r="DS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT20" t="n">
         <v>47</v>
       </c>
-      <c r="DS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT20" t="n">
+      <c r="DU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="n">
         <v>11.36</v>
       </c>
-      <c r="DU20" t="n">
+      <c r="DW20" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="DV20" t="n">
+      <c r="DX20" t="n">
         <v>3</v>
       </c>
-      <c r="DW20" t="n">
+      <c r="DY20" t="n">
         <v>16.29</v>
       </c>
-      <c r="DX20" t="n">
+      <c r="DZ20" t="n">
         <v>1.21</v>
       </c>
-      <c r="DY20" t="n">
+      <c r="EA20" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -8868,7 +8928,7 @@
         <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI21" t="n">
         <v>91.38</v>
@@ -8880,10 +8940,10 @@
         <v>2.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.25</v>
+        <v>-0.12</v>
       </c>
       <c r="AN21" t="n">
         <v>28.12</v>
@@ -8892,7 +8952,7 @@
         <v>0.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AQ21" t="n">
         <v>10.38</v>
@@ -8946,7 +9006,7 @@
         <v>2.47</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="BI21" t="n">
         <v>2.47</v>
@@ -8970,10 +9030,10 @@
         <v>0.93</v>
       </c>
       <c r="BP21" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
@@ -9053,106 +9113,108 @@
       <c r="CQ21" t="n">
         <v>3.78</v>
       </c>
-      <c r="CR21" t="n">
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr"/>
+      <c r="CT21" t="n">
         <v>1.76</v>
       </c>
-      <c r="CS21" t="n">
+      <c r="CU21" t="n">
         <v>2.13</v>
       </c>
-      <c r="CT21" t="n">
+      <c r="CV21" t="n">
         <v>1.83</v>
       </c>
-      <c r="CU21" t="n">
+      <c r="CW21" t="n">
         <v>1.92</v>
       </c>
-      <c r="CV21" t="n">
+      <c r="CX21" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW21" t="n">
+      <c r="CY21" t="n">
         <v>1.82</v>
       </c>
-      <c r="CX21" t="n">
+      <c r="CZ21" t="n">
         <v>1.41</v>
       </c>
-      <c r="CY21" t="n">
+      <c r="DA21" t="n">
         <v>2.31</v>
       </c>
-      <c r="CZ21" t="n">
+      <c r="DB21" t="n">
         <v>4.26</v>
       </c>
-      <c r="DA21" t="n">
+      <c r="DC21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DB21" t="n">
+      <c r="DD21" t="n">
         <v>1.87</v>
       </c>
-      <c r="DC21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DD21" t="n">
+      <c r="DE21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DF21" t="n">
         <v>91</v>
       </c>
-      <c r="DE21" t="n">
+      <c r="DG21" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DF21" t="n">
+      <c r="DH21" t="n">
         <v>3</v>
       </c>
-      <c r="DG21" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="DH21" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="DI21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="DK21" t="n">
         <v>31.8</v>
       </c>
-      <c r="DJ21" t="n">
+      <c r="DL21" t="n">
         <v>1.07</v>
       </c>
-      <c r="DK21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DL21" t="n">
+      <c r="DM21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN21" t="n">
         <v>11.8</v>
       </c>
-      <c r="DM21" t="n">
+      <c r="DO21" t="n">
         <v>8.34</v>
       </c>
-      <c r="DN21" t="n">
+      <c r="DP21" t="n">
         <v>7.07</v>
       </c>
-      <c r="DO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP21" t="n">
-        <v>0</v>
-      </c>
       <c r="DQ21" t="n">
         <v>0</v>
       </c>
       <c r="DR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT21" t="n">
         <v>49.07</v>
       </c>
-      <c r="DS21" t="n">
+      <c r="DU21" t="n">
         <v>0.26</v>
       </c>
-      <c r="DT21" t="n">
+      <c r="DV21" t="n">
         <v>13.54</v>
       </c>
-      <c r="DU21" t="n">
+      <c r="DW21" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="DV21" t="n">
+      <c r="DX21" t="n">
         <v>5.06</v>
       </c>
-      <c r="DW21" t="n">
+      <c r="DY21" t="n">
         <v>15.53</v>
       </c>
-      <c r="DX21" t="n">
+      <c r="DZ21" t="n">
         <v>1.44</v>
       </c>
-      <c r="DY21" t="n">
+      <c r="EA21" t="n">
         <v>2.67</v>
       </c>
     </row>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2244,49 +2244,49 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" t="n">
-        <v>94.29000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
         <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>29.86</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2298,82 +2298,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.71</v>
+        <v>50</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.86</v>
+        <v>11.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.57</v>
+        <v>17.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BR4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
         <v>1.83</v>
@@ -2382,43 +2382,43 @@
         <v>1.87</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC4" t="n">
         <v>3.01</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CH4" t="n">
         <v>1.28</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.09</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN4" t="n">
         <v>1.61</v>
@@ -2430,78 +2430,78 @@
         <v>2.41</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CU4" t="n">
         <v>2.13</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW4" t="n">
         <v>1.84</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY4" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DB4" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DE4" t="n">
         <v>1.86</v>
       </c>
       <c r="DF4" t="n">
-        <v>99.86</v>
+        <v>99.73</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DI4" t="n">
-        <v>4.78</v>
+        <v>4.86</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.14</v>
       </c>
       <c r="DK4" t="n">
-        <v>36.57</v>
+        <v>38.34</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="DN4" t="n">
-        <v>11.42</v>
+        <v>11.67</v>
       </c>
       <c r="DO4" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.07</v>
+        <v>6.87</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
@@ -2513,28 +2513,28 @@
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>52.21</v>
+        <v>52.66</v>
       </c>
       <c r="DU4" t="n">
         <v>0.14</v>
       </c>
       <c r="DV4" t="n">
-        <v>12.5</v>
+        <v>12.73</v>
       </c>
       <c r="DW4" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="DY4" t="n">
-        <v>16.93</v>
+        <v>17.47</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH14" t="n">
         <v>1.62</v>
@@ -6182,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AL14" t="n">
         <v>3</v>
@@ -6245,7 +6245,7 @@
         <v>0.99</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="BG14" t="n">
         <v>2.62</v>
@@ -6395,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="DE14" t="n">
         <v>1.31</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="DI14" t="n">
         <v>4.06</v>
@@ -6464,7 +6464,7 @@
         <v>1.04</v>
       </c>
       <c r="EA14" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="15">
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -8454,79 +8454,79 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>97.70999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="I20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>5.57</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M20" t="n">
-        <v>49.43</v>
+        <v>45.88</v>
       </c>
       <c r="N20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>12.29</v>
+        <v>11.75</v>
       </c>
       <c r="Q20" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>13</v>
       </c>
-      <c r="R20" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>14.14</v>
-      </c>
       <c r="AA20" t="n">
-        <v>10.43</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.29</v>
+        <v>17.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8610,61 +8610,61 @@
         <v>2.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.43</v>
+        <v>8.33</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="BR20" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS20" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT20" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU20" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BZ20" t="n">
         <v>2.69</v>
@@ -8673,7 +8673,7 @@
         <v>2.87</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC20" t="n">
         <v>3.32</v>
@@ -8682,13 +8682,13 @@
         <v>3.83</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
@@ -8709,16 +8709,16 @@
         <v>2.12</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
@@ -8735,19 +8735,19 @@
         <v>1.91</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CY20" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DB20" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="DC20" t="n">
         <v>0</v>
@@ -8756,40 +8756,40 @@
         <v>1.86</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="DF20" t="n">
-        <v>87.70999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="DG20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DH20" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DI20" t="n">
-        <v>4.28</v>
+        <v>4.07</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DK20" t="n">
-        <v>38.29</v>
+        <v>37.13</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DN20" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="DO20" t="n">
-        <v>9.859999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="DP20" t="n">
-        <v>7.92</v>
+        <v>8.27</v>
       </c>
       <c r="DQ20" t="n">
         <v>0.07000000000000001</v>
@@ -8801,28 +8801,28 @@
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>47</v>
+        <v>46.6</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>11.36</v>
+        <v>10.93</v>
       </c>
       <c r="DW20" t="n">
-        <v>8.359999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DX20" t="n">
         <v>3</v>
       </c>
       <c r="DY20" t="n">
-        <v>16.29</v>
+        <v>16.27</v>
       </c>
       <c r="DZ20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="EA20" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2274,10 +2274,10 @@
         <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AS4" t="n">
         <v>7.25</v>
@@ -2298,25 +2298,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>50</v>
+        <v>49.88</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.5</v>
+        <v>11.62</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.75</v>
+        <v>7.88</v>
       </c>
       <c r="BC4" t="n">
         <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.62</v>
+        <v>17.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
@@ -2495,10 +2495,10 @@
         <v>2.07</v>
       </c>
       <c r="DN4" t="n">
-        <v>11.67</v>
+        <v>11.73</v>
       </c>
       <c r="DO4" t="n">
-        <v>10.6</v>
+        <v>10.66</v>
       </c>
       <c r="DP4" t="n">
         <v>6.87</v>
@@ -2513,25 +2513,25 @@
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>52.66</v>
+        <v>52.6</v>
       </c>
       <c r="DU4" t="n">
         <v>0.14</v>
       </c>
       <c r="DV4" t="n">
-        <v>12.73</v>
+        <v>12.8</v>
       </c>
       <c r="DW4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DX4" t="n">
         <v>3.93</v>
       </c>
       <c r="DY4" t="n">
-        <v>17.47</v>
+        <v>17.6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EA4" t="n">
         <v>2.47</v>
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2634,139 +2634,139 @@
         <v>2.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>83.56999999999999</v>
+        <v>84.88</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.71</v>
+        <v>30.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.14</v>
+        <v>11.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.14</v>
+        <v>9.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.14</v>
+        <v>55.62</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.14</v>
+        <v>13.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.86</v>
+        <v>15.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY5" t="n">
         <v>1.16</v>
@@ -2775,10 +2775,10 @@
         <v>1.39</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
       <c r="CC5" t="n">
         <v>2.08</v>
@@ -2793,28 +2793,28 @@
         <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH5" t="n">
         <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO5" t="n">
         <v>1.25</v>
@@ -2823,7 +2823,7 @@
         <v>1.84</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CR5" t="n">
         <v>1.96</v>
@@ -2832,7 +2832,7 @@
         <v>1.77</v>
       </c>
       <c r="CT5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CU5" t="n">
         <v>1.94</v>
@@ -2843,91 +2843,91 @@
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DA5" t="n">
         <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DE5" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="DF5" t="n">
-        <v>90.53</v>
+        <v>90.75</v>
       </c>
       <c r="DG5" t="n">
         <v>0.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="DI5" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="DK5" t="n">
-        <v>33.26</v>
+        <v>33.12</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>10.73</v>
+        <v>10.56</v>
       </c>
       <c r="DO5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>56.27</v>
+        <v>56.44</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DV5" t="n">
-        <v>16.33</v>
+        <v>16.31</v>
       </c>
       <c r="DW5" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="DX5" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="DY5" t="n">
-        <v>17.27</v>
+        <v>17.38</v>
       </c>
       <c r="DZ5" t="n">
         <v>1.7</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="6">
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3813,52 +3813,52 @@
         <v>2.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>74.70999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.29</v>
+        <v>26.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.86</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3870,82 +3870,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.71</v>
+        <v>47.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>14.29</v>
+        <v>15.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.8</v>
@@ -3954,22 +3954,22 @@
         <v>1.9</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="CE8" t="n">
         <v>1.45</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG8" t="n">
         <v>2.51</v>
@@ -3981,13 +3981,13 @@
         <v>1.71</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK8" t="n">
         <v>1.76</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CM8" t="n">
         <v>1.98</v>
@@ -3996,13 +3996,13 @@
         <v>1.59</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="inlineStr"/>
@@ -4013,100 +4013,100 @@
         <v>2.09</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW8" t="n">
         <v>1.8</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CY8" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DB8" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DF8" t="n">
-        <v>90</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DH8" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="DI8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DK8" t="n">
         <v>33</v>
       </c>
       <c r="DL8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DM8" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>10.47</v>
+        <v>10.88</v>
       </c>
       <c r="DO8" t="n">
-        <v>8.470000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>56.4</v>
+        <v>55.81</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DV8" t="n">
-        <v>13.53</v>
+        <v>13.25</v>
       </c>
       <c r="DW8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="DX8" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="DY8" t="n">
-        <v>15.74</v>
+        <v>16.38</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="9">
@@ -4509,94 +4509,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>86.5</v>
+        <v>84.67</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="K10" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M10" t="n">
-        <v>45.12</v>
+        <v>43.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P10" t="n">
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.88</v>
+        <v>52.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.38</v>
+        <v>12.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4680,70 +4680,70 @@
         <v>3.57</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.07</v>
+        <v>7.88</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="BR10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CC10" t="n">
         <v>3.86</v>
@@ -4752,28 +4752,28 @@
         <v>4.19</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI10" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK10" t="n">
         <v>1.77</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CM10" t="n">
         <v>1.93</v>
@@ -4785,10 +4785,10 @@
         <v>1.45</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="inlineStr"/>
@@ -4803,92 +4803,92 @@
       </c>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY10" t="inlineStr"/>
       <c r="CZ10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DB10" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DE10" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DF10" t="n">
-        <v>85.59999999999999</v>
+        <v>84.63</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="DI10" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DK10" t="n">
-        <v>38.06</v>
+        <v>37.37</v>
       </c>
       <c r="DL10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DN10" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="DO10" t="n">
-        <v>11.13</v>
+        <v>11.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>51.94</v>
+        <v>52</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DV10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="DW10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DX10" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="DY10" t="n">
-        <v>16.53</v>
+        <v>16.81</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="EA10" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="11">
@@ -4898,94 +4898,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="M11" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47.57</v>
+        <v>46.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.71</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.29</v>
+        <v>7.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5069,70 +5069,70 @@
         <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.87</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="BQ11" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.44</v>
+        <v>3.68</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC11" t="n">
         <v>7.06</v>
@@ -5144,25 +5144,25 @@
         <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
         <v>1.31</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CK11" t="n">
         <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CM11" t="n">
         <v>2.04</v>
@@ -5171,13 +5171,13 @@
         <v>1.63</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="CR11" t="inlineStr"/>
       <c r="CS11" t="inlineStr"/>
@@ -5200,88 +5200,88 @@
         <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DB11" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="DF11" t="n">
-        <v>62.93</v>
+        <v>61.5</v>
       </c>
       <c r="DG11" t="n">
         <v>0.06</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DI11" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="DK11" t="n">
-        <v>17.13</v>
+        <v>17.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="DN11" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="DO11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DP11" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>44.54</v>
+        <v>44</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DV11" t="n">
-        <v>8.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DW11" t="n">
-        <v>5.27</v>
+        <v>5.75</v>
       </c>
       <c r="DX11" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>15.14</v>
+        <v>15.25</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -5684,94 +5684,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5</v>
+        <v>3.71</v>
       </c>
       <c r="H13" t="n">
-        <v>100.33</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>6.43</v>
       </c>
       <c r="L13" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>42.5</v>
+        <v>40.14</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>10.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="R13" t="n">
-        <v>4.5</v>
+        <v>5.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>57</v>
+        <v>54.71</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.17</v>
+        <v>18.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>14</v>
+        <v>12.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.5</v>
+        <v>17.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5855,67 +5855,67 @@
         <v>3.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.93</v>
+        <v>9.73</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="BR13" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CB13" t="n">
         <v>3.33</v>
@@ -5927,43 +5927,43 @@
         <v>2.68</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CH13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CO13" t="n">
         <v>1.34</v>
       </c>
-      <c r="CI13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="inlineStr"/>
@@ -5977,97 +5977,97 @@
         <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CX13" t="n">
         <v>1.93</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB13" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="DF13" t="n">
-        <v>87.92</v>
+        <v>86.06</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DH13" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DI13" t="n">
-        <v>5.71</v>
+        <v>5.53</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="DK13" t="n">
-        <v>33.07</v>
+        <v>32.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="DN13" t="n">
-        <v>9.859999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>9.789999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DP13" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>51.86</v>
+        <v>51.13</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DV13" t="n">
-        <v>15.28</v>
+        <v>14.93</v>
       </c>
       <c r="DW13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="DX13" t="n">
-        <v>4.79</v>
+        <v>4.94</v>
       </c>
       <c r="DY13" t="n">
-        <v>15.64</v>
+        <v>15.53</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="14">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6564,139 +6564,139 @@
         <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>92.14</v>
+        <v>89.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>28.29</v>
+        <v>28.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.71</v>
+        <v>6.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>52.29</v>
+        <v>51.12</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>1.9</v>
@@ -6705,25 +6705,25 @@
         <v>1.97</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CE15" t="n">
         <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH15" t="n">
         <v>1.35</v>
@@ -6735,16 +6735,16 @@
         <v>1.93</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO15" t="n">
         <v>1.33</v>
@@ -6753,7 +6753,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="inlineStr"/>
@@ -6767,97 +6767,97 @@
         <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
         <v>1.97</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB15" t="n">
         <v>3.68</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DF15" t="n">
-        <v>93.27</v>
+        <v>92</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DH15" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DI15" t="n">
-        <v>5.33</v>
+        <v>5.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DK15" t="n">
-        <v>36</v>
+        <v>35.62</v>
       </c>
       <c r="DL15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DM15" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="DN15" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DO15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DP15" t="n">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>55.2</v>
+        <v>54.44</v>
       </c>
       <c r="DU15" t="n">
         <v>0.06</v>
       </c>
       <c r="DV15" t="n">
-        <v>13.07</v>
+        <v>12.88</v>
       </c>
       <c r="DW15" t="n">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>14.87</v>
+        <v>14.82</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="16">
@@ -8046,13 +8046,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.38</v>
@@ -8136,139 +8136,139 @@
         <v>2.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>83.14</v>
+        <v>83.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AN19" t="n">
-        <v>36.71</v>
+        <v>37.62</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.43</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>44.29</v>
+        <v>46.75</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.71</v>
+        <v>5.88</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.86</v>
+        <v>13.12</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.2</v>
+        <v>10.31</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX19" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BY19" t="n">
         <v>1.93</v>
@@ -8277,55 +8277,55 @@
         <v>1.99</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="CE19" t="n">
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK19" t="n">
         <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM19" t="n">
         <v>2.19</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CR19" t="inlineStr"/>
       <c r="CS19" t="inlineStr"/>
@@ -8351,85 +8351,85 @@
         <v>1.34</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB19" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="DC19" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DE19" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="DF19" t="n">
-        <v>91.06999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="DG19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DH19" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DI19" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="DK19" t="n">
-        <v>38.73</v>
+        <v>39.06</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="DN19" t="n">
-        <v>8.869999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DO19" t="n">
-        <v>8.470000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DP19" t="n">
-        <v>6.54</v>
+        <v>7</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
       </c>
       <c r="DT19" t="n">
-        <v>52.14</v>
+        <v>52.88</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DV19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="DW19" t="n">
-        <v>8.529999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DX19" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="DY19" t="n">
-        <v>12.6</v>
+        <v>12.75</v>
       </c>
       <c r="DZ19" t="n">
         <v>1.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="20">
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -8454,46 +8454,46 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
-        <v>93.62</v>
+        <v>94.78</v>
       </c>
       <c r="I20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="L20" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M20" t="n">
-        <v>45.88</v>
+        <v>45.11</v>
       </c>
       <c r="N20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="P20" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="R20" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -8505,28 +8505,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>47.88</v>
+        <v>49</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.12</v>
+        <v>18.11</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -8610,70 +8610,70 @@
         <v>2.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.33</v>
+        <v>8.44</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
       <c r="BR20" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS20" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU20" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CC20" t="n">
         <v>3.32</v>
@@ -8685,10 +8685,10 @@
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
@@ -8697,28 +8697,28 @@
         <v>1.76</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
@@ -8741,88 +8741,88 @@
         <v>1.82</v>
       </c>
       <c r="CZ20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DA20" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DB20" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="DC20" t="n">
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="DF20" t="n">
-        <v>86.2</v>
+        <v>87.31</v>
       </c>
       <c r="DG20" t="n">
         <v>0.06</v>
       </c>
       <c r="DH20" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DK20" t="n">
-        <v>37.13</v>
+        <v>37.25</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="DN20" t="n">
-        <v>10.33</v>
+        <v>10.18</v>
       </c>
       <c r="DO20" t="n">
-        <v>10.2</v>
+        <v>10.37</v>
       </c>
       <c r="DP20" t="n">
-        <v>8.27</v>
+        <v>8.06</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DS20" t="n">
         <v>0</v>
       </c>
       <c r="DT20" t="n">
-        <v>46.6</v>
+        <v>47.31</v>
       </c>
       <c r="DU20" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DV20" t="n">
-        <v>10.93</v>
+        <v>11.12</v>
       </c>
       <c r="DW20" t="n">
-        <v>7.94</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DX20" t="n">
         <v>3</v>
       </c>
       <c r="DY20" t="n">
-        <v>16.27</v>
+        <v>16.88</v>
       </c>
       <c r="DZ20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EA20" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2532,94 +2532,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>97.2</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>36.6</v>
+        <v>36.82</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="P5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.1</v>
+        <v>7.27</v>
       </c>
       <c r="R5" t="n">
-        <v>7.5</v>
+        <v>8.09</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.2</v>
+        <v>55.82</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>19.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.4</v>
+        <v>11.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.5</v>
+        <v>18.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2703,70 +2703,70 @@
         <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.77</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT5" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CA5" t="n">
         <v>3.57</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC5" t="n">
         <v>2.06</v>
@@ -2781,7 +2781,7 @@
         <v>2.62</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH5" t="n">
         <v>1.43</v>
@@ -2790,16 +2790,16 @@
         <v>1.91</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK5" t="n">
         <v>1.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN5" t="n">
         <v>1.75</v>
@@ -2808,10 +2808,10 @@
         <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CR5" t="n">
         <v>1.96</v>
@@ -2820,7 +2820,7 @@
         <v>1.77</v>
       </c>
       <c r="CT5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CU5" t="n">
         <v>1.94</v>
@@ -2841,52 +2841,52 @@
         <v>1.28</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DF5" t="n">
-        <v>92</v>
+        <v>91.09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DI5" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>34.36</v>
+        <v>34.57</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DM5" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="DN5" t="n">
-        <v>10.86</v>
+        <v>11.04</v>
       </c>
       <c r="DO5" t="n">
         <v>9</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.23</v>
+        <v>8.48</v>
       </c>
       <c r="DQ5" t="n">
         <v>0.13</v>
@@ -2898,28 +2898,28 @@
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>56.14</v>
+        <v>55.52</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DV5" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="DW5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="DX5" t="n">
-        <v>6.37</v>
+        <v>6.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>16.91</v>
+        <v>17.04</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="6">
@@ -3715,13 +3715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3805,49 +3805,49 @@
         <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AI8" t="n">
-        <v>72.7</v>
+        <v>72.27</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.9</v>
+        <v>26.73</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.4</v>
+        <v>9.91</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.5</v>
+        <v>6.91</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3862,82 +3862,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.1</v>
+        <v>49.91</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.1</v>
+        <v>10.45</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>15.8</v>
+        <v>16.27</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.359999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY8" t="n">
         <v>1.9</v>
@@ -3946,55 +3946,55 @@
         <v>1.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="inlineStr"/>
@@ -4008,97 +4008,97 @@
         <v>1.86</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DB8" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DF8" t="n">
-        <v>88.5</v>
+        <v>87.61</v>
       </c>
       <c r="DG8" t="n">
         <v>0.09</v>
       </c>
       <c r="DH8" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="DI8" t="n">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DK8" t="n">
-        <v>32.77</v>
+        <v>32.87</v>
       </c>
       <c r="DL8" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DN8" t="n">
-        <v>10.54</v>
+        <v>10.48</v>
       </c>
       <c r="DO8" t="n">
-        <v>8.68</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.18</v>
+        <v>6.39</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>55.63</v>
+        <v>55.74</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DV8" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="DW8" t="n">
-        <v>8.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DX8" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="DY8" t="n">
-        <v>16.59</v>
+        <v>16.78</v>
       </c>
       <c r="DZ8" t="n">
         <v>1.39</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="9">
@@ -6470,94 +6470,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H15" t="n">
-        <v>88.64</v>
+        <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M15" t="n">
-        <v>39.36</v>
+        <v>41.83</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O15" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="P15" t="n">
-        <v>13.27</v>
+        <v>13.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="R15" t="n">
-        <v>6.91</v>
+        <v>6.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.18</v>
+        <v>57.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.09</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.27</v>
+        <v>9.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.55</v>
+        <v>17.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6641,70 +6641,70 @@
         <v>2.91</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.949999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CA15" t="n">
         <v>3.38</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC15" t="n">
         <v>3.28</v>
@@ -6719,7 +6719,7 @@
         <v>2.71</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH15" t="n">
         <v>1.3</v>
@@ -6734,13 +6734,13 @@
         <v>1.56</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO15" t="n">
         <v>1.26</v>
@@ -6763,97 +6763,97 @@
         <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.97</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.33</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB15" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="DC15" t="n">
         <v>0.13</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DF15" t="n">
-        <v>88.04000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DH15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DI15" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DK15" t="n">
-        <v>34.32</v>
+        <v>35.82</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DM15" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DN15" t="n">
-        <v>11.72</v>
+        <v>11.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>8.82</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DP15" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>53.41</v>
+        <v>54.05</v>
       </c>
       <c r="DU15" t="n">
         <v>0.09</v>
       </c>
       <c r="DV15" t="n">
-        <v>11.77</v>
+        <v>12.3</v>
       </c>
       <c r="DW15" t="n">
-        <v>7.36</v>
+        <v>7.82</v>
       </c>
       <c r="DX15" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="DY15" t="n">
-        <v>14.73</v>
+        <v>15.39</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="16">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0.18</v>
@@ -8918,52 +8918,52 @@
         <v>2.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" t="n">
-        <v>86.64</v>
+        <v>85.08</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>29</v>
+        <v>27.83</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.73</v>
+        <v>9.92</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.45</v>
+        <v>10.75</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -8975,82 +8975,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.09</v>
+        <v>43.08</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.91</v>
+        <v>12.17</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.09</v>
+        <v>7.58</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="BD21" t="n">
-        <v>15.64</v>
+        <v>15.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.59</v>
+        <v>8.65</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL21" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP21" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="BR21" t="n">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS21" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT21" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU21" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV21" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BY21" t="n">
         <v>1.85</v>
@@ -9059,16 +9059,16 @@
         <v>1.97</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CB21" t="n">
         <v>3.36</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CE21" t="n">
         <v>1.32</v>
@@ -9077,13 +9077,13 @@
         <v>2.76</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CH21" t="n">
         <v>1.21</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CJ21" t="n">
         <v>1.82</v>
@@ -9092,22 +9092,22 @@
         <v>1.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ21" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CR21" t="inlineStr"/>
       <c r="CS21" t="inlineStr"/>
@@ -9121,97 +9121,97 @@
         <v>1.81</v>
       </c>
       <c r="CW21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX21" t="n">
         <v>1.91</v>
       </c>
       <c r="CY21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ21" t="n">
         <v>1.4</v>
       </c>
       <c r="DA21" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DB21" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DC21" t="n">
         <v>0.13</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DE21" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DF21" t="n">
-        <v>88.23</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="DG21" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DH21" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DI21" t="n">
-        <v>4.82</v>
+        <v>4.74</v>
       </c>
       <c r="DJ21" t="n">
         <v>0.04</v>
       </c>
       <c r="DK21" t="n">
-        <v>31.68</v>
+        <v>30.95</v>
       </c>
       <c r="DL21" t="n">
         <v>0.87</v>
       </c>
       <c r="DM21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="DP21" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="DQ21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DR21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT21" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="DU21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DV21" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="DW21" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="DX21" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="DY21" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="DZ21" t="n">
         <v>1.41</v>
       </c>
-      <c r="DN21" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="DO21" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="DP21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="DQ21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DR21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT21" t="n">
-        <v>48</v>
-      </c>
-      <c r="DU21" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DV21" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="DW21" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="DX21" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="DY21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="DZ21" t="n">
-        <v>1.45</v>
-      </c>
       <c r="EA21" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2026.xlsx
@@ -2532,13 +2532,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.18</v>
@@ -2622,52 +2622,52 @@
         <v>2.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.67</v>
+        <v>86.92</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.5</v>
+        <v>32.31</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.75</v>
+        <v>11.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.58</v>
+        <v>10.77</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AV5" t="n">
         <v>0.08</v>
@@ -2679,82 +2679,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.25</v>
+        <v>55.46</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.08</v>
+        <v>12.77</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="BD5" t="n">
-        <v>15.58</v>
+        <v>15.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL5" t="n">
         <v>1.17</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.3</v>
@@ -2763,46 +2763,46 @@
         <v>1.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CE5" t="n">
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH5" t="n">
         <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.85</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO5" t="n">
         <v>1.25</v>
@@ -2811,7 +2811,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CR5" t="n">
         <v>1.96</v>
@@ -2829,13 +2829,13 @@
         <v>1.8</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CX5" t="n">
         <v>1.93</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.28</v>
@@ -2844,49 +2844,49 @@
         <v>1.89</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DF5" t="n">
-        <v>91.09</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="DI5" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DK5" t="n">
-        <v>34.57</v>
+        <v>34.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="DM5" t="n">
         <v>1.91</v>
       </c>
       <c r="DN5" t="n">
-        <v>11.04</v>
+        <v>11.13</v>
       </c>
       <c r="DO5" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.48</v>
+        <v>8.41</v>
       </c>
       <c r="DQ5" t="n">
         <v>0.13</v>
@@ -2898,28 +2898,28 @@
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>55.52</v>
+        <v>55.62</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DV5" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="DW5" t="n">
-        <v>9.92</v>
+        <v>9.75</v>
       </c>
       <c r="DX5" t="n">
-        <v>6.39</v>
+        <v>6.25</v>
       </c>
       <c r="DY5" t="n">
-        <v>17.04</v>
+        <v>17</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -6470,25 +6470,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>0.08</v>
@@ -6497,67 +6497,67 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.75</v>
+        <v>6.69</v>
       </c>
       <c r="L15" t="n">
         <v>0.08</v>
       </c>
       <c r="M15" t="n">
-        <v>41.83</v>
+        <v>40.62</v>
       </c>
       <c r="N15" t="n">
         <v>1.08</v>
       </c>
       <c r="O15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>13.33</v>
+        <v>13.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>6.58</v>
+        <v>6.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.17</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>14.54</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.08</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.92</v>
+        <v>5.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.67</v>
+        <v>17.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AF15" t="n">
         <v>0.18</v>
@@ -6641,70 +6641,70 @@
         <v>2.91</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BQ15" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BW15" t="n">
         <v>4.17</v>
       </c>
-      <c r="BR15" t="n">
-        <v>95.65000000000001</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>86.95999999999999</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>4.35</v>
-      </c>
       <c r="BX15" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC15" t="n">
         <v>3.28</v>
@@ -6713,10 +6713,10 @@
         <v>3.94</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
         <v>2.56</v>
@@ -6725,22 +6725,22 @@
         <v>1.3</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO15" t="n">
         <v>1.26</v>
@@ -6763,13 +6763,13 @@
         <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CX15" t="n">
         <v>1.97</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.33</v>
@@ -6781,76 +6781,76 @@
         <v>3.62</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DF15" t="n">
-        <v>89.81999999999999</v>
+        <v>89.08</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DH15" t="n">
         <v>2.96</v>
       </c>
       <c r="DI15" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="DJ15" t="n">
         <v>0.17</v>
       </c>
       <c r="DK15" t="n">
-        <v>35.82</v>
+        <v>35.42</v>
       </c>
       <c r="DL15" t="n">
         <v>1.17</v>
       </c>
       <c r="DM15" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>11.82</v>
+        <v>11.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>8.949999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DP15" t="n">
-        <v>7.39</v>
+        <v>7.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>54.05</v>
+        <v>53.54</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DV15" t="n">
-        <v>12.3</v>
+        <v>12.67</v>
       </c>
       <c r="DW15" t="n">
-        <v>7.82</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DX15" t="n">
-        <v>4.48</v>
+        <v>4.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>15.39</v>
+        <v>15.33</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="EA15" t="n">
         <v>2.83</v>
